--- a/Firmware/Modules/Diag/Diag_Validation.xlsx
+++ b/Firmware/Modules/Diag/Diag_Validation.xlsx
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -767,6 +767,33 @@
       <c r="D11" t="inlineStr">
         <is>
           <t>5 چانک برگردد</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>SaveNow بدون سرریز استک و Init بدون بافر استاتیک اضافه</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>هاست: tools/measure_ram.py (عمق استک تسک ctrl و بودجه RAM) + ریبوت برد و بررسی ماندگاری رکورد</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>قاب SaveNow روی استک تسک کنترل جا شود، رکورد در صفحه قدیمی‌تر با seq+1 نوشته شود و بعد از ریست خوانده شود</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>هاست 2026-10-15: ctrl از 2264/1024 (221%) به 384/1024 (37.5%) رسید و FREE RAM به 1544 بایت؛ تست برد در انتظار</t>
         </is>
       </c>
     </row>
@@ -831,7 +858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -848,6 +875,23 @@
       <c r="C1" t="inlineStr">
         <is>
           <t>اصلاح</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>سرریز RAM هنگام لینک (264 بایت) بعد از استاتیک‌شدن بافرهای Init، و قاب ~2064 بایتی func__Diag_SaveNow روی استک 1024 بایتی تسک کنترل (سرریز استک هنگام ذخیره)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>رزرو هیپ لینکر صفر شد (تخصیص فقط استاتیک است) و Init/SaveNow با بافر کمکی Stage بازنویسی شدند: فقط seqها اسکالر می‌مانند؛ کامیت‌های fix(linker) و fix(Diag) روی شاخه arena/859ce091-changeover</t>
         </is>
       </c>
     </row>

--- a/Firmware/Modules/Diag/Diag_Validation.xlsx
+++ b/Firmware/Modules/Diag/Diag_Validation.xlsx
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -794,6 +794,33 @@
       <c r="E12" t="inlineStr">
         <is>
           <t>هاست 2026-10-15: ctrl از 2264/1024 (221%) به 384/1024 (37.5%) رسید و FREE RAM به 1544 بایت؛ تست برد در انتظار</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ذخیره فلش حین شارژ فعال: تعلیق شارژر دور نوشتن</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>شارژ فعال؛ صبر تا ذخیره دوره‌ای Diag؛ مشاهده گیت‌های PWM روی اسکوپ و ادامه شارژ بعد از ذخیره</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>حین پاک/نوشتن فلش هر دو گیت PWM متوقف، بعد از ذخیره شارژ بدون پرش ادامه یابد و رکورد سالم ذخیره شود</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>هاست: هر دو گیت سبز و بودجه RAM/استک سالم (ctrl ‏384/1024‎، آزاد 1544 بایت)؛ نتیجه برد: در انتظار</t>
         </is>
       </c>
     </row>
@@ -858,7 +885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -892,6 +919,23 @@
       <c r="C2" t="inlineStr">
         <is>
           <t>رزرو هیپ لینکر صفر شد (تخصیص فقط استاتیک است) و Init/SaveNow با بافر کمکی Stage بازنویسی شدند: فقط seqها اسکالر می‌مانند؛ کامیت‌های fix(linker) و fix(Diag) روی شاخه arena/859ce091-changeover</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ممیزی خط‌به‌خط: ذخیره فلش Diag (حین شارژ حدود هر ۶۰ ثانیه) برخلاف ذخیره‌های NVM و CalLut شارژر را معلق نمی‌کرد؛ پاک‌کردن صفحه کل CPU را ۲۰ تا ۴۰ میلی‌ثانیه نگه می‌دارد و گیت‌ها داخل پنجره کور سوییچ می‌کردند</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>در func__Diag_SaveNow دور WriteFlash، ‏func__Charger_SetSuspended(true)‎ + ‏func__BspPwm_StopAll()‎ و بعد ‏SetSuspended(false)‎ اضافه شد (زمینه تسک کنترل، توقف بی‌درنگ، آینه duty دست‌نخورده)؛ هر دو گیت سبز</t>
         </is>
       </c>
     </row>

--- a/Firmware/Modules/Diag/Diag_Validation.xlsx
+++ b/Firmware/Modules/Diag/Diag_Validation.xlsx
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -821,6 +821,50 @@
       <c r="E13" t="inlineStr">
         <is>
           <t>هاست: هر دو گیت سبز و بودجه RAM/استک سالم (ctrl ‏384/1024‎، آزاد 1544 بایت)؛ نتیجه برد: در انتظار</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>شمارنده‌های خطا با نام FAULT_* رمزگشایی می‌شوند (نه شماره خام بیت)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>هاست: python3 tools/check_diag_fault_bits.py + مقایسه اسمبلی func__Diag_RecordFault قبل/بعد؛ برد: واداشتن خطای قطع باتری و خطای فنی و خواندن شمارنده‌ها از پنل</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>چک هاست PASS؛ اسمبلی تابع قبل/بعد بایت‌به‌بایت یکسان؛ روی برد هر رویداد فقط شمارنده خودش را زیاد کند</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>هاست 2026-10-15: چک‌نگهبان اول روی کد قدیم FAIL شد (هر سه خط خام را گرفت)، بعد از اصلاح PASS؛ اسمبلی یکسان؛ هر دو گیت سبز؛ نتیجه برد: در انتظار</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ممیزی خط‌به‌خط (مورد ۶): func__Diag_RecordFault شمارنده‌ها را با شماره خام بیت (‏1u &lt;&lt; 6‎، ‏1u &lt;&lt; 7‎ و بیت ۰) رمزگشایی می‌کرد؛ جابه‌جایی بیت‌های FAULT در app_types.h بی‌صدا آمار را غلط می‌کرد و کامنت «reuse for ADC» روی شمارنده ovCount گمراه‌کننده بود</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>هر سه شرط با ثابت‌های نام‌دار FAULT_CHARGER_BAT_LOST / FAULT_CHARGER_TECHNICAL / FAULT_ADC نوشته شد (نام فیلد ovCount به‌خاطر چیدمان رکورد فلش ماند)؛ نگهبان tools/check_diag_fault_bits.py اضافه شد تا برگشت شماره خام برای همیشه FAIL شود؛ یکسانی رفتار با مقایسه اسمبلی ثابت شد</t>
         </is>
       </c>
     </row>

--- a/Firmware/Modules/Diag/Diag_Validation.xlsx
+++ b/Firmware/Modules/Diag/Diag_Validation.xlsx
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -848,23 +848,6 @@
       <c r="E14" t="inlineStr">
         <is>
           <t>هاست 2026-10-15: چک‌نگهبان اول روی کد قدیم FAIL شد (هر سه خط خام را گرفت)، بعد از اصلاح PASS؛ اسمبلی یکسان؛ هر دو گیت سبز؛ نتیجه برد: در انتظار</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>ممیزی خط‌به‌خط (مورد ۶): func__Diag_RecordFault شمارنده‌ها را با شماره خام بیت (‏1u &lt;&lt; 6‎، ‏1u &lt;&lt; 7‎ و بیت ۰) رمزگشایی می‌کرد؛ جابه‌جایی بیت‌های FAULT در app_types.h بی‌صدا آمار را غلط می‌کرد و کامنت «reuse for ADC» روی شمارنده ovCount گمراه‌کننده بود</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>هر سه شرط با ثابت‌های نام‌دار FAULT_CHARGER_BAT_LOST / FAULT_CHARGER_TECHNICAL / FAULT_ADC نوشته شد (نام فیلد ovCount به‌خاطر چیدمان رکورد فلش ماند)؛ نگهبان tools/check_diag_fault_bits.py اضافه شد تا برگشت شماره خام برای همیشه FAIL شود؛ یکسانی رفتار با مقایسه اسمبلی ثابت شد</t>
         </is>
       </c>
     </row>
@@ -929,7 +912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -980,6 +963,23 @@
       <c r="C3" t="inlineStr">
         <is>
           <t>در func__Diag_SaveNow دور WriteFlash، ‏func__Charger_SetSuspended(true)‎ + ‏func__BspPwm_StopAll()‎ و بعد ‏SetSuspended(false)‎ اضافه شد (زمینه تسک کنترل، توقف بی‌درنگ، آینه duty دست‌نخورده)؛ هر دو گیت سبز</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ممیزی خط‌به‌خط (مورد ۶): func__Diag_RecordFault شمارنده‌ها را با شماره خام بیت (‏1u &lt;&lt; 6‎، ‏1u &lt;&lt; 7‎ و بیت ۰) رمزگشایی می‌کرد؛ جابه‌جایی بیت‌های FAULT در app_types.h بی‌صدا آمار را غلط می‌کرد و کامنت «reuse for ADC» روی شمارنده ovCount گمراه‌کننده بود</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>هر سه شرط با ثابت‌های نام‌دار FAULT_CHARGER_BAT_LOST / FAULT_CHARGER_TECHNICAL / FAULT_ADC نوشته شد (نام فیلد ovCount به‌خاطر چیدمان رکورد فلش ماند)؛ نگهبان tools/check_diag_fault_bits.py اضافه شد تا برگشت شماره خام برای همیشه FAIL شود؛ یکسانی رفتار با مقایسه اسمبلی ثابت شد</t>
         </is>
       </c>
     </row>

--- a/Firmware/Modules/Diag/Diag_Validation.xlsx
+++ b/Firmware/Modules/Diag/Diag_Validation.xlsx
@@ -498,7 +498,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>11 مورد ذخیره روی برد تأیید شد: 1) زمان کل شارژ هر کانال+مجموع، 2) تعداد شارژ کامل، 3) آپتایم کل+از آخرین ریست، 4) تعداد ریست، 5) ماکس/مین ولتاژها (Vin/Vpack/Vlow/Vhigh/Imb)، 6) جریان ماکس هر کانال، 7) 10 خطای آخر با ساعت، 8) لاگ 20 قطع/وصل برق شهر، 9) شمارنده‌ها (عدم تعادل/باتری کم/قطع/فنی/اضافه ولتاژ)، 10) زمان همگام‌سازی ساعت، 11) نسخه/UID</t>
+          <t>11 مورد ذخیره روی برد تأیید شد: 1) زمان کل شارژ هر کانال+مجموع، 2) تعداد شارژ کامل، 3) آپتایم کل+از آخرین ریست، 4) تعداد ریست، 5) ماکس/مین ولتاژها (Vin/Vpack/Vlow/Vhigh/Imb)، 6) جریان ماکس هر کانال، 7) 10 خطای آخر با ساعت، 8) لاگ 20 قطع/وصل برق شهر، 9) شمارنده‌ها (عدم تعادل/باتری کم/قطع FAULT_CHARGER_BAT_LOST/فنی FAULT_CHARGER_TECHNICAL/FAULT_ADC)، 10) زمان همگام‌سازی ساعت، 11) نسخه/UID</t>
         </is>
       </c>
     </row>

--- a/Firmware/Modules/Diag/Diag_Validation.xlsx
+++ b/Firmware/Modules/Diag/Diag_Validation.xlsx
@@ -739,7 +739,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ارسال 0x30 با unix</t>
+          <t>ارسال فرمان 48 (TIME_SYNC) با زمان یونیکس</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -761,7 +761,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ارسال 0x31</t>
+          <t>ارسال فرمان 49 (DIAG_REQ)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">

--- a/Firmware/Modules/Diag/Diag_Validation.xlsx
+++ b/Firmware/Modules/Diag/Diag_Validation.xlsx
@@ -563,7 +563,9 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>فلش پاک</t>
+          <t>گام ۱: فلش هر دو صفحهٔ Diag (نشانی 1032192 و 1033216) را کامل پاک کن.
+گام ۲: برد را بوت کن و رکورد خوانده‌شده را از پنل بخوان.
+گام ۳: باید رکورد پیش‌فرض ساخته شده باشد: کمینه‌ها 4294967295 (بزرگ‌ترین عدد 32 بیتی) و همهٔ شمارنده‌ها صفر.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -585,7 +587,9 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>نوشتن رکورد A با CRC درست</t>
+          <t>گام ۱: یک رکورد سالم با CRC درست در صفحهٔ A بنویس و بقیهٔ فلش را خالی بگذار.
+گام ۲: برد را بوت کن.
+گام ۳: رکورد خوانده‌شده را با همان رکوردی که نوشتی مقایسه کن؛ باید عیناً همان باشد (CRC درست یعنی پذیرفته شده).</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -607,7 +611,9 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>A seq=1 B seq=2</t>
+          <t>گام ۱: در صفحهٔ A رکورد سالم با شمارهٔ ترتیب (seq) برابر 1 و در صفحهٔ B رکورد سالم با seq برابر 2 بنویس.
+گام ۲: برد را بوت کن.
+گام ۳: رکورد فعال باید رکورد صفحهٔ B باشد، چون جدیدتر است (seq بزرگ‌تر برنده است).</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -629,7 +635,9 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>کانال 0 و 1 هر کدام 3600 ثانیه</t>
+          <t>گام ۱: برد را بوت کن و شمارنده‌های زمان شارژ را صفرِ شروع در نظر بگیر.
+گام ۲: برای کانال 0 مقدار 3600 ثانیه و برای کانال 1 هم 3600 ثانیه شارژ ثبت کن (func__Diag_AddChargeSec).
+گام ۳: شمارنده‌ها را بخوان: مجموع (total) باید 7200 شده باشد و شمارندهٔ هر کانال 3600.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -651,7 +659,9 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>چند بار</t>
+          <t>گام ۱: برد را بوت کن.
+گام ۲: چند بار (مثلاً 3 بار) پایان شارژ کامل را ثبت کن (func__Diag_RecordChargeComplete).
+گام ۳: شمارندهٔ chargeCount را بخوان؛ باید دقیقاً به همان تعداد دفعات بالا رفته باشد.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -673,7 +683,9 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>باتری قطع با snapshot</t>
+          <t>گام ۱: یک snapshot معتبر با ولتاژهای معلوم آماده کن.
+گام ۲: خطای قطع باتری (FAULT_CHARGER_BAT_LOST) را همراه همان snapshot ثبت کن (func__Diag_RecordFault).
+گام ۳: لیست 10 خطای آخر را بخوان: این رویداد باید در اول لیست باشد، با ساعت برد و همان ولتاژهای snapshot.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -695,7 +707,10 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>قطع سپس وصل</t>
+          <t>گام ۱: ساعت برد را همگام کن تا زمان‌ها معنادار باشند.
+گام ۲: برق شهر (ورودی) را قطع کن و چند ثانیه صبر کن.
+گام ۳: ورودی را دوباره وصل کن.
+گام ۴: در لاگ 20 رویداد برق، ردیف تازه را بخوان: زمان قطع (offTime)، زمان وصل (onTime) و مدت قطع (duration) باید درست و با ساعت واقعی یکی باشد.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -717,7 +732,9 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vin 0..32V</t>
+          <t>گام ۱: ولتاژ ورودی را از 0 تا 32 ولت آهسته بالا و پایین ببر (منبع متغیر).
+گام ۲: در چند نقطهٔ معلوم (مثلاً 12، 24 و 30 ولت) توقف کن تا نمونه‌برداری انجام شود.
+گام ۳: کمینه و بیشینهٔ ثبت‌شدهٔ Vin را بخوان؛ باید با کمترین و بیشترین ولتاژی که دادی یکی باشد.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -739,7 +756,9 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ارسال فرمان 48 (TIME_SYNC) با زمان یونیکس</t>
+          <t>گام ۱: زمان یونیکس فعلی را از کامپیوتر بگیر.
+گام ۲: فرمان 48 (TIME_SYNC) را با همان زمان یونیکس از لینک ESP بفرست.
+گام ۳: boardTimeBase را بخوان: باید برابر «زمان یونیکس منهای آپتایم برد» باشد، یعنی از این به بعد ساعت برد برابر ساعت واقعی می‌شود.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -761,7 +780,9 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ارسال فرمان 49 (DIAG_REQ)</t>
+          <t>گام ۱: لینک ESP را فعال و سالم نگه دار.
+گام ۲: فرمان 49 (DIAG_REQ) را بفرست.
+گام ۳: پاسخ‌ها را جمع کن: باید کل رکورد در 5 چانک برگردد و CRC رکورد درست باشد.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -783,7 +804,9 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>هاست: tools/measure_ram.py (عمق استک تسک ctrl و بودجه RAM) + ریبوت برد و بررسی ماندگاری رکورد</t>
+          <t>گام ۱ (هاست): ابزار tools/measure_ram.py را اجرا کن و عمق استک تسک کنترل (ctrl) و حافظهٔ آزاد را بخوان.
+گام ۲ (هاست): قاب func__Diag_SaveNow باید روی استک تسک کنترل جا شده باشد و هیچ بافر استاتیک اضافه‌ای در Init نباشد.
+گام ۳ (برد): برد را ریبوت کن و رکورد ذخیره‌شده را بخوان: باید در صفحهٔ قدیمی‌تر با seq+1 نوشته شده و بعد از ریست سالم خوانده شود.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -810,7 +833,10 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>شارژ فعال؛ صبر تا ذخیره دوره‌ای Diag؛ مشاهده گیت‌های PWM روی اسکوپ و ادامه شارژ بعد از ذخیره</t>
+          <t>گام ۱: شارژ واقعی را فعال کن (کانال در BULK باشد) و اسیلوسکوپ را روی گیت هر دو کانال بگذار.
+گام ۲: صبر کن ذخیرهٔ دوره‌ای Diag خودش برسد (حدود هر 60 ثانیه).
+گام ۳: لحظهٔ پاک/نوشتن فلش روی اسکوپ: هر دو گیت PWM باید متوقف باشند.
+گام ۴: بلافاصله بعد از ذخیره، شارژ باید بدون پرش ادامه پیدا کند و رکورد هم سالم ذخیره شده باشد. نتیجهٔ برد هنوز در انتظار است.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -837,7 +863,10 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>هاست: python3 tools/check_diag_fault_bits.py + مقایسه اسمبلی func__Diag_RecordFault قبل/بعد؛ برد: واداشتن خطای قطع باتری و خطای فنی و خواندن شمارنده‌ها از پنل</t>
+          <t>گام ۱ (هاست): python3 tools/check_diag_fault_bits.py را اجرا کن؛ باید PASS بدهد (قبل از اصلاح روی کد قدیم FAIL می‌شد).
+گام ۲ (هاست): اسمبلی تابع func__Diag_RecordFault قبل و بعد از اصلاح را مقایسه کن؛ باید بایت‌به‌بایت یکی باشد.
+گام ۳ (برد): از پنل یک‌بار خطای قطع باتری و یک‌بار خطای فنی بساز.
+گام ۴ (برد): شمارنده‌ها را بخوان: هر رویداد باید فقط شمارندهٔ خودش را زیاد کرده باشد (قطع باتری ← FAULT_CHARGER_BAT_LOST، فنی ← FAULT_CHARGER_TECHNICAL، ADC ← شمارندهٔ ovCount). نتیجهٔ برد هنوز در انتظار است.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">

--- a/Firmware/Modules/Diag/Diag_Validation.xlsx
+++ b/Firmware/Modules/Diag/Diag_Validation.xlsx
@@ -1056,7 +1056,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1092,6 +1092,18 @@
       <c r="B3" t="inlineStr">
         <is>
           <t>پیاده‌سازی فلش و لاگ</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>README.md</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>شرح ماژول، رکورد و مسیر تست</t>
         </is>
       </c>
     </row>

--- a/Firmware/Modules/Diag/Diag_Validation.xlsx
+++ b/Firmware/Modules/Diag/Diag_Validation.xlsx
@@ -15,15 +15,20 @@
     <sheet name="فهرست‌ها" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="ماشین حالت" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$1:$G$14</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'برنامه تست'!$1:$1</definedName>
+  </definedNames>
+  <calcPr calcId="124519" fullCalcOnLoad="1" iterate="1" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="5">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,8 +57,46 @@
       <name val="Vazirmatn"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Tahoma"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <color rgb="000563C1"/>
+      <sz val="11"/>
+      <u val="single"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -65,8 +108,18 @@
         <fgColor rgb="001F3864"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F6FC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E2F3"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -88,11 +141,25 @@
         <color rgb="009DB7E8"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B4C6E7"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B4C6E7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B4C6E7"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -106,6 +173,54 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -468,6 +583,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="007F7F7F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -475,35 +591,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>برگه تست و اعتبارسنجی عملی ماژول Diag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>Diag | لاگ تشخیصی 11 مورد تأییدشده: زمان کل شارژ هر کانال+مجموع، تعداد شارژ کامل، آپتایم کل+از آخرین ریست، تعداد ریست، ماکس/مین ولتاژها، جریان ماکس، 10 خطای آخر با ساعت، لاگ 20 قطع/وصل، شمارنده‌ها، زمان همگام‌سازی، نسخه/UID</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>هدف فایل</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>11 مورد ذخیره روی برد تأیید شد: 1) زمان کل شارژ هر کانال+مجموع، 2) تعداد شارژ کامل، 3) آپتایم کل+از آخرین ریست، 4) تعداد ریست، 5) ماکس/مین ولتاژها (Vin/Vpack/Vlow/Vhigh/Imb)، 6) جریان ماکس هر کانال، 7) 10 خطای آخر با ساعت، 8) لاگ 20 قطع/وصل برق شهر، 9) شمارنده‌ها (عدم تعادل/باتری کم/قطع FAULT_CHARGER_BAT_LOST/فنی FAULT_CHARGER_TECHNICAL/FAULT_ADC)، 10) زمان همگام‌سازی ساعت، 11) نسخه/UID</t>
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>تست‌ها: 1) فلش ping-pong 0x0800F800/0xFC00 با CRC32، 2) Init انتخاب رکورد سالم با seq جدیدتر، 3) AddChargeSec هر کانال، 4) RecordChargeComplete، 5) RecordFault با snapshot کامل، 6) RecordPowerOff/On با محاسبه duration، 7) UpdateMinMax، 8) Tick هر ثانیه + debounce save 60s، 9) TIME_SYNC از ESP، 10) DIAG_REQ و ارسال 5 چانک</t>
         </is>
@@ -517,195 +635,251 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001F4E79"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>ردیف</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>شرح تست</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>روش</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>نتیجه مورد انتظار</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>نتیجه واقعی</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
+        <is>
+          <t>وضعیت</t>
+        </is>
+      </c>
+      <c r="G1" s="6" t="inlineStr">
+        <is>
+          <t>تاریخ</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="40.5" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>Init بدون رکورد</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>گام ۱: فلش هر دو صفحهٔ Diag (نشانی 1032192 و 1033216) را کامل پاک کن.
 گام ۲: برد را بوت کن و رکورد خوانده‌شده را از پنل بخوان.
 گام ۳: باید رکورد پیش‌فرض ساخته شده باشد: کمینه‌ها 4294967295 (بزرگ‌ترین عدد 32 بیتی) و همهٔ شمارنده‌ها صفر.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>پیش‌فرض با min=0xFFFFFFFF و شمارنده صفر</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="E2" s="8" t="n"/>
+      <c r="F2" s="10" t="n"/>
+      <c r="G2" s="11">
+        <f>IF(OR(F2="",F2="در انتظار"),"",IF(G2="",TODAY(),G2))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="40.5" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>Init با یک رکورد سالم</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>گام ۱: یک رکورد سالم با CRC درست در صفحهٔ A بنویس و بقیهٔ فلش را خالی بگذار.
 گام ۲: برد را بوت کن.
 گام ۳: رکورد خوانده‌شده را با همان رکوردی که نوشتی مقایسه کن؛ باید عیناً همان باشد (CRC درست یعنی پذیرفته شده).</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>همان رکورد خوانده شود</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="E3" s="12" t="n"/>
+      <c r="F3" s="14" t="n"/>
+      <c r="G3" s="15">
+        <f>IF(OR(F3="",F3="در انتظار"),"",IF(G3="",TODAY(),G3))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="40.5" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Init با دو رکورد سالم</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>گام ۱: در صفحهٔ A رکورد سالم با شمارهٔ ترتیب (seq) برابر 1 و در صفحهٔ B رکورد سالم با seq برابر 2 بنویس.
 گام ۲: برد را بوت کن.
 گام ۳: رکورد فعال باید رکورد صفحهٔ B باشد، چون جدیدتر است (seq بزرگ‌تر برنده است).</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>B برنده (جدیدتر)</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="E4" s="8" t="n"/>
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="11">
+        <f>IF(OR(F4="",F4="در انتظار"),"",IF(G4="",TODAY(),G4))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="40.5" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>AddChargeSec</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>گام ۱: برد را بوت کن و شمارنده‌های زمان شارژ را صفرِ شروع در نظر بگیر.
 گام ۲: برای کانال 0 مقدار 3600 ثانیه و برای کانال 1 هم 3600 ثانیه شارژ ثبت کن (func__Diag_AddChargeSec).
 گام ۳: شمارنده‌ها را بخوان: مجموع (total) باید 7200 شده باشد و شمارندهٔ هر کانال 3600.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>total و per-channel افزایش</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="E5" s="12" t="n"/>
+      <c r="F5" s="14" t="n"/>
+      <c r="G5" s="15">
+        <f>IF(OR(F5="",F5="در انتظار"),"",IF(G5="",TODAY(),G5))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="40.5" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>RecordChargeComplete</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>گام ۱: برد را بوت کن.
 گام ۲: چند بار (مثلاً 3 بار) پایان شارژ کامل را ثبت کن (func__Diag_RecordChargeComplete).
 گام ۳: شمارندهٔ chargeCount را بخوان؛ باید دقیقاً به همان تعداد دفعات بالا رفته باشد.</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>chargeCount افزایش</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="E6" s="8" t="n"/>
+      <c r="F6" s="10" t="n"/>
+      <c r="G6" s="11">
+        <f>IF(OR(F6="",F6="در انتظار"),"",IF(G6="",TODAY(),G6))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="40.5" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>RecordFault</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>گام ۱: یک snapshot معتبر با ولتاژهای معلوم آماده کن.
 گام ۲: خطای قطع باتری (FAULT_CHARGER_BAT_LOST) را همراه همان snapshot ثبت کن (func__Diag_RecordFault).
 گام ۳: لیست 10 خطای آخر را بخوان: این رویداد باید در اول لیست باشد، با ساعت برد و همان ولتاژهای snapshot.</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>در لیست 10تایی با زمان</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="E7" s="12" t="n"/>
+      <c r="F7" s="14" t="n"/>
+      <c r="G7" s="15">
+        <f>IF(OR(F7="",F7="در انتظار"),"",IF(G7="",TODAY(),G7))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="54" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>PowerOff/On</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>گام ۱: ساعت برد را همگام کن تا زمان‌ها معنادار باشند.
 گام ۲: برق شهر (ورودی) را قطع کن و چند ثانیه صبر کن.
@@ -713,125 +887,154 @@
 گام ۴: در لاگ 20 رویداد برق، ردیف تازه را بخوان: زمان قطع (offTime)، زمان وصل (onTime) و مدت قطع (duration) باید درست و با ساعت واقعی یکی باشد.</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>offTime/onTime/duration درست</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="10" t="n"/>
+      <c r="G8" s="11">
+        <f>IF(OR(F8="",F8="در انتظار"),"",IF(G8="",TODAY(),G8))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="40.5" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>Min/Max</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t>گام ۱: ولتاژ ورودی را از 0 تا 32 ولت آهسته بالا و پایین ببر (منبع متغیر).
 گام ۲: در چند نقطهٔ معلوم (مثلاً 12، 24 و 30 ولت) توقف کن تا نمونه‌برداری انجام شود.
 گام ۳: کمینه و بیشینهٔ ثبت‌شدهٔ Vin را بخوان؛ باید با کمترین و بیشترین ولتاژی که دادی یکی باشد.</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t>max/min به‌روز</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="E9" s="12" t="n"/>
+      <c r="F9" s="14" t="n"/>
+      <c r="G9" s="15">
+        <f>IF(OR(F9="",F9="در انتظار"),"",IF(G9="",TODAY(),G9))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="40.5" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>TIME_SYNC</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>گام ۱: زمان یونیکس فعلی را از کامپیوتر بگیر.
 گام ۲: فرمان 48 (TIME_SYNC) را با همان زمان یونیکس از لینک ESP بفرست.
 گام ۳: boardTimeBase را بخوان: باید برابر «زمان یونیکس منهای آپتایم برد» باشد، یعنی از این به بعد ساعت برد برابر ساعت واقعی می‌شود.</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>boardTimeBase = unix - uptime</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="10" t="n"/>
+      <c r="G10" s="11">
+        <f>IF(OR(F10="",F10="در انتظار"),"",IF(G10="",TODAY(),G10))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="40.5" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>DIAG_REQ</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>گام ۱: لینک ESP را فعال و سالم نگه دار.
 گام ۲: فرمان 49 (DIAG_REQ) را بفرست.
 گام ۳: پاسخ‌ها را جمع کن: باید کل رکورد در 5 چانک برگردد و CRC رکورد درست باشد.</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t>5 چانک برگردد</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="E11" s="12" t="n"/>
+      <c r="F11" s="14" t="n"/>
+      <c r="G11" s="15">
+        <f>IF(OR(F11="",F11="در انتظار"),"",IF(G11="",TODAY(),G11))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="40.5" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>SaveNow بدون سرریز استک و Init بدون بافر استاتیک اضافه</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="21" t="inlineStr">
         <is>
           <t>گام ۱ (هاست): ابزار tools/measure_ram.py را اجرا کن و عمق استک تسک کنترل (ctrl) و حافظهٔ آزاد را بخوان.
 گام ۲ (هاست): قاب func__Diag_SaveNow باید روی استک تسک کنترل جا شده باشد و هیچ بافر استاتیک اضافه‌ای در Init نباشد.
 گام ۳ (برد): برد را ریبوت کن و رکورد ذخیره‌شده را بخوان: باید در صفحهٔ قدیمی‌تر با seq+1 نوشته شده و بعد از ریست سالم خوانده شود.</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>قاب SaveNow روی استک تسک کنترل جا شود، رکورد در صفحه قدیمی‌تر با seq+1 نوشته شود و بعد از ریست خوانده شود</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>هاست 2026-10-15: ctrl از 2264/1024 (221%) به 384/1024 (37.5%) رسید و FREE RAM به 1544 بایت؛ تست برد در انتظار</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="F12" s="10" t="n"/>
+      <c r="G12" s="11">
+        <f>IF(OR(F12="",F12="در انتظار"),"",IF(G12="",TODAY(),G12))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="54" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>ذخیره فلش حین شارژ فعال: تعلیق شارژر دور نوشتن</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t>گام ۱: شارژ واقعی را فعال کن (کانال در BULK باشد) و اسیلوسکوپ را روی گیت هر دو کانال بگذار.
 گام ۲: صبر کن ذخیرهٔ دوره‌ای Diag خودش برسد (حدود هر 60 ثانیه).
@@ -839,29 +1042,34 @@
 گام ۴: بلافاصله بعد از ذخیره، شارژ باید بدون پرش ادامه پیدا کند و رکورد هم سالم ذخیره شده باشد. نتیجهٔ برد هنوز در انتظار است.</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="12" t="inlineStr">
         <is>
           <t>حین پاک/نوشتن فلش هر دو گیت PWM متوقف، بعد از ذخیره شارژ بدون پرش ادامه یابد و رکورد سالم ذخیره شود</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="12" t="inlineStr">
         <is>
           <t>هاست: هر دو گیت سبز و بودجه RAM/استک سالم (ctrl ‏384/1024‎، آزاد 1544 بایت)؛ نتیجه برد: در انتظار</t>
         </is>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="F13" s="14" t="n"/>
+      <c r="G13" s="15">
+        <f>IF(OR(F13="",F13="در انتظار"),"",IF(G13="",TODAY(),G13))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="54" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>شمارنده‌های خطا با نام FAULT_* رمزگشایی می‌شوند (نه شماره خام بیت)</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="21" t="inlineStr">
         <is>
           <t>گام ۱ (هاست): python3 tools/check_diag_fault_bits.py را اجرا کن؛ باید PASS بدهد (قبل از اصلاح روی کد قدیم FAIL می‌شد).
 گام ۲ (هاست): اسمبلی تابع func__Diag_RecordFault قبل و بعد از اصلاح را مقایسه کن؛ باید بایت‌به‌بایت یکی باشد.
@@ -869,68 +1077,329 @@
 گام ۴ (برد): شمارنده‌ها را بخوان: هر رویداد باید فقط شمارندهٔ خودش را زیاد کرده باشد (قطع باتری ← FAULT_CHARGER_BAT_LOST، فنی ← FAULT_CHARGER_TECHNICAL، ADC ← شمارندهٔ ovCount). نتیجهٔ برد هنوز در انتظار است.</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>چک هاست PASS؛ اسمبلی تابع قبل/بعد بایت‌به‌بایت یکسان؛ روی برد هر رویداد فقط شمارنده خودش را زیاد کند</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>هاست 2026-10-15: چک‌نگهبان اول روی کد قدیم FAIL شد (هر سه خط خام را گرفت)، بعد از اصلاح PASS؛ اسمبلی یکسان؛ هر دو گیت سبز؛ نتیجه برد: در انتظار</t>
         </is>
       </c>
+      <c r="F14" s="10" t="n"/>
+      <c r="G14" s="11">
+        <f>IF(OR(F14="",F14="در انتظار"),"",IF(G14="",TODAY(),G14))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="G15" s="16">
+        <f>IF(OR(F15="",F15="در انتظار"),"",IF(G15="",TODAY(),G15))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="G16" s="16">
+        <f>IF(OR(F16="",F16="در انتظار"),"",IF(G16="",TODAY(),G16))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="G17" s="16">
+        <f>IF(OR(F17="",F17="در انتظار"),"",IF(G17="",TODAY(),G17))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="G18" s="16">
+        <f>IF(OR(F18="",F18="در انتظار"),"",IF(G18="",TODAY(),G18))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="G19" s="16">
+        <f>IF(OR(F19="",F19="در انتظار"),"",IF(G19="",TODAY(),G19))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="G20" s="16">
+        <f>IF(OR(F20="",F20="در انتظار"),"",IF(G20="",TODAY(),G20))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="G21" s="16">
+        <f>IF(OR(F21="",F21="در انتظار"),"",IF(G21="",TODAY(),G21))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="G22" s="16">
+        <f>IF(OR(F22="",F22="در انتظار"),"",IF(G22="",TODAY(),G22))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="G23" s="16">
+        <f>IF(OR(F23="",F23="در انتظار"),"",IF(G23="",TODAY(),G23))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="G24" s="16">
+        <f>IF(OR(F24="",F24="در انتظار"),"",IF(G24="",TODAY(),G24))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="G25" s="16">
+        <f>IF(OR(F25="",F25="در انتظار"),"",IF(G25="",TODAY(),G25))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="G26" s="16">
+        <f>IF(OR(F26="",F26="در انتظار"),"",IF(G26="",TODAY(),G26))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="G27" s="16">
+        <f>IF(OR(F27="",F27="در انتظار"),"",IF(G27="",TODAY(),G27))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="G28" s="16">
+        <f>IF(OR(F28="",F28="در انتظار"),"",IF(G28="",TODAY(),G28))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="G29" s="16">
+        <f>IF(OR(F29="",F29="در انتظار"),"",IF(G29="",TODAY(),G29))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="G30" s="16">
+        <f>IF(OR(F30="",F30="در انتظار"),"",IF(G30="",TODAY(),G30))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="G31" s="16">
+        <f>IF(OR(F31="",F31="در انتظار"),"",IF(G31="",TODAY(),G31))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="G32" s="16">
+        <f>IF(OR(F32="",F32="در انتظار"),"",IF(G32="",TODAY(),G32))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="G33" s="16">
+        <f>IF(OR(F33="",F33="در انتظار"),"",IF(G33="",TODAY(),G33))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="G34" s="16">
+        <f>IF(OR(F34="",F34="در انتظار"),"",IF(G34="",TODAY(),G34))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="G35" s="16">
+        <f>IF(OR(F35="",F35="در انتظار"),"",IF(G35="",TODAY(),G35))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="G36" s="16">
+        <f>IF(OR(F36="",F36="در انتظار"),"",IF(G36="",TODAY(),G36))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="G37" s="16">
+        <f>IF(OR(F37="",F37="در انتظار"),"",IF(G37="",TODAY(),G37))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="G38" s="16">
+        <f>IF(OR(F38="",F38="در انتظار"),"",IF(G38="",TODAY(),G38))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="G39" s="16">
+        <f>IF(OR(F39="",F39="در انتظار"),"",IF(G39="",TODAY(),G39))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="G40" s="16">
+        <f>IF(OR(F40="",F40="در انتظار"),"",IF(G40="",TODAY(),G40))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="G41" s="16">
+        <f>IF(OR(F41="",F41="در انتظار"),"",IF(G41="",TODAY(),G41))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="G42" s="16">
+        <f>IF(OR(F42="",F42="در انتظار"),"",IF(G42="",TODAY(),G42))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="G43" s="16">
+        <f>IF(OR(F43="",F43="در انتظار"),"",IF(G43="",TODAY(),G43))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="G44" s="16">
+        <f>IF(OR(F44="",F44="در انتظار"),"",IF(G44="",TODAY(),G44))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="G45" s="16">
+        <f>IF(OR(F45="",F45="در انتظار"),"",IF(G45="",TODAY(),G45))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="G46" s="16">
+        <f>IF(OR(F46="",F46="در انتظار"),"",IF(G46="",TODAY(),G46))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="G47" s="16">
+        <f>IF(OR(F47="",F47="در انتظار"),"",IF(G47="",TODAY(),G47))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="G48" s="16">
+        <f>IF(OR(F48="",F48="در انتظار"),"",IF(G48="",TODAY(),G48))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="G49" s="16">
+        <f>IF(OR(F49="",F49="در انتظار"),"",IF(G49="",TODAY(),G49))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="G50" s="16">
+        <f>IF(OR(F50="",F50="در انتظار"),"",IF(G50="",TODAY(),G50))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="G51" s="16">
+        <f>IF(OR(F51="",F51="در انتظار"),"",IF(G51="",TODAY(),G51))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="G52" s="16">
+        <f>IF(OR(F52="",F52="در انتظار"),"",IF(G52="",TODAY(),G52))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="G53" s="16">
+        <f>IF(OR(F53="",F53="در انتظار"),"",IF(G53="",TODAY(),G53))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="G54" s="16">
+        <f>IF(OR(F54="",F54="در انتظار"),"",IF(G54="",TODAY(),G54))</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G14"/>
+  <dataValidations count="1">
+    <dataValidation sqref="F2:F94" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" prompt="وضعیت تست را از فهرست انتخاب کنید" type="list">
+      <formula1>='فهرست‌ها'!$A$7:$A$12</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00BF8F00"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>سناریو</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>مرجع کد</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>ذخیره فلش</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="22" t="inlineStr">
         <is>
           <t>diag.c func__Diag_WriteFlash</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>پروتکل ESP</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="22" t="inlineStr">
         <is>
           <t>esp_link.c SendDiagChunk/SendDiagAll</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -938,6 +1407,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00C00000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -945,74 +1415,78 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>شرح ایراد</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>اصلاح</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>سرریز RAM هنگام لینک (264 بایت) بعد از استاتیک‌شدن بافرهای Init، و قاب ~2064 بایتی func__Diag_SaveNow روی استک 1024 بایتی تسک کنترل (سرریز استک هنگام ذخیره)</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>رزرو هیپ لینکر صفر شد (تخصیص فقط استاتیک است) و Init/SaveNow با بافر کمکی Stage بازنویسی شدند: فقط seqها اسکالر می‌مانند؛ کامیت‌های fix(linker) و fix(Diag) روی شاخه arena/859ce091-changeover</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>ممیزی خط‌به‌خط: ذخیره فلش Diag (حین شارژ حدود هر ۶۰ ثانیه) برخلاف ذخیره‌های NVM و CalLut شارژر را معلق نمی‌کرد؛ پاک‌کردن صفحه کل CPU را ۲۰ تا ۴۰ میلی‌ثانیه نگه می‌دارد و گیت‌ها داخل پنجره کور سوییچ می‌کردند</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>در func__Diag_SaveNow دور WriteFlash، ‏func__Charger_SetSuspended(true)‎ + ‏func__BspPwm_StopAll()‎ و بعد ‏SetSuspended(false)‎ اضافه شد (زمینه تسک کنترل، توقف بی‌درنگ، آینه duty دست‌نخورده)؛ هر دو گیت سبز</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="22" t="inlineStr">
         <is>
           <t>ممیزی خط‌به‌خط (مورد ۶): func__Diag_RecordFault شمارنده‌ها را با شماره خام بیت (‏1u &lt;&lt; 6‎، ‏1u &lt;&lt; 7‎ و بیت ۰) رمزگشایی می‌کرد؛ جابه‌جایی بیت‌های FAULT در app_types.h بی‌صدا آمار را غلط می‌کرد و کامنت «reuse for ADC» روی شمارنده ovCount گمراه‌کننده بود</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="22" t="inlineStr">
         <is>
           <t>هر سه شرط با ثابت‌های نام‌دار FAULT_CHARGER_BAT_LOST / FAULT_CHARGER_TECHNICAL / FAULT_ADC نوشته شد (نام فیلد ovCount به‌خاطر چیدمان رکورد فلش ماند)؛ نگهبان tools/check_diag_fault_bits.py اضافه شد تا برگشت شماره خام برای همیشه FAIL شود؛ یکسانی رفتار با مقایسه اسمبلی ثابت شد</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1020,6 +1494,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00548235"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -1027,19 +1502,19 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>تأیید</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>امضا</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>11 مورد دیاگ روی برد تست شد و پنل سه‌صفحه‌ای نمایش می‌دهد</t>
         </is>
@@ -1053,61 +1528,117 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00808080"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>فایل</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>توضیح</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="22" t="inlineStr">
         <is>
           <t>diag.h</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>ساختار diag_record_t و API</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="22" t="inlineStr">
         <is>
           <t>diag.c</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>پیاده‌سازی فلش و لاگ</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="22" t="inlineStr">
         <is>
           <t>README.md</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>شرح ماژول، رکورد و مسیر تست</t>
         </is>
       </c>
     </row>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>وضعیت</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>انجام شد</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>قبول</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>رد</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>مسدود</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>نیاز به تکرار</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1115,7 +1646,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002F5597"/>
+    <tabColor rgb="007030A0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -1127,55 +1658,56 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="17" t="inlineStr">
         <is>
           <t>ماشین حالت ماژول لاگ تشخیصی (Diag)</t>
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>حالت‌ها و گذارهای همین ماژول</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="19" t="inlineStr">
         <is>
           <t>Diag_State_Machine.xlsx</t>
         </is>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t>ماشین حالت کل برنامه (نمای سیستمی)</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>../../../Documentation/System_State_Machine.xlsx</t>
         </is>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="18" t="inlineStr">
         <is>
           <t>راهنمای رنگ‌ها</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>سبز = عادی/سالم · زرد = هشدار یا انتظار · قرمز = خطا یا قفل · نارنجی = در حال کار · خاکستری = بی‌کار · آبی = اطلاعاتی</t>
         </is>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="18" t="inlineStr">
         <is>
           <t>بازتولید</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>python3 tools/make_module_state_machines.py</t>
         </is>
@@ -1188,6 +1720,7 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Firmware/Modules/Diag/Diag_Validation.xlsx
+++ b/Firmware/Modules/Diag/Diag_Validation.xlsx
@@ -9,15 +9,18 @@
   <sheets>
     <sheet name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="برنامه تست" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="مراجع سناریو" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="ثبت ایراد" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="تأیید نهایی" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="فهرست‌ها" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="ماشین حالت" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="تست‌های برنامه‌نویسی" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="مراجع سناریو" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ثبت ایراد" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="تأیید نهایی" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="فهرست‌ها" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="ماشین حالت" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$1:$G$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$1:$G$52</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'برنامه تست'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'تست‌های برنامه‌نویسی'!$A$2:$G$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'تست‌های برنامه‌نویسی'!$2:$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" iterate="1" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
@@ -28,7 +31,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -95,6 +98,12 @@
       <sz val="11"/>
       <u val="single"/>
     </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="13"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -159,7 +168,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -221,6 +230,8 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -639,7 +650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -992,49 +1003,15 @@
     <row r="12" ht="40.5" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>SaveNow بدون سرریز استک و Init بدون بافر استاتیک اضافه</t>
-        </is>
-      </c>
-      <c r="C12" s="21" t="inlineStr">
-        <is>
-          <t>گام ۱ (هاست): ابزار tools/measure_ram.py را اجرا کن و عمق استک تسک کنترل (ctrl) و حافظهٔ آزاد را بخوان.
-گام ۲ (هاست): قاب func__Diag_SaveNow باید روی استک تسک کنترل جا شده باشد و هیچ بافر استاتیک اضافه‌ای در Init نباشد.
-گام ۳ (برد): برد را ریبوت کن و رکورد ذخیره‌شده را بخوان: باید در صفحهٔ قدیمی‌تر با seq+1 نوشته شده و بعد از ریست سالم خوانده شود.</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>قاب SaveNow روی استک تسک کنترل جا شود، رکورد در صفحه قدیمی‌تر با seq+1 نوشته شود و بعد از ریست خوانده شود</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>هاست 2026-10-15: ctrl از 2264/1024 (221%) به 384/1024 (37.5%) رسید و FREE RAM به 1544 بایت؛ تست برد در انتظار</t>
-        </is>
-      </c>
-      <c r="F12" s="10" t="n"/>
-      <c r="G12" s="11">
-        <f>IF(OR(F12="",F12="در انتظار"),"",IF(G12="",TODAY(),G12))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="54" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>ذخیره فلش حین شارژ فعال: تعلیق شارژر دور نوشتن</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>گام ۱: شارژ واقعی را فعال کن (کانال در BULK باشد) و اسیلوسکوپ را روی گیت هر دو کانال بگذار.
 گام ۲: صبر کن ذخیرهٔ دوره‌ای Diag خودش برسد (حدود هر 60 ثانیه).
@@ -1042,314 +1019,544 @@
 گام ۴: بلافاصله بعد از ذخیره، شارژ باید بدون پرش ادامه پیدا کند و رکورد هم سالم ذخیره شده باشد. نتیجهٔ برد هنوز در انتظار است.</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D12" s="12" t="inlineStr">
         <is>
           <t>حین پاک/نوشتن فلش هر دو گیت PWM متوقف، بعد از ذخیره شارژ بدون پرش ادامه یابد و رکورد سالم ذخیره شود</t>
         </is>
       </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="E12" s="12" t="inlineStr">
         <is>
           <t>هاست: هر دو گیت سبز و بودجه RAM/استک سالم (ctrl ‏384/1024‎، آزاد 1544 بایت)؛ نتیجه برد: در انتظار</t>
         </is>
       </c>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="15">
+      <c r="F12" s="14" t="n"/>
+      <c r="G12" s="15">
         <f>IF(OR(F13="",F13="در انتظار"),"",IF(G13="",TODAY(),G13))</f>
         <v/>
       </c>
     </row>
+    <row r="13" ht="54" customHeight="1">
+      <c r="G13" s="16">
+        <f>IF(OR(F15="",F15="در انتظار"),"",IF(G15="",TODAY(),G15))</f>
+        <v/>
+      </c>
+    </row>
     <row r="14" ht="54" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>شمارنده‌های خطا با نام FAULT_* رمزگشایی می‌شوند (نه شماره خام بیت)</t>
-        </is>
-      </c>
-      <c r="C14" s="21" t="inlineStr">
-        <is>
-          <t>گام ۱ (هاست): python3 tools/check_diag_fault_bits.py را اجرا کن؛ باید PASS بدهد (قبل از اصلاح روی کد قدیم FAIL می‌شد).
-گام ۲ (هاست): اسمبلی تابع func__Diag_RecordFault قبل و بعد از اصلاح را مقایسه کن؛ باید بایت‌به‌بایت یکی باشد.
-گام ۳ (برد): از پنل یک‌بار خطای قطع باتری و یک‌بار خطای فنی بساز.
-گام ۴ (برد): شمارنده‌ها را بخوان: هر رویداد باید فقط شمارندهٔ خودش را زیاد کرده باشد (قطع باتری ← FAULT_CHARGER_BAT_LOST، فنی ← FAULT_CHARGER_TECHNICAL، ADC ← شمارندهٔ ovCount). نتیجهٔ برد هنوز در انتظار است.</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>چک هاست PASS؛ اسمبلی تابع قبل/بعد بایت‌به‌بایت یکسان؛ روی برد هر رویداد فقط شمارنده خودش را زیاد کند</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>هاست 2026-10-15: چک‌نگهبان اول روی کد قدیم FAIL شد (هر سه خط خام را گرفت)، بعد از اصلاح PASS؛ اسمبلی یکسان؛ هر دو گیت سبز؛ نتیجه برد: در انتظار</t>
-        </is>
-      </c>
-      <c r="F14" s="10" t="n"/>
-      <c r="G14" s="11">
-        <f>IF(OR(F14="",F14="در انتظار"),"",IF(G14="",TODAY(),G14))</f>
+      <c r="G14" s="16">
+        <f>IF(OR(F16="",F16="در انتظار"),"",IF(G16="",TODAY(),G16))</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="G15" s="16">
-        <f>IF(OR(F15="",F15="در انتظار"),"",IF(G15="",TODAY(),G15))</f>
+        <f>IF(OR(F17="",F17="در انتظار"),"",IF(G17="",TODAY(),G17))</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="G16" s="16">
-        <f>IF(OR(F16="",F16="در انتظار"),"",IF(G16="",TODAY(),G16))</f>
+        <f>IF(OR(F18="",F18="در انتظار"),"",IF(G18="",TODAY(),G18))</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="G17" s="16">
-        <f>IF(OR(F17="",F17="در انتظار"),"",IF(G17="",TODAY(),G17))</f>
+        <f>IF(OR(F19="",F19="در انتظار"),"",IF(G19="",TODAY(),G19))</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="G18" s="16">
-        <f>IF(OR(F18="",F18="در انتظار"),"",IF(G18="",TODAY(),G18))</f>
+        <f>IF(OR(F20="",F20="در انتظار"),"",IF(G20="",TODAY(),G20))</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="G19" s="16">
-        <f>IF(OR(F19="",F19="در انتظار"),"",IF(G19="",TODAY(),G19))</f>
+        <f>IF(OR(F21="",F21="در انتظار"),"",IF(G21="",TODAY(),G21))</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="G20" s="16">
-        <f>IF(OR(F20="",F20="در انتظار"),"",IF(G20="",TODAY(),G20))</f>
+        <f>IF(OR(F22="",F22="در انتظار"),"",IF(G22="",TODAY(),G22))</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="G21" s="16">
-        <f>IF(OR(F21="",F21="در انتظار"),"",IF(G21="",TODAY(),G21))</f>
+        <f>IF(OR(F23="",F23="در انتظار"),"",IF(G23="",TODAY(),G23))</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="G22" s="16">
-        <f>IF(OR(F22="",F22="در انتظار"),"",IF(G22="",TODAY(),G22))</f>
+        <f>IF(OR(F24="",F24="در انتظار"),"",IF(G24="",TODAY(),G24))</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="G23" s="16">
-        <f>IF(OR(F23="",F23="در انتظار"),"",IF(G23="",TODAY(),G23))</f>
+        <f>IF(OR(F25="",F25="در انتظار"),"",IF(G25="",TODAY(),G25))</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="G24" s="16">
-        <f>IF(OR(F24="",F24="در انتظار"),"",IF(G24="",TODAY(),G24))</f>
+        <f>IF(OR(F26="",F26="در انتظار"),"",IF(G26="",TODAY(),G26))</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="G25" s="16">
-        <f>IF(OR(F25="",F25="در انتظار"),"",IF(G25="",TODAY(),G25))</f>
+        <f>IF(OR(F27="",F27="در انتظار"),"",IF(G27="",TODAY(),G27))</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="G26" s="16">
-        <f>IF(OR(F26="",F26="در انتظار"),"",IF(G26="",TODAY(),G26))</f>
+        <f>IF(OR(F28="",F28="در انتظار"),"",IF(G28="",TODAY(),G28))</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="G27" s="16">
-        <f>IF(OR(F27="",F27="در انتظار"),"",IF(G27="",TODAY(),G27))</f>
+        <f>IF(OR(F29="",F29="در انتظار"),"",IF(G29="",TODAY(),G29))</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="G28" s="16">
-        <f>IF(OR(F28="",F28="در انتظار"),"",IF(G28="",TODAY(),G28))</f>
+        <f>IF(OR(F30="",F30="در انتظار"),"",IF(G30="",TODAY(),G30))</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="G29" s="16">
-        <f>IF(OR(F29="",F29="در انتظار"),"",IF(G29="",TODAY(),G29))</f>
+        <f>IF(OR(F31="",F31="در انتظار"),"",IF(G31="",TODAY(),G31))</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="G30" s="16">
-        <f>IF(OR(F30="",F30="در انتظار"),"",IF(G30="",TODAY(),G30))</f>
+        <f>IF(OR(F32="",F32="در انتظار"),"",IF(G32="",TODAY(),G32))</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="G31" s="16">
-        <f>IF(OR(F31="",F31="در انتظار"),"",IF(G31="",TODAY(),G31))</f>
+        <f>IF(OR(F33="",F33="در انتظار"),"",IF(G33="",TODAY(),G33))</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="G32" s="16">
-        <f>IF(OR(F32="",F32="در انتظار"),"",IF(G32="",TODAY(),G32))</f>
+        <f>IF(OR(F34="",F34="در انتظار"),"",IF(G34="",TODAY(),G34))</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="G33" s="16">
-        <f>IF(OR(F33="",F33="در انتظار"),"",IF(G33="",TODAY(),G33))</f>
+        <f>IF(OR(F35="",F35="در انتظار"),"",IF(G35="",TODAY(),G35))</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="G34" s="16">
-        <f>IF(OR(F34="",F34="در انتظار"),"",IF(G34="",TODAY(),G34))</f>
+        <f>IF(OR(F36="",F36="در انتظار"),"",IF(G36="",TODAY(),G36))</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="G35" s="16">
-        <f>IF(OR(F35="",F35="در انتظار"),"",IF(G35="",TODAY(),G35))</f>
+        <f>IF(OR(F37="",F37="در انتظار"),"",IF(G37="",TODAY(),G37))</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="G36" s="16">
-        <f>IF(OR(F36="",F36="در انتظار"),"",IF(G36="",TODAY(),G36))</f>
+        <f>IF(OR(F38="",F38="در انتظار"),"",IF(G38="",TODAY(),G38))</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="G37" s="16">
-        <f>IF(OR(F37="",F37="در انتظار"),"",IF(G37="",TODAY(),G37))</f>
+        <f>IF(OR(F39="",F39="در انتظار"),"",IF(G39="",TODAY(),G39))</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="G38" s="16">
-        <f>IF(OR(F38="",F38="در انتظار"),"",IF(G38="",TODAY(),G38))</f>
+        <f>IF(OR(F40="",F40="در انتظار"),"",IF(G40="",TODAY(),G40))</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="G39" s="16">
-        <f>IF(OR(F39="",F39="در انتظار"),"",IF(G39="",TODAY(),G39))</f>
+        <f>IF(OR(F41="",F41="در انتظار"),"",IF(G41="",TODAY(),G41))</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="G40" s="16">
-        <f>IF(OR(F40="",F40="در انتظار"),"",IF(G40="",TODAY(),G40))</f>
+        <f>IF(OR(F42="",F42="در انتظار"),"",IF(G42="",TODAY(),G42))</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="G41" s="16">
-        <f>IF(OR(F41="",F41="در انتظار"),"",IF(G41="",TODAY(),G41))</f>
+        <f>IF(OR(F43="",F43="در انتظار"),"",IF(G43="",TODAY(),G43))</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="G42" s="16">
-        <f>IF(OR(F42="",F42="در انتظار"),"",IF(G42="",TODAY(),G42))</f>
+        <f>IF(OR(F44="",F44="در انتظار"),"",IF(G44="",TODAY(),G44))</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="G43" s="16">
-        <f>IF(OR(F43="",F43="در انتظار"),"",IF(G43="",TODAY(),G43))</f>
+        <f>IF(OR(F45="",F45="در انتظار"),"",IF(G45="",TODAY(),G45))</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="G44" s="16">
-        <f>IF(OR(F44="",F44="در انتظار"),"",IF(G44="",TODAY(),G44))</f>
+        <f>IF(OR(F46="",F46="در انتظار"),"",IF(G46="",TODAY(),G46))</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="G45" s="16">
-        <f>IF(OR(F45="",F45="در انتظار"),"",IF(G45="",TODAY(),G45))</f>
+        <f>IF(OR(F47="",F47="در انتظار"),"",IF(G47="",TODAY(),G47))</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="G46" s="16">
-        <f>IF(OR(F46="",F46="در انتظار"),"",IF(G46="",TODAY(),G46))</f>
+        <f>IF(OR(F48="",F48="در انتظار"),"",IF(G48="",TODAY(),G48))</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="G47" s="16">
-        <f>IF(OR(F47="",F47="در انتظار"),"",IF(G47="",TODAY(),G47))</f>
+        <f>IF(OR(F49="",F49="در انتظار"),"",IF(G49="",TODAY(),G49))</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="G48" s="16">
-        <f>IF(OR(F48="",F48="در انتظار"),"",IF(G48="",TODAY(),G48))</f>
+        <f>IF(OR(F50="",F50="در انتظار"),"",IF(G50="",TODAY(),G50))</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="G49" s="16">
-        <f>IF(OR(F49="",F49="در انتظار"),"",IF(G49="",TODAY(),G49))</f>
+        <f>IF(OR(F51="",F51="در انتظار"),"",IF(G51="",TODAY(),G51))</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="G50" s="16">
-        <f>IF(OR(F50="",F50="در انتظار"),"",IF(G50="",TODAY(),G50))</f>
+        <f>IF(OR(F52="",F52="در انتظار"),"",IF(G52="",TODAY(),G52))</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="G51" s="16">
-        <f>IF(OR(F51="",F51="در انتظار"),"",IF(G51="",TODAY(),G51))</f>
+        <f>IF(OR(F53="",F53="در انتظار"),"",IF(G53="",TODAY(),G53))</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="G52" s="16">
-        <f>IF(OR(F52="",F52="در انتظار"),"",IF(G52="",TODAY(),G52))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53">
-      <c r="G53" s="16">
-        <f>IF(OR(F53="",F53="در انتظار"),"",IF(G53="",TODAY(),G53))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54">
-      <c r="G54" s="16">
         <f>IF(OR(F54="",F54="در انتظار"),"",IF(G54="",TODAY(),G54))</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G14"/>
+  <autoFilter ref="A1:G52"/>
   <dataValidations count="1">
     <dataValidation sqref="F2:F94" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" prompt="وضعیت تست را از فهرست انتخاب کنید" type="list">
       <formula1>='فهرست‌ها'!$A$7:$A$12</formula1>
     </dataValidation>
   </dataValidations>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId2"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00808080"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>تست‌های برنامه‌نویسی و هاست (جدا از ولیدیشن عملی برد)</t>
+        </is>
+      </c>
+      <c r="B1" s="24" t="inlineStr">
+        <is>
+          <t>این شیت جدا از ولیدیشن عملی برد است: چک‌های کدنویسی، تست‌های هاست، بازبینی کد و تزریق با دیباگر. این‌ها با گیت‌های check_ai_rules و check_firmware_syntax و تست‌های هاست پوشش داده می‌شوند؛ برای بررسی عملکرد روی برد واقعی لازم نیستند.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>ردیف</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>شرح تست</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>روش</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>نتیجه مورد انتظار</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>نتیجه واقعی</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>وضعیت</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>تاریخ</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="40.5" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>SaveNow بدون سرریز استک و Init بدون بافر استاتیک اضافه</t>
+        </is>
+      </c>
+      <c r="C3" s="21" t="inlineStr">
+        <is>
+          <t>گام ۱ (هاست): ابزار tools/measure_ram.py را اجرا کن و عمق استک تسک کنترل (ctrl) و حافظهٔ آزاد را بخوان.
+گام ۲ (هاست): قاب func__Diag_SaveNow باید روی استک تسک کنترل جا شده باشد و هیچ بافر استاتیک اضافه‌ای در Init نباشد.
+گام ۳ (برد): برد را ریبوت کن و رکورد ذخیره‌شده را بخوان: باید در صفحهٔ قدیمی‌تر با seq+1 نوشته شده و بعد از ریست سالم خوانده شود.</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>قاب SaveNow روی استک تسک کنترل جا شود، رکورد در صفحه قدیمی‌تر با seq+1 نوشته شود و بعد از ریست خوانده شود</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>هاست 2026-10-15: ctrl از 2264/1024 (221%) به 384/1024 (37.5%) رسید و FREE RAM به 1544 بایت؛ تست برد در انتظار</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="n"/>
+      <c r="G3" s="11">
+        <f>IF(OR(F3="",F3="در انتظار"),"",IF(G3="",TODAY(),G3))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="54" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>شمارنده‌های خطا با نام FAULT_* رمزگشایی می‌شوند (نه شماره خام بیت)</t>
+        </is>
+      </c>
+      <c r="C4" s="21" t="inlineStr">
+        <is>
+          <t>گام ۱ (هاست): python3 tools/check_diag_fault_bits.py را اجرا کن؛ باید PASS بدهد (قبل از اصلاح روی کد قدیم FAIL می‌شد).
+گام ۲ (هاست): اسمبلی تابع func__Diag_RecordFault قبل و بعد از اصلاح را مقایسه کن؛ باید بایت‌به‌بایت یکی باشد.
+گام ۳ (برد): از پنل یک‌بار خطای قطع باتری و یک‌بار خطای فنی بساز.
+گام ۴ (برد): شمارنده‌ها را بخوان: هر رویداد باید فقط شمارندهٔ خودش را زیاد کرده باشد (قطع باتری ← FAULT_CHARGER_BAT_LOST، فنی ← FAULT_CHARGER_TECHNICAL، ADC ← شمارندهٔ ovCount). نتیجهٔ برد هنوز در انتظار است.</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>چک هاست PASS؛ اسمبلی تابع قبل/بعد بایت‌به‌بایت یکسان؛ روی برد هر رویداد فقط شمارنده خودش را زیاد کند</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>هاست 2026-10-15: چک‌نگهبان اول روی کد قدیم FAIL شد (هر سه خط خام را گرفت)، بعد از اصلاح PASS؛ اسمبلی یکسان؛ هر دو گیت سبز؛ نتیجه برد: در انتظار</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="11">
+        <f>IF(OR(F4="",F4="در انتظار"),"",IF(G4="",TODAY(),G4))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="G5" s="16">
+        <f>IF(OR(F5="",F5="در انتظار"),"",IF(G5="",TODAY(),G5))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="G6" s="16">
+        <f>IF(OR(F6="",F6="در انتظار"),"",IF(G6="",TODAY(),G6))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="G7" s="16">
+        <f>IF(OR(F7="",F7="در انتظار"),"",IF(G7="",TODAY(),G7))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="G8" s="16">
+        <f>IF(OR(F8="",F8="در انتظار"),"",IF(G8="",TODAY(),G8))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="G9" s="16">
+        <f>IF(OR(F9="",F9="در انتظار"),"",IF(G9="",TODAY(),G9))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="G10" s="16">
+        <f>IF(OR(F10="",F10="در انتظار"),"",IF(G10="",TODAY(),G10))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="G11" s="16">
+        <f>IF(OR(F11="",F11="در انتظار"),"",IF(G11="",TODAY(),G11))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="G12" s="16">
+        <f>IF(OR(F12="",F12="در انتظار"),"",IF(G12="",TODAY(),G12))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="G13" s="16">
+        <f>IF(OR(F13="",F13="در انتظار"),"",IF(G13="",TODAY(),G13))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="G14" s="16">
+        <f>IF(OR(F14="",F14="در انتظار"),"",IF(G14="",TODAY(),G14))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="G15" s="16">
+        <f>IF(OR(F15="",F15="در انتظار"),"",IF(G15="",TODAY(),G15))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="G16" s="16">
+        <f>IF(OR(F16="",F16="در انتظار"),"",IF(G16="",TODAY(),G16))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="G17" s="16">
+        <f>IF(OR(F17="",F17="در انتظار"),"",IF(G17="",TODAY(),G17))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="G18" s="16">
+        <f>IF(OR(F18="",F18="در انتظار"),"",IF(G18="",TODAY(),G18))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="G19" s="16">
+        <f>IF(OR(F19="",F19="در انتظار"),"",IF(G19="",TODAY(),G19))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="G20" s="16">
+        <f>IF(OR(F20="",F20="در انتظار"),"",IF(G20="",TODAY(),G20))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="G21" s="16">
+        <f>IF(OR(F21="",F21="در انتظار"),"",IF(G21="",TODAY(),G21))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="G22" s="16">
+        <f>IF(OR(F22="",F22="در انتظار"),"",IF(G22="",TODAY(),G22))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="G23" s="16">
+        <f>IF(OR(F23="",F23="در انتظار"),"",IF(G23="",TODAY(),G23))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="G24" s="16">
+        <f>IF(OR(F24="",F24="در انتظار"),"",IF(G24="",TODAY(),G24))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:G4"/>
+  <dataValidations count="1">
+    <dataValidation sqref="F3 F4 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>='فهرست‌ها'!$A$7:$A$12</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00BF8F00"/>
@@ -1404,7 +1611,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C00000"/>
@@ -1491,7 +1698,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00548235"/>
@@ -1525,7 +1732,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00808080"/>
@@ -1643,7 +1850,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="007030A0"/>

--- a/Firmware/Modules/Diag/Diag_Validation.xlsx
+++ b/Firmware/Modules/Diag/Diag_Validation.xlsx
@@ -650,7 +650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -732,545 +732,482 @@
     <row r="3" ht="40.5" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>Init با یک رکورد سالم</t>
+          <t>AddChargeSec</t>
         </is>
       </c>
       <c r="C3" s="13" t="inlineStr">
         <is>
-          <t>گام ۱: یک رکورد سالم با CRC درست در صفحهٔ A بنویس و بقیهٔ فلش را خالی بگذار.
-گام ۲: برد را بوت کن.
-گام ۳: رکورد خوانده‌شده را با همان رکوردی که نوشتی مقایسه کن؛ باید عیناً همان باشد (CRC درست یعنی پذیرفته شده).</t>
+          <t>گام ۱: یک باتری نیمه‌خالی را به شارژ واقعی بزن و زمان بگیر.
+گام ۲: بعد از مدتی شارژ، از پنل گزارش زمان شارژ همان کانال را بخوان.
+گام ۳: عدد گزارش را با زمان واقعی خودت مقایسه کن.</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>همان رکورد خوانده شود</t>
+          <t>زمان شارژ ثبت‌شده با زمان واقعی می‌خواند و برای هر کانال جدا نگه داشته می‌شود</t>
         </is>
       </c>
       <c r="E3" s="12" t="n"/>
       <c r="F3" s="14" t="n"/>
       <c r="G3" s="15">
-        <f>IF(OR(F3="",F3="در انتظار"),"",IF(G3="",TODAY(),G3))</f>
+        <f>IF(OR(F5="",F5="در انتظار"),"",IF(G5="",TODAY(),G5))</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="40.5" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Init با دو رکورد سالم</t>
+          <t>RecordChargeComplete</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>گام ۱: در صفحهٔ A رکورد سالم با شمارهٔ ترتیب (seq) برابر 1 و در صفحهٔ B رکورد سالم با seq برابر 2 بنویس.
-گام ۲: برد را بوت کن.
-گام ۳: رکورد فعال باید رکورد صفحهٔ B باشد، چون جدیدتر است (seq بزرگ‌تر برنده است).</t>
+          <t>گام ۱: یک باتری را تا پرشدن کامل شارژ کن.
+گام ۲: در گزارش پنل ببین «شارژ کامل» ثبت شده یا نه.
+گام ۳: یک بار دیگر هم انجام بده و شمارش را چک کن.</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>B برنده (جدیدتر)</t>
+          <t>هر شارژ کامل یک بار شمرده و ثبت می‌شود</t>
         </is>
       </c>
       <c r="E4" s="8" t="n"/>
       <c r="F4" s="10" t="n"/>
       <c r="G4" s="11">
-        <f>IF(OR(F4="",F4="در انتظار"),"",IF(G4="",TODAY(),G4))</f>
+        <f>IF(OR(F6="",F6="در انتظار"),"",IF(G6="",TODAY(),G6))</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="40.5" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>AddChargeSec</t>
+          <t>RecordFault</t>
         </is>
       </c>
       <c r="C5" s="13" t="inlineStr">
         <is>
-          <t>گام ۱: برد را بوت کن و شمارنده‌های زمان شارژ را صفرِ شروع در نظر بگیر.
-گام ۲: برای کانال 0 مقدار 3600 ثانیه و برای کانال 1 هم 3600 ثانیه شارژ ثبت کن (func__Diag_AddChargeSec).
-گام ۳: شمارنده‌ها را بخوان: مجموع (total) باید 7200 شده باشد و شمارندهٔ هر کانال 3600.</t>
+          <t>گام ۱: ساعت دستگاه را از پنل درست کن.
+گام ۲: حین شارژ سیم باتری را بکش تا خطای ۶ بیاید.
+گام ۳: در سوابق پنل ببین خطا با زمان درست ثبت شده.</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>total و per-channel افزایش</t>
+          <t>خطای ۶ در سوابق با زمان درست هست</t>
         </is>
       </c>
       <c r="E5" s="12" t="n"/>
       <c r="F5" s="14" t="n"/>
       <c r="G5" s="15">
-        <f>IF(OR(F5="",F5="در انتظار"),"",IF(G5="",TODAY(),G5))</f>
+        <f>IF(OR(F7="",F7="در انتظار"),"",IF(G7="",TODAY(),G7))</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="40.5" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>RecordChargeComplete</t>
+          <t>PowerOff/On</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>گام ۱: برد را بوت کن.
-گام ۲: چند بار (مثلاً 3 بار) پایان شارژ کامل را ثبت کن (func__Diag_RecordChargeComplete).
-گام ۳: شمارندهٔ chargeCount را بخوان؛ باید دقیقاً به همان تعداد دفعات بالا رفته باشد.</t>
+          <t>گام ۱: ساعت را از پنل همگام کن.
+گام ۲: برق شهر را بکش، یک دقیقه صبر کن و برگردان.
+گام ۳: در سوابق، قطع و وصل و مدت خاموشی را چک کن.</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>chargeCount افزایش</t>
+          <t>قطع و وصل برق با زمان و مدت درست ثبت شده</t>
         </is>
       </c>
       <c r="E6" s="8" t="n"/>
       <c r="F6" s="10" t="n"/>
       <c r="G6" s="11">
-        <f>IF(OR(F6="",F6="در انتظار"),"",IF(G6="",TODAY(),G6))</f>
+        <f>IF(OR(F8="",F8="در انتظار"),"",IF(G8="",TODAY(),G8))</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="40.5" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>RecordFault</t>
+          <t>Min/Max</t>
         </is>
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>گام ۱: یک snapshot معتبر با ولتاژهای معلوم آماده کن.
-گام ۲: خطای قطع باتری (FAULT_CHARGER_BAT_LOST) را همراه همان snapshot ثبت کن (func__Diag_RecordFault).
-گام ۳: لیست 10 خطای آخر را بخوان: این رویداد باید در اول لیست باشد، با ساعت برد و همان ولتاژهای snapshot.</t>
+          <t>گام ۱: ورودی را از منبع آزمایشگاهی بده.
+گام ۲: ولتاژ را آرام از کم به زیاد و برگردان (مثلاً ۱۸ تا ۳۰ ولت).
+گام ۳: کمینه و بیشینهٔ ثبت‌شده را در گزارش با منبع مقایسه کن.</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>در لیست 10تایی با زمان</t>
+          <t>کمینه و بیشینهٔ ولتاژ ورودی درست ثبت شده</t>
         </is>
       </c>
       <c r="E7" s="12" t="n"/>
       <c r="F7" s="14" t="n"/>
       <c r="G7" s="15">
-        <f>IF(OR(F7="",F7="در انتظار"),"",IF(G7="",TODAY(),G7))</f>
+        <f>IF(OR(F9="",F9="در انتظار"),"",IF(G9="",TODAY(),G9))</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="54" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>PowerOff/On</t>
+          <t>TIME_SYNC</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>گام ۱: ساعت برد را همگام کن تا زمان‌ها معنادار باشند.
-گام ۲: برق شهر (ورودی) را قطع کن و چند ثانیه صبر کن.
-گام ۳: ورودی را دوباره وصل کن.
-گام ۴: در لاگ 20 رویداد برق، ردیف تازه را بخوان: زمان قطع (offTime)، زمان وصل (onTime) و مدت قطع (duration) باید درست و با ساعت واقعی یکی باشد.</t>
+          <t>گام ۱: از پنل ساعت دستگاه را با ساعت کامپیوتر همگام کن.
+گام ۲: یک رویداد بساز (مثلاً خطای ۶).
+گام ۳: زمان رویداد را در سوابق با ساعت واقعی مقایسه کن.</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>offTime/onTime/duration درست</t>
+          <t>زمان رویدادها با ساعت واقعی می‌خواند</t>
         </is>
       </c>
       <c r="E8" s="8" t="n"/>
       <c r="F8" s="10" t="n"/>
       <c r="G8" s="11">
-        <f>IF(OR(F8="",F8="در انتظار"),"",IF(G8="",TODAY(),G8))</f>
+        <f>IF(OR(F10="",F10="در انتظار"),"",IF(G10="",TODAY(),G10))</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="40.5" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Min/Max</t>
+          <t>DIAG_REQ</t>
         </is>
       </c>
       <c r="C9" s="13" t="inlineStr">
         <is>
-          <t>گام ۱: ولتاژ ورودی را از 0 تا 32 ولت آهسته بالا و پایین ببر (منبع متغیر).
-گام ۲: در چند نقطهٔ معلوم (مثلاً 12، 24 و 30 ولت) توقف کن تا نمونه‌برداری انجام شود.
-گام ۳: کمینه و بیشینهٔ ثبت‌شدهٔ Vin را بخوان؛ باید با کمترین و بیشترین ولتاژی که دادی یکی باشد.</t>
+          <t>گام ۱: در پنل درخواست گزارش کامل بده.
+گام ۲: صبر کن همهٔ بخش‌های گزارش بیاید و بخوانشان.</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>max/min به‌روز</t>
+          <t>گزارش کامل و خوانا می‌آید؛ بخشی گم نمی‌شود</t>
         </is>
       </c>
       <c r="E9" s="12" t="n"/>
       <c r="F9" s="14" t="n"/>
       <c r="G9" s="15">
-        <f>IF(OR(F9="",F9="در انتظار"),"",IF(G9="",TODAY(),G9))</f>
+        <f>IF(OR(F11="",F11="در انتظار"),"",IF(G11="",TODAY(),G11))</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="40.5" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>TIME_SYNC</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>گام ۱: زمان یونیکس فعلی را از کامپیوتر بگیر.
-گام ۲: فرمان 48 (TIME_SYNC) را با همان زمان یونیکس از لینک ESP بفرست.
-گام ۳: boardTimeBase را بخوان: باید برابر «زمان یونیکس منهای آپتایم برد» باشد، یعنی از این به بعد ساعت برد برابر ساعت واقعی می‌شود.</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>boardTimeBase = unix - uptime</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="n"/>
-      <c r="F10" s="10" t="n"/>
-      <c r="G10" s="11">
-        <f>IF(OR(F10="",F10="در انتظار"),"",IF(G10="",TODAY(),G10))</f>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>ذخیره فلش حین شارژ فعال: تعلیق شارژر دور نوشتن</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>گام ۱: شارژ واقعی یک باتری را شروع کن.
+گام ۲: حین شارژ یک خطای ۶ بساز و پاک کن تا دستگاه سابقه ذخیره کند.
+گام ۳: بعدش ببین شارژ عادی ادامه دارد و گزارش تازه سالم خوانده می‌شود.</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>ذخیره‌کردن سابقه وسط شارژ، شارژ را خراب نمی‌کند و گزارش سالم است</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>هاست: هر دو گیت سبز و بودجه RAM/استک سالم (ctrl ‏384/1024‎، آزاد 1544 بایت)؛ نتیجه برد: در انتظار</t>
+        </is>
+      </c>
+      <c r="F10" s="14" t="n"/>
+      <c r="G10" s="15">
+        <f>IF(OR(F13="",F13="در انتظار"),"",IF(G13="",TODAY(),G13))</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="40.5" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>DIAG_REQ</t>
-        </is>
-      </c>
-      <c r="C11" s="13" t="inlineStr">
-        <is>
-          <t>گام ۱: لینک ESP را فعال و سالم نگه دار.
-گام ۲: فرمان 49 (DIAG_REQ) را بفرست.
-گام ۳: پاسخ‌ها را جمع کن: باید کل رکورد در 5 چانک برگردد و CRC رکورد درست باشد.</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>5 چانک برگردد</t>
-        </is>
-      </c>
-      <c r="E11" s="12" t="n"/>
-      <c r="F11" s="14" t="n"/>
-      <c r="G11" s="15">
-        <f>IF(OR(F11="",F11="در انتظار"),"",IF(G11="",TODAY(),G11))</f>
+      <c r="G11" s="16">
+        <f>IF(OR(F15="",F15="در انتظار"),"",IF(G15="",TODAY(),G15))</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="40.5" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="inlineStr">
-        <is>
-          <t>ذخیره فلش حین شارژ فعال: تعلیق شارژر دور نوشتن</t>
-        </is>
-      </c>
-      <c r="C12" s="13" t="inlineStr">
-        <is>
-          <t>گام ۱: شارژ واقعی را فعال کن (کانال در BULK باشد) و اسیلوسکوپ را روی گیت هر دو کانال بگذار.
-گام ۲: صبر کن ذخیرهٔ دوره‌ای Diag خودش برسد (حدود هر 60 ثانیه).
-گام ۳: لحظهٔ پاک/نوشتن فلش روی اسکوپ: هر دو گیت PWM باید متوقف باشند.
-گام ۴: بلافاصله بعد از ذخیره، شارژ باید بدون پرش ادامه پیدا کند و رکورد هم سالم ذخیره شده باشد. نتیجهٔ برد هنوز در انتظار است.</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>حین پاک/نوشتن فلش هر دو گیت PWM متوقف، بعد از ذخیره شارژ بدون پرش ادامه یابد و رکورد سالم ذخیره شود</t>
-        </is>
-      </c>
-      <c r="E12" s="12" t="inlineStr">
-        <is>
-          <t>هاست: هر دو گیت سبز و بودجه RAM/استک سالم (ctrl ‏384/1024‎، آزاد 1544 بایت)؛ نتیجه برد: در انتظار</t>
-        </is>
-      </c>
-      <c r="F12" s="14" t="n"/>
-      <c r="G12" s="15">
-        <f>IF(OR(F13="",F13="در انتظار"),"",IF(G13="",TODAY(),G13))</f>
+      <c r="G12" s="16">
+        <f>IF(OR(F16="",F16="در انتظار"),"",IF(G16="",TODAY(),G16))</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="54" customHeight="1">
       <c r="G13" s="16">
-        <f>IF(OR(F15="",F15="در انتظار"),"",IF(G15="",TODAY(),G15))</f>
+        <f>IF(OR(F17="",F17="در انتظار"),"",IF(G17="",TODAY(),G17))</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="54" customHeight="1">
       <c r="G14" s="16">
-        <f>IF(OR(F16="",F16="در انتظار"),"",IF(G16="",TODAY(),G16))</f>
+        <f>IF(OR(F18="",F18="در انتظار"),"",IF(G18="",TODAY(),G18))</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="G15" s="16">
-        <f>IF(OR(F17="",F17="در انتظار"),"",IF(G17="",TODAY(),G17))</f>
+        <f>IF(OR(F19="",F19="در انتظار"),"",IF(G19="",TODAY(),G19))</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="G16" s="16">
-        <f>IF(OR(F18="",F18="در انتظار"),"",IF(G18="",TODAY(),G18))</f>
+        <f>IF(OR(F20="",F20="در انتظار"),"",IF(G20="",TODAY(),G20))</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="G17" s="16">
-        <f>IF(OR(F19="",F19="در انتظار"),"",IF(G19="",TODAY(),G19))</f>
+        <f>IF(OR(F21="",F21="در انتظار"),"",IF(G21="",TODAY(),G21))</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="G18" s="16">
-        <f>IF(OR(F20="",F20="در انتظار"),"",IF(G20="",TODAY(),G20))</f>
+        <f>IF(OR(F22="",F22="در انتظار"),"",IF(G22="",TODAY(),G22))</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="G19" s="16">
-        <f>IF(OR(F21="",F21="در انتظار"),"",IF(G21="",TODAY(),G21))</f>
+        <f>IF(OR(F23="",F23="در انتظار"),"",IF(G23="",TODAY(),G23))</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="G20" s="16">
-        <f>IF(OR(F22="",F22="در انتظار"),"",IF(G22="",TODAY(),G22))</f>
+        <f>IF(OR(F24="",F24="در انتظار"),"",IF(G24="",TODAY(),G24))</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="G21" s="16">
-        <f>IF(OR(F23="",F23="در انتظار"),"",IF(G23="",TODAY(),G23))</f>
+        <f>IF(OR(F25="",F25="در انتظار"),"",IF(G25="",TODAY(),G25))</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="G22" s="16">
-        <f>IF(OR(F24="",F24="در انتظار"),"",IF(G24="",TODAY(),G24))</f>
+        <f>IF(OR(F26="",F26="در انتظار"),"",IF(G26="",TODAY(),G26))</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="G23" s="16">
-        <f>IF(OR(F25="",F25="در انتظار"),"",IF(G25="",TODAY(),G25))</f>
+        <f>IF(OR(F27="",F27="در انتظار"),"",IF(G27="",TODAY(),G27))</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="G24" s="16">
-        <f>IF(OR(F26="",F26="در انتظار"),"",IF(G26="",TODAY(),G26))</f>
+        <f>IF(OR(F28="",F28="در انتظار"),"",IF(G28="",TODAY(),G28))</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="G25" s="16">
-        <f>IF(OR(F27="",F27="در انتظار"),"",IF(G27="",TODAY(),G27))</f>
+        <f>IF(OR(F29="",F29="در انتظار"),"",IF(G29="",TODAY(),G29))</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="G26" s="16">
-        <f>IF(OR(F28="",F28="در انتظار"),"",IF(G28="",TODAY(),G28))</f>
+        <f>IF(OR(F30="",F30="در انتظار"),"",IF(G30="",TODAY(),G30))</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="G27" s="16">
-        <f>IF(OR(F29="",F29="در انتظار"),"",IF(G29="",TODAY(),G29))</f>
+        <f>IF(OR(F31="",F31="در انتظار"),"",IF(G31="",TODAY(),G31))</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="G28" s="16">
-        <f>IF(OR(F30="",F30="در انتظار"),"",IF(G30="",TODAY(),G30))</f>
+        <f>IF(OR(F32="",F32="در انتظار"),"",IF(G32="",TODAY(),G32))</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="G29" s="16">
-        <f>IF(OR(F31="",F31="در انتظار"),"",IF(G31="",TODAY(),G31))</f>
+        <f>IF(OR(F33="",F33="در انتظار"),"",IF(G33="",TODAY(),G33))</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="G30" s="16">
-        <f>IF(OR(F32="",F32="در انتظار"),"",IF(G32="",TODAY(),G32))</f>
+        <f>IF(OR(F34="",F34="در انتظار"),"",IF(G34="",TODAY(),G34))</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="G31" s="16">
-        <f>IF(OR(F33="",F33="در انتظار"),"",IF(G33="",TODAY(),G33))</f>
+        <f>IF(OR(F35="",F35="در انتظار"),"",IF(G35="",TODAY(),G35))</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="G32" s="16">
-        <f>IF(OR(F34="",F34="در انتظار"),"",IF(G34="",TODAY(),G34))</f>
+        <f>IF(OR(F36="",F36="در انتظار"),"",IF(G36="",TODAY(),G36))</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="G33" s="16">
-        <f>IF(OR(F35="",F35="در انتظار"),"",IF(G35="",TODAY(),G35))</f>
+        <f>IF(OR(F37="",F37="در انتظار"),"",IF(G37="",TODAY(),G37))</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="G34" s="16">
-        <f>IF(OR(F36="",F36="در انتظار"),"",IF(G36="",TODAY(),G36))</f>
+        <f>IF(OR(F38="",F38="در انتظار"),"",IF(G38="",TODAY(),G38))</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="G35" s="16">
-        <f>IF(OR(F37="",F37="در انتظار"),"",IF(G37="",TODAY(),G37))</f>
+        <f>IF(OR(F39="",F39="در انتظار"),"",IF(G39="",TODAY(),G39))</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="G36" s="16">
-        <f>IF(OR(F38="",F38="در انتظار"),"",IF(G38="",TODAY(),G38))</f>
+        <f>IF(OR(F40="",F40="در انتظار"),"",IF(G40="",TODAY(),G40))</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="G37" s="16">
-        <f>IF(OR(F39="",F39="در انتظار"),"",IF(G39="",TODAY(),G39))</f>
+        <f>IF(OR(F41="",F41="در انتظار"),"",IF(G41="",TODAY(),G41))</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="G38" s="16">
-        <f>IF(OR(F40="",F40="در انتظار"),"",IF(G40="",TODAY(),G40))</f>
+        <f>IF(OR(F42="",F42="در انتظار"),"",IF(G42="",TODAY(),G42))</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="G39" s="16">
-        <f>IF(OR(F41="",F41="در انتظار"),"",IF(G41="",TODAY(),G41))</f>
+        <f>IF(OR(F43="",F43="در انتظار"),"",IF(G43="",TODAY(),G43))</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="G40" s="16">
-        <f>IF(OR(F42="",F42="در انتظار"),"",IF(G42="",TODAY(),G42))</f>
+        <f>IF(OR(F44="",F44="در انتظار"),"",IF(G44="",TODAY(),G44))</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="G41" s="16">
-        <f>IF(OR(F43="",F43="در انتظار"),"",IF(G43="",TODAY(),G43))</f>
+        <f>IF(OR(F45="",F45="در انتظار"),"",IF(G45="",TODAY(),G45))</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="G42" s="16">
-        <f>IF(OR(F44="",F44="در انتظار"),"",IF(G44="",TODAY(),G44))</f>
+        <f>IF(OR(F46="",F46="در انتظار"),"",IF(G46="",TODAY(),G46))</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="G43" s="16">
-        <f>IF(OR(F45="",F45="در انتظار"),"",IF(G45="",TODAY(),G45))</f>
+        <f>IF(OR(F47="",F47="در انتظار"),"",IF(G47="",TODAY(),G47))</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="G44" s="16">
-        <f>IF(OR(F46="",F46="در انتظار"),"",IF(G46="",TODAY(),G46))</f>
+        <f>IF(OR(F48="",F48="در انتظار"),"",IF(G48="",TODAY(),G48))</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="G45" s="16">
-        <f>IF(OR(F47="",F47="در انتظار"),"",IF(G47="",TODAY(),G47))</f>
+        <f>IF(OR(F49="",F49="در انتظار"),"",IF(G49="",TODAY(),G49))</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="G46" s="16">
-        <f>IF(OR(F48="",F48="در انتظار"),"",IF(G48="",TODAY(),G48))</f>
+        <f>IF(OR(F50="",F50="در انتظار"),"",IF(G50="",TODAY(),G50))</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="G47" s="16">
-        <f>IF(OR(F49="",F49="در انتظار"),"",IF(G49="",TODAY(),G49))</f>
+        <f>IF(OR(F51="",F51="در انتظار"),"",IF(G51="",TODAY(),G51))</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="G48" s="16">
-        <f>IF(OR(F50="",F50="در انتظار"),"",IF(G50="",TODAY(),G50))</f>
+        <f>IF(OR(F52="",F52="در انتظار"),"",IF(G52="",TODAY(),G52))</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="G49" s="16">
-        <f>IF(OR(F51="",F51="در انتظار"),"",IF(G51="",TODAY(),G51))</f>
+        <f>IF(OR(F53="",F53="در انتظار"),"",IF(G53="",TODAY(),G53))</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="G50" s="16">
-        <f>IF(OR(F52="",F52="در انتظار"),"",IF(G52="",TODAY(),G52))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="G51" s="16">
-        <f>IF(OR(F53="",F53="در انتظار"),"",IF(G53="",TODAY(),G53))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="G52" s="16">
         <f>IF(OR(F54="",F54="در انتظار"),"",IF(G54="",TODAY(),G54))</f>
         <v/>
       </c>
@@ -1425,14 +1362,62 @@
       </c>
     </row>
     <row r="5">
-      <c r="G5" s="16">
-        <f>IF(OR(F5="",F5="در انتظار"),"",IF(G5="",TODAY(),G5))</f>
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Init با دو رکورد سالم</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>گام ۱: در صفحهٔ A رکورد سالم با شمارهٔ ترتیب (seq) برابر 1 و در صفحهٔ B رکورد سالم با seq برابر 2 بنویس.
+گام ۲: برد را بوت کن.
+گام ۳: رکورد فعال باید رکورد صفحهٔ B باشد، چون جدیدتر است (seq بزرگ‌تر برنده است).</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>B برنده (جدیدتر)</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="n"/>
+      <c r="F5" s="10" t="n"/>
+      <c r="G5" s="11">
+        <f>IF(OR(F4="",F4="در انتظار"),"",IF(G4="",TODAY(),G4))</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="G6" s="16">
-        <f>IF(OR(F6="",F6="در انتظار"),"",IF(G6="",TODAY(),G6))</f>
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Init با یک رکورد سالم</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>گام ۱: یک رکورد سالم با CRC درست در صفحهٔ A بنویس و بقیهٔ فلش را خالی بگذار.
+گام ۲: برد را بوت کن.
+گام ۳: رکورد خوانده‌شده را با همان رکوردی که نوشتی مقایسه کن؛ باید عیناً همان باشد (CRC درست یعنی پذیرفته شده).</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>همان رکورد خوانده شود</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="n"/>
+      <c r="F6" s="14" t="n"/>
+      <c r="G6" s="15">
+        <f>IF(OR(F3="",F3="در انتظار"),"",IF(G3="",TODAY(),G3))</f>
         <v/>
       </c>
     </row>

--- a/Firmware/Modules/Diag/Diag_Validation.xlsx
+++ b/Firmware/Modules/Diag/Diag_Validation.xlsx
@@ -31,7 +31,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -104,6 +104,36 @@
       <color rgb="001F3864"/>
       <sz val="13"/>
     </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <color rgb="000563C1"/>
+      <sz val="11"/>
+      <u val="single"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -168,7 +198,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -232,6 +262,45 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -602,37 +671,41 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="25" t="inlineStr">
         <is>
           <t>برگه تست و اعتبارسنجی عملی ماژول Diag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="25" t="inlineStr">
         <is>
           <t>Diag | لاگ تشخیصی 11 مورد تأییدشده: زمان کل شارژ هر کانال+مجموع، تعداد شارژ کامل، آپتایم کل+از آخرین ریست، تعداد ریست، ماکس/مین ولتاژها، جریان ماکس، 10 خطای آخر با ساعت، لاگ 20 قطع/وصل، شمارنده‌ها، زمان همگام‌سازی، نسخه/UID</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="26" t="inlineStr">
         <is>
           <t>هدف فایل</t>
         </is>
       </c>
     </row>
-    <row r="4"/>
+    <row r="4">
+      <c r="A4" s="27" t="n"/>
+    </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>11 مورد ذخیره روی برد تأیید شد: 1) زمان کل شارژ هر کانال+مجموع، 2) تعداد شارژ کامل، 3) آپتایم کل+از آخرین ریست، 4) تعداد ریست، 5) ماکس/مین ولتاژها (Vin/Vpack/Vlow/Vhigh/Imb)، 6) جریان ماکس هر کانال، 7) 10 خطای آخر با ساعت، 8) لاگ 20 قطع/وصل برق شهر، 9) شمارنده‌ها (عدم تعادل/باتری کم/قطع FAULT_CHARGER_BAT_LOST/فنی FAULT_CHARGER_TECHNICAL/FAULT_ADC)، 10) زمان همگام‌سازی ساعت، 11) نسخه/UID</t>
         </is>
       </c>
     </row>
-    <row r="6"/>
+    <row r="6">
+      <c r="A6" s="27" t="n"/>
+    </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="25" t="inlineStr">
         <is>
           <t>تست‌ها: 1) فلش ping-pong 0x0800F800/0xFC00 با CRC32، 2) Init انتخاب رکورد سالم با seq جدیدتر، 3) AddChargeSec هر کانال، 4) RecordChargeComplete، 5) RecordFault با snapshot کامل، 6) RecordPowerOff/On با محاسبه duration، 7) UpdateMinMax، 8) Tick هر ثانیه + debounce save 60s، 9) TIME_SYNC از ESP، 10) DIAG_REQ و ارسال 5 چانک</t>
         </is>
@@ -663,551 +736,791 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>ردیف</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="26" t="inlineStr">
         <is>
           <t>شرح تست</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="26" t="inlineStr">
         <is>
           <t>روش</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="26" t="inlineStr">
         <is>
           <t>نتیجه مورد انتظار</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="26" t="inlineStr">
         <is>
           <t>نتیجه واقعی</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="F1" s="26" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="G1" s="6" t="inlineStr">
+      <c r="G1" s="26" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
     </row>
     <row r="2" ht="40.5" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="28" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="29" t="inlineStr">
         <is>
           <t>Init بدون رکورد</t>
         </is>
       </c>
-      <c r="C2" s="9" t="inlineStr">
+      <c r="C2" s="30" t="inlineStr">
         <is>
           <t>گام ۱: فلش هر دو صفحهٔ Diag (نشانی 1032192 و 1033216) را کامل پاک کن.
 گام ۲: برد را بوت کن و رکورد خوانده‌شده را از پنل بخوان.
 گام ۳: باید رکورد پیش‌فرض ساخته شده باشد: کمینه‌ها 4294967295 (بزرگ‌ترین عدد 32 بیتی) و همهٔ شمارنده‌ها صفر.</t>
         </is>
       </c>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="D2" s="29" t="inlineStr">
         <is>
           <t>پیش‌فرض با min=0xFFFFFFFF و شمارنده صفر</t>
         </is>
       </c>
-      <c r="E2" s="8" t="n"/>
-      <c r="F2" s="10" t="n"/>
-      <c r="G2" s="11">
+      <c r="E2" s="29" t="n"/>
+      <c r="F2" s="31" t="n"/>
+      <c r="G2" s="32">
         <f>IF(OR(F2="",F2="در انتظار"),"",IF(G2="",TODAY(),G2))</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="40.5" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="28" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="33" t="inlineStr">
         <is>
           <t>AddChargeSec</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="C3" s="34" t="inlineStr">
         <is>
           <t>گام ۱: یک باتری نیمه‌خالی را به شارژ واقعی بزن و زمان بگیر.
 گام ۲: بعد از مدتی شارژ، از پنل گزارش زمان شارژ همان کانال را بخوان.
 گام ۳: عدد گزارش را با زمان واقعی خودت مقایسه کن.</t>
         </is>
       </c>
-      <c r="D3" s="12" t="inlineStr">
+      <c r="D3" s="33" t="inlineStr">
         <is>
           <t>زمان شارژ ثبت‌شده با زمان واقعی می‌خواند و برای هر کانال جدا نگه داشته می‌شود</t>
         </is>
       </c>
-      <c r="E3" s="12" t="n"/>
-      <c r="F3" s="14" t="n"/>
-      <c r="G3" s="15">
+      <c r="E3" s="33" t="n"/>
+      <c r="F3" s="35" t="n"/>
+      <c r="G3" s="36">
         <f>IF(OR(F5="",F5="در انتظار"),"",IF(G5="",TODAY(),G5))</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="40.5" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>RecordChargeComplete</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="30" t="inlineStr">
         <is>
           <t>گام ۱: یک باتری را تا پرشدن کامل شارژ کن.
 گام ۲: در گزارش پنل ببین «شارژ کامل» ثبت شده یا نه.
 گام ۳: یک بار دیگر هم انجام بده و شمارش را چک کن.</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D4" s="29" t="inlineStr">
         <is>
           <t>هر شارژ کامل یک بار شمرده و ثبت می‌شود</t>
         </is>
       </c>
-      <c r="E4" s="8" t="n"/>
-      <c r="F4" s="10" t="n"/>
-      <c r="G4" s="11">
+      <c r="E4" s="29" t="n"/>
+      <c r="F4" s="31" t="n"/>
+      <c r="G4" s="32">
         <f>IF(OR(F6="",F6="در انتظار"),"",IF(G6="",TODAY(),G6))</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="40.5" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="33" t="inlineStr">
         <is>
           <t>RecordFault</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="34" t="inlineStr">
         <is>
           <t>گام ۱: ساعت دستگاه را از پنل درست کن.
 گام ۲: حین شارژ سیم باتری را بکش تا خطای ۶ بیاید.
 گام ۳: در سوابق پنل ببین خطا با زمان درست ثبت شده.</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="D5" s="33" t="inlineStr">
         <is>
           <t>خطای ۶ در سوابق با زمان درست هست</t>
         </is>
       </c>
-      <c r="E5" s="12" t="n"/>
-      <c r="F5" s="14" t="n"/>
-      <c r="G5" s="15">
+      <c r="E5" s="33" t="n"/>
+      <c r="F5" s="35" t="n"/>
+      <c r="G5" s="36">
         <f>IF(OR(F7="",F7="در انتظار"),"",IF(G7="",TODAY(),G7))</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="40.5" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="28" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>PowerOff/On</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="30" t="inlineStr">
         <is>
           <t>گام ۱: ساعت را از پنل همگام کن.
 گام ۲: برق شهر را بکش، یک دقیقه صبر کن و برگردان.
 گام ۳: در سوابق، قطع و وصل و مدت خاموشی را چک کن.</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" s="29" t="inlineStr">
         <is>
           <t>قطع و وصل برق با زمان و مدت درست ثبت شده</t>
         </is>
       </c>
-      <c r="E6" s="8" t="n"/>
-      <c r="F6" s="10" t="n"/>
-      <c r="G6" s="11">
+      <c r="E6" s="29" t="n"/>
+      <c r="F6" s="31" t="n"/>
+      <c r="G6" s="32">
         <f>IF(OR(F8="",F8="در انتظار"),"",IF(G8="",TODAY(),G8))</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="40.5" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="28" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>Min/Max</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="34" t="inlineStr">
         <is>
           <t>گام ۱: ورودی را از منبع آزمایشگاهی بده.
 گام ۲: ولتاژ را آرام از کم به زیاد و برگردان (مثلاً ۱۸ تا ۳۰ ولت).
 گام ۳: کمینه و بیشینهٔ ثبت‌شده را در گزارش با منبع مقایسه کن.</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="33" t="inlineStr">
         <is>
           <t>کمینه و بیشینهٔ ولتاژ ورودی درست ثبت شده</t>
         </is>
       </c>
-      <c r="E7" s="12" t="n"/>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="15">
+      <c r="E7" s="33" t="n"/>
+      <c r="F7" s="35" t="n"/>
+      <c r="G7" s="36">
         <f>IF(OR(F9="",F9="در انتظار"),"",IF(G9="",TODAY(),G9))</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="54" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="28" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="29" t="inlineStr">
         <is>
           <t>TIME_SYNC</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="30" t="inlineStr">
         <is>
           <t>گام ۱: از پنل ساعت دستگاه را با ساعت کامپیوتر همگام کن.
 گام ۲: یک رویداد بساز (مثلاً خطای ۶).
 گام ۳: زمان رویداد را در سوابق با ساعت واقعی مقایسه کن.</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D8" s="29" t="inlineStr">
         <is>
           <t>زمان رویدادها با ساعت واقعی می‌خواند</t>
         </is>
       </c>
-      <c r="E8" s="8" t="n"/>
-      <c r="F8" s="10" t="n"/>
-      <c r="G8" s="11">
+      <c r="E8" s="29" t="n"/>
+      <c r="F8" s="31" t="n"/>
+      <c r="G8" s="32">
         <f>IF(OR(F10="",F10="در انتظار"),"",IF(G10="",TODAY(),G10))</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="40.5" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="28" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="33" t="inlineStr">
         <is>
           <t>DIAG_REQ</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="C9" s="34" t="inlineStr">
         <is>
           <t>گام ۱: در پنل درخواست گزارش کامل بده.
 گام ۲: صبر کن همهٔ بخش‌های گزارش بیاید و بخوانشان.</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="33" t="inlineStr">
         <is>
           <t>گزارش کامل و خوانا می‌آید؛ بخشی گم نمی‌شود</t>
         </is>
       </c>
-      <c r="E9" s="12" t="n"/>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="15">
+      <c r="E9" s="33" t="n"/>
+      <c r="F9" s="35" t="n"/>
+      <c r="G9" s="36">
         <f>IF(OR(F11="",F11="در انتظار"),"",IF(G11="",TODAY(),G11))</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="40.5" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="28" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="33" t="inlineStr">
         <is>
           <t>ذخیره فلش حین شارژ فعال: تعلیق شارژر دور نوشتن</t>
         </is>
       </c>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C10" s="34" t="inlineStr">
         <is>
           <t>گام ۱: شارژ واقعی یک باتری را شروع کن.
 گام ۲: حین شارژ یک خطای ۶ بساز و پاک کن تا دستگاه سابقه ذخیره کند.
 گام ۳: بعدش ببین شارژ عادی ادامه دارد و گزارش تازه سالم خوانده می‌شود.</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="33" t="inlineStr">
         <is>
           <t>ذخیره‌کردن سابقه وسط شارژ، شارژ را خراب نمی‌کند و گزارش سالم است</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="33" t="inlineStr">
         <is>
           <t>هاست: هر دو گیت سبز و بودجه RAM/استک سالم (ctrl ‏384/1024‎، آزاد 1544 بایت)؛ نتیجه برد: در انتظار</t>
         </is>
       </c>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="15">
+      <c r="F10" s="35" t="n"/>
+      <c r="G10" s="36">
         <f>IF(OR(F13="",F13="در انتظار"),"",IF(G13="",TODAY(),G13))</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="40.5" customHeight="1">
-      <c r="G11" s="16">
+      <c r="A11" s="27" t="n"/>
+      <c r="B11" s="27" t="n"/>
+      <c r="C11" s="27" t="n"/>
+      <c r="D11" s="27" t="n"/>
+      <c r="E11" s="27" t="n"/>
+      <c r="F11" s="27" t="n"/>
+      <c r="G11" s="37">
         <f>IF(OR(F15="",F15="در انتظار"),"",IF(G15="",TODAY(),G15))</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="40.5" customHeight="1">
-      <c r="G12" s="16">
+      <c r="A12" s="27" t="n"/>
+      <c r="B12" s="27" t="n"/>
+      <c r="C12" s="27" t="n"/>
+      <c r="D12" s="27" t="n"/>
+      <c r="E12" s="27" t="n"/>
+      <c r="F12" s="27" t="n"/>
+      <c r="G12" s="37">
         <f>IF(OR(F16="",F16="در انتظار"),"",IF(G16="",TODAY(),G16))</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="54" customHeight="1">
-      <c r="G13" s="16">
+      <c r="A13" s="27" t="n"/>
+      <c r="B13" s="27" t="n"/>
+      <c r="C13" s="27" t="n"/>
+      <c r="D13" s="27" t="n"/>
+      <c r="E13" s="27" t="n"/>
+      <c r="F13" s="27" t="n"/>
+      <c r="G13" s="37">
         <f>IF(OR(F17="",F17="در انتظار"),"",IF(G17="",TODAY(),G17))</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="54" customHeight="1">
-      <c r="G14" s="16">
+      <c r="A14" s="27" t="n"/>
+      <c r="B14" s="27" t="n"/>
+      <c r="C14" s="27" t="n"/>
+      <c r="D14" s="27" t="n"/>
+      <c r="E14" s="27" t="n"/>
+      <c r="F14" s="27" t="n"/>
+      <c r="G14" s="37">
         <f>IF(OR(F18="",F18="در انتظار"),"",IF(G18="",TODAY(),G18))</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="G15" s="16">
+      <c r="A15" s="27" t="n"/>
+      <c r="B15" s="27" t="n"/>
+      <c r="C15" s="27" t="n"/>
+      <c r="D15" s="27" t="n"/>
+      <c r="E15" s="27" t="n"/>
+      <c r="F15" s="27" t="n"/>
+      <c r="G15" s="37">
         <f>IF(OR(F19="",F19="در انتظار"),"",IF(G19="",TODAY(),G19))</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="G16" s="16">
+      <c r="A16" s="27" t="n"/>
+      <c r="B16" s="27" t="n"/>
+      <c r="C16" s="27" t="n"/>
+      <c r="D16" s="27" t="n"/>
+      <c r="E16" s="27" t="n"/>
+      <c r="F16" s="27" t="n"/>
+      <c r="G16" s="37">
         <f>IF(OR(F20="",F20="در انتظار"),"",IF(G20="",TODAY(),G20))</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="G17" s="16">
+      <c r="A17" s="27" t="n"/>
+      <c r="B17" s="27" t="n"/>
+      <c r="C17" s="27" t="n"/>
+      <c r="D17" s="27" t="n"/>
+      <c r="E17" s="27" t="n"/>
+      <c r="F17" s="27" t="n"/>
+      <c r="G17" s="37">
         <f>IF(OR(F21="",F21="در انتظار"),"",IF(G21="",TODAY(),G21))</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="G18" s="16">
+      <c r="A18" s="27" t="n"/>
+      <c r="B18" s="27" t="n"/>
+      <c r="C18" s="27" t="n"/>
+      <c r="D18" s="27" t="n"/>
+      <c r="E18" s="27" t="n"/>
+      <c r="F18" s="27" t="n"/>
+      <c r="G18" s="37">
         <f>IF(OR(F22="",F22="در انتظار"),"",IF(G22="",TODAY(),G22))</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="G19" s="16">
+      <c r="A19" s="27" t="n"/>
+      <c r="B19" s="27" t="n"/>
+      <c r="C19" s="27" t="n"/>
+      <c r="D19" s="27" t="n"/>
+      <c r="E19" s="27" t="n"/>
+      <c r="F19" s="27" t="n"/>
+      <c r="G19" s="37">
         <f>IF(OR(F23="",F23="در انتظار"),"",IF(G23="",TODAY(),G23))</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="G20" s="16">
+      <c r="A20" s="27" t="n"/>
+      <c r="B20" s="27" t="n"/>
+      <c r="C20" s="27" t="n"/>
+      <c r="D20" s="27" t="n"/>
+      <c r="E20" s="27" t="n"/>
+      <c r="F20" s="27" t="n"/>
+      <c r="G20" s="37">
         <f>IF(OR(F24="",F24="در انتظار"),"",IF(G24="",TODAY(),G24))</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="G21" s="16">
+      <c r="A21" s="27" t="n"/>
+      <c r="B21" s="27" t="n"/>
+      <c r="C21" s="27" t="n"/>
+      <c r="D21" s="27" t="n"/>
+      <c r="E21" s="27" t="n"/>
+      <c r="F21" s="27" t="n"/>
+      <c r="G21" s="37">
         <f>IF(OR(F25="",F25="در انتظار"),"",IF(G25="",TODAY(),G25))</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="G22" s="16">
+      <c r="A22" s="27" t="n"/>
+      <c r="B22" s="27" t="n"/>
+      <c r="C22" s="27" t="n"/>
+      <c r="D22" s="27" t="n"/>
+      <c r="E22" s="27" t="n"/>
+      <c r="F22" s="27" t="n"/>
+      <c r="G22" s="37">
         <f>IF(OR(F26="",F26="در انتظار"),"",IF(G26="",TODAY(),G26))</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="G23" s="16">
+      <c r="A23" s="27" t="n"/>
+      <c r="B23" s="27" t="n"/>
+      <c r="C23" s="27" t="n"/>
+      <c r="D23" s="27" t="n"/>
+      <c r="E23" s="27" t="n"/>
+      <c r="F23" s="27" t="n"/>
+      <c r="G23" s="37">
         <f>IF(OR(F27="",F27="در انتظار"),"",IF(G27="",TODAY(),G27))</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="G24" s="16">
+      <c r="A24" s="27" t="n"/>
+      <c r="B24" s="27" t="n"/>
+      <c r="C24" s="27" t="n"/>
+      <c r="D24" s="27" t="n"/>
+      <c r="E24" s="27" t="n"/>
+      <c r="F24" s="27" t="n"/>
+      <c r="G24" s="37">
         <f>IF(OR(F28="",F28="در انتظار"),"",IF(G28="",TODAY(),G28))</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="G25" s="16">
+      <c r="A25" s="27" t="n"/>
+      <c r="B25" s="27" t="n"/>
+      <c r="C25" s="27" t="n"/>
+      <c r="D25" s="27" t="n"/>
+      <c r="E25" s="27" t="n"/>
+      <c r="F25" s="27" t="n"/>
+      <c r="G25" s="37">
         <f>IF(OR(F29="",F29="در انتظار"),"",IF(G29="",TODAY(),G29))</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="G26" s="16">
+      <c r="A26" s="27" t="n"/>
+      <c r="B26" s="27" t="n"/>
+      <c r="C26" s="27" t="n"/>
+      <c r="D26" s="27" t="n"/>
+      <c r="E26" s="27" t="n"/>
+      <c r="F26" s="27" t="n"/>
+      <c r="G26" s="37">
         <f>IF(OR(F30="",F30="در انتظار"),"",IF(G30="",TODAY(),G30))</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="G27" s="16">
+      <c r="A27" s="27" t="n"/>
+      <c r="B27" s="27" t="n"/>
+      <c r="C27" s="27" t="n"/>
+      <c r="D27" s="27" t="n"/>
+      <c r="E27" s="27" t="n"/>
+      <c r="F27" s="27" t="n"/>
+      <c r="G27" s="37">
         <f>IF(OR(F31="",F31="در انتظار"),"",IF(G31="",TODAY(),G31))</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="G28" s="16">
+      <c r="A28" s="27" t="n"/>
+      <c r="B28" s="27" t="n"/>
+      <c r="C28" s="27" t="n"/>
+      <c r="D28" s="27" t="n"/>
+      <c r="E28" s="27" t="n"/>
+      <c r="F28" s="27" t="n"/>
+      <c r="G28" s="37">
         <f>IF(OR(F32="",F32="در انتظار"),"",IF(G32="",TODAY(),G32))</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="G29" s="16">
+      <c r="A29" s="27" t="n"/>
+      <c r="B29" s="27" t="n"/>
+      <c r="C29" s="27" t="n"/>
+      <c r="D29" s="27" t="n"/>
+      <c r="E29" s="27" t="n"/>
+      <c r="F29" s="27" t="n"/>
+      <c r="G29" s="37">
         <f>IF(OR(F33="",F33="در انتظار"),"",IF(G33="",TODAY(),G33))</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="G30" s="16">
+      <c r="A30" s="27" t="n"/>
+      <c r="B30" s="27" t="n"/>
+      <c r="C30" s="27" t="n"/>
+      <c r="D30" s="27" t="n"/>
+      <c r="E30" s="27" t="n"/>
+      <c r="F30" s="27" t="n"/>
+      <c r="G30" s="37">
         <f>IF(OR(F34="",F34="در انتظار"),"",IF(G34="",TODAY(),G34))</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="G31" s="16">
+      <c r="A31" s="27" t="n"/>
+      <c r="B31" s="27" t="n"/>
+      <c r="C31" s="27" t="n"/>
+      <c r="D31" s="27" t="n"/>
+      <c r="E31" s="27" t="n"/>
+      <c r="F31" s="27" t="n"/>
+      <c r="G31" s="37">
         <f>IF(OR(F35="",F35="در انتظار"),"",IF(G35="",TODAY(),G35))</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="G32" s="16">
+      <c r="A32" s="27" t="n"/>
+      <c r="B32" s="27" t="n"/>
+      <c r="C32" s="27" t="n"/>
+      <c r="D32" s="27" t="n"/>
+      <c r="E32" s="27" t="n"/>
+      <c r="F32" s="27" t="n"/>
+      <c r="G32" s="37">
         <f>IF(OR(F36="",F36="در انتظار"),"",IF(G36="",TODAY(),G36))</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="G33" s="16">
+      <c r="A33" s="27" t="n"/>
+      <c r="B33" s="27" t="n"/>
+      <c r="C33" s="27" t="n"/>
+      <c r="D33" s="27" t="n"/>
+      <c r="E33" s="27" t="n"/>
+      <c r="F33" s="27" t="n"/>
+      <c r="G33" s="37">
         <f>IF(OR(F37="",F37="در انتظار"),"",IF(G37="",TODAY(),G37))</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="G34" s="16">
+      <c r="A34" s="27" t="n"/>
+      <c r="B34" s="27" t="n"/>
+      <c r="C34" s="27" t="n"/>
+      <c r="D34" s="27" t="n"/>
+      <c r="E34" s="27" t="n"/>
+      <c r="F34" s="27" t="n"/>
+      <c r="G34" s="37">
         <f>IF(OR(F38="",F38="در انتظار"),"",IF(G38="",TODAY(),G38))</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="G35" s="16">
+      <c r="A35" s="27" t="n"/>
+      <c r="B35" s="27" t="n"/>
+      <c r="C35" s="27" t="n"/>
+      <c r="D35" s="27" t="n"/>
+      <c r="E35" s="27" t="n"/>
+      <c r="F35" s="27" t="n"/>
+      <c r="G35" s="37">
         <f>IF(OR(F39="",F39="در انتظار"),"",IF(G39="",TODAY(),G39))</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="G36" s="16">
+      <c r="A36" s="27" t="n"/>
+      <c r="B36" s="27" t="n"/>
+      <c r="C36" s="27" t="n"/>
+      <c r="D36" s="27" t="n"/>
+      <c r="E36" s="27" t="n"/>
+      <c r="F36" s="27" t="n"/>
+      <c r="G36" s="37">
         <f>IF(OR(F40="",F40="در انتظار"),"",IF(G40="",TODAY(),G40))</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="G37" s="16">
+      <c r="A37" s="27" t="n"/>
+      <c r="B37" s="27" t="n"/>
+      <c r="C37" s="27" t="n"/>
+      <c r="D37" s="27" t="n"/>
+      <c r="E37" s="27" t="n"/>
+      <c r="F37" s="27" t="n"/>
+      <c r="G37" s="37">
         <f>IF(OR(F41="",F41="در انتظار"),"",IF(G41="",TODAY(),G41))</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="G38" s="16">
+      <c r="A38" s="27" t="n"/>
+      <c r="B38" s="27" t="n"/>
+      <c r="C38" s="27" t="n"/>
+      <c r="D38" s="27" t="n"/>
+      <c r="E38" s="27" t="n"/>
+      <c r="F38" s="27" t="n"/>
+      <c r="G38" s="37">
         <f>IF(OR(F42="",F42="در انتظار"),"",IF(G42="",TODAY(),G42))</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="G39" s="16">
+      <c r="A39" s="27" t="n"/>
+      <c r="B39" s="27" t="n"/>
+      <c r="C39" s="27" t="n"/>
+      <c r="D39" s="27" t="n"/>
+      <c r="E39" s="27" t="n"/>
+      <c r="F39" s="27" t="n"/>
+      <c r="G39" s="37">
         <f>IF(OR(F43="",F43="در انتظار"),"",IF(G43="",TODAY(),G43))</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="G40" s="16">
+      <c r="A40" s="27" t="n"/>
+      <c r="B40" s="27" t="n"/>
+      <c r="C40" s="27" t="n"/>
+      <c r="D40" s="27" t="n"/>
+      <c r="E40" s="27" t="n"/>
+      <c r="F40" s="27" t="n"/>
+      <c r="G40" s="37">
         <f>IF(OR(F44="",F44="در انتظار"),"",IF(G44="",TODAY(),G44))</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="G41" s="16">
+      <c r="A41" s="27" t="n"/>
+      <c r="B41" s="27" t="n"/>
+      <c r="C41" s="27" t="n"/>
+      <c r="D41" s="27" t="n"/>
+      <c r="E41" s="27" t="n"/>
+      <c r="F41" s="27" t="n"/>
+      <c r="G41" s="37">
         <f>IF(OR(F45="",F45="در انتظار"),"",IF(G45="",TODAY(),G45))</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="G42" s="16">
+      <c r="A42" s="27" t="n"/>
+      <c r="B42" s="27" t="n"/>
+      <c r="C42" s="27" t="n"/>
+      <c r="D42" s="27" t="n"/>
+      <c r="E42" s="27" t="n"/>
+      <c r="F42" s="27" t="n"/>
+      <c r="G42" s="37">
         <f>IF(OR(F46="",F46="در انتظار"),"",IF(G46="",TODAY(),G46))</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="G43" s="16">
+      <c r="A43" s="27" t="n"/>
+      <c r="B43" s="27" t="n"/>
+      <c r="C43" s="27" t="n"/>
+      <c r="D43" s="27" t="n"/>
+      <c r="E43" s="27" t="n"/>
+      <c r="F43" s="27" t="n"/>
+      <c r="G43" s="37">
         <f>IF(OR(F47="",F47="در انتظار"),"",IF(G47="",TODAY(),G47))</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="G44" s="16">
+      <c r="A44" s="27" t="n"/>
+      <c r="B44" s="27" t="n"/>
+      <c r="C44" s="27" t="n"/>
+      <c r="D44" s="27" t="n"/>
+      <c r="E44" s="27" t="n"/>
+      <c r="F44" s="27" t="n"/>
+      <c r="G44" s="37">
         <f>IF(OR(F48="",F48="در انتظار"),"",IF(G48="",TODAY(),G48))</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="G45" s="16">
+      <c r="A45" s="27" t="n"/>
+      <c r="B45" s="27" t="n"/>
+      <c r="C45" s="27" t="n"/>
+      <c r="D45" s="27" t="n"/>
+      <c r="E45" s="27" t="n"/>
+      <c r="F45" s="27" t="n"/>
+      <c r="G45" s="37">
         <f>IF(OR(F49="",F49="در انتظار"),"",IF(G49="",TODAY(),G49))</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="G46" s="16">
+      <c r="A46" s="27" t="n"/>
+      <c r="B46" s="27" t="n"/>
+      <c r="C46" s="27" t="n"/>
+      <c r="D46" s="27" t="n"/>
+      <c r="E46" s="27" t="n"/>
+      <c r="F46" s="27" t="n"/>
+      <c r="G46" s="37">
         <f>IF(OR(F50="",F50="در انتظار"),"",IF(G50="",TODAY(),G50))</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="G47" s="16">
+      <c r="A47" s="27" t="n"/>
+      <c r="B47" s="27" t="n"/>
+      <c r="C47" s="27" t="n"/>
+      <c r="D47" s="27" t="n"/>
+      <c r="E47" s="27" t="n"/>
+      <c r="F47" s="27" t="n"/>
+      <c r="G47" s="37">
         <f>IF(OR(F51="",F51="در انتظار"),"",IF(G51="",TODAY(),G51))</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="G48" s="16">
+      <c r="A48" s="27" t="n"/>
+      <c r="B48" s="27" t="n"/>
+      <c r="C48" s="27" t="n"/>
+      <c r="D48" s="27" t="n"/>
+      <c r="E48" s="27" t="n"/>
+      <c r="F48" s="27" t="n"/>
+      <c r="G48" s="37">
         <f>IF(OR(F52="",F52="در انتظار"),"",IF(G52="",TODAY(),G52))</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="G49" s="16">
+      <c r="A49" s="27" t="n"/>
+      <c r="B49" s="27" t="n"/>
+      <c r="C49" s="27" t="n"/>
+      <c r="D49" s="27" t="n"/>
+      <c r="E49" s="27" t="n"/>
+      <c r="F49" s="27" t="n"/>
+      <c r="G49" s="37">
         <f>IF(OR(F53="",F53="در انتظار"),"",IF(G53="",TODAY(),G53))</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="G50" s="16">
+      <c r="A50" s="27" t="n"/>
+      <c r="B50" s="27" t="n"/>
+      <c r="C50" s="27" t="n"/>
+      <c r="D50" s="27" t="n"/>
+      <c r="E50" s="27" t="n"/>
+      <c r="F50" s="27" t="n"/>
+      <c r="G50" s="37">
         <f>IF(OR(F54="",F54="در انتظار"),"",IF(G54="",TODAY(),G54))</f>
         <v/>
       </c>
@@ -1244,100 +1557,105 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="23" t="inlineStr">
+      <c r="A1" s="38" t="inlineStr">
         <is>
           <t>تست‌های برنامه‌نویسی و هاست (جدا از ولیدیشن عملی برد)</t>
         </is>
       </c>
-      <c r="B1" s="24" t="inlineStr">
+      <c r="B1" s="39" t="inlineStr">
         <is>
           <t>این شیت جدا از ولیدیشن عملی برد است: چک‌های کدنویسی، تست‌های هاست، بازبینی کد و تزریق با دیباگر. این‌ها با گیت‌های check_ai_rules و check_firmware_syntax و تست‌های هاست پوشش داده می‌شوند؛ برای بررسی عملکرد روی برد واقعی لازم نیستند.</t>
         </is>
       </c>
+      <c r="C1" s="27" t="n"/>
+      <c r="D1" s="27" t="n"/>
+      <c r="E1" s="27" t="n"/>
+      <c r="F1" s="27" t="n"/>
+      <c r="G1" s="27" t="n"/>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="26" t="inlineStr">
         <is>
           <t>ردیف</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="26" t="inlineStr">
         <is>
           <t>شرح تست</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="26" t="inlineStr">
         <is>
           <t>روش</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="26" t="inlineStr">
         <is>
           <t>نتیجه مورد انتظار</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E2" s="26" t="inlineStr">
         <is>
           <t>نتیجه واقعی</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="26" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G2" s="26" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
     </row>
     <row r="3" ht="40.5" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="28" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
         <is>
           <t>SaveNow بدون سرریز استک و Init بدون بافر استاتیک اضافه</t>
         </is>
       </c>
-      <c r="C3" s="21" t="inlineStr">
+      <c r="C3" s="40" t="inlineStr">
         <is>
           <t>گام ۱ (هاست): ابزار tools/measure_ram.py را اجرا کن و عمق استک تسک کنترل (ctrl) و حافظهٔ آزاد را بخوان.
 گام ۲ (هاست): قاب func__Diag_SaveNow باید روی استک تسک کنترل جا شده باشد و هیچ بافر استاتیک اضافه‌ای در Init نباشد.
 گام ۳ (برد): برد را ریبوت کن و رکورد ذخیره‌شده را بخوان: باید در صفحهٔ قدیمی‌تر با seq+1 نوشته شده و بعد از ریست سالم خوانده شود.</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D3" s="29" t="inlineStr">
         <is>
           <t>قاب SaveNow روی استک تسک کنترل جا شود، رکورد در صفحه قدیمی‌تر با seq+1 نوشته شود و بعد از ریست خوانده شود</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="29" t="inlineStr">
         <is>
           <t>هاست 2026-10-15: ctrl از 2264/1024 (221%) به 384/1024 (37.5%) رسید و FREE RAM به 1544 بایت؛ تست برد در انتظار</t>
         </is>
       </c>
-      <c r="F3" s="10" t="n"/>
-      <c r="G3" s="11">
+      <c r="F3" s="31" t="n"/>
+      <c r="G3" s="32">
         <f>IF(OR(F3="",F3="در انتظار"),"",IF(G3="",TODAY(),G3))</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="54" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>شمارنده‌های خطا با نام FAULT_* رمزگشایی می‌شوند (نه شماره خام بیت)</t>
         </is>
       </c>
-      <c r="C4" s="21" t="inlineStr">
+      <c r="C4" s="40" t="inlineStr">
         <is>
           <t>گام ۱ (هاست): python3 tools/check_diag_fault_bits.py را اجرا کن؛ باید PASS بدهد (قبل از اصلاح روی کد قدیم FAIL می‌شد).
 گام ۲ (هاست): اسمبلی تابع func__Diag_RecordFault قبل و بعد از اصلاح را مقایسه کن؛ باید بایت‌به‌بایت یکی باشد.
@@ -1345,186 +1663,294 @@
 گام ۴ (برد): شمارنده‌ها را بخوان: هر رویداد باید فقط شمارندهٔ خودش را زیاد کرده باشد (قطع باتری ← FAULT_CHARGER_BAT_LOST، فنی ← FAULT_CHARGER_TECHNICAL، ADC ← شمارندهٔ ovCount). نتیجهٔ برد هنوز در انتظار است.</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D4" s="29" t="inlineStr">
         <is>
           <t>چک هاست PASS؛ اسمبلی تابع قبل/بعد بایت‌به‌بایت یکسان؛ روی برد هر رویداد فقط شمارنده خودش را زیاد کند</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E4" s="29" t="inlineStr">
         <is>
           <t>هاست 2026-10-15: چک‌نگهبان اول روی کد قدیم FAIL شد (هر سه خط خام را گرفت)، بعد از اصلاح PASS؛ اسمبلی یکسان؛ هر دو گیت سبز؛ نتیجه برد: در انتظار</t>
         </is>
       </c>
-      <c r="F4" s="10" t="n"/>
-      <c r="G4" s="11">
+      <c r="F4" s="31" t="n"/>
+      <c r="G4" s="32">
         <f>IF(OR(F4="",F4="در انتظار"),"",IF(G4="",TODAY(),G4))</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>Init با دو رکورد سالم</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="30" t="inlineStr">
         <is>
           <t>گام ۱: در صفحهٔ A رکورد سالم با شمارهٔ ترتیب (seq) برابر 1 و در صفحهٔ B رکورد سالم با seq برابر 2 بنویس.
 گام ۲: برد را بوت کن.
 گام ۳: رکورد فعال باید رکورد صفحهٔ B باشد، چون جدیدتر است (seq بزرگ‌تر برنده است).</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="29" t="inlineStr">
         <is>
           <t>B برنده (جدیدتر)</t>
         </is>
       </c>
-      <c r="E5" s="8" t="n"/>
-      <c r="F5" s="10" t="n"/>
-      <c r="G5" s="11">
+      <c r="E5" s="29" t="n"/>
+      <c r="F5" s="31" t="n"/>
+      <c r="G5" s="32">
         <f>IF(OR(F4="",F4="در انتظار"),"",IF(G4="",TODAY(),G4))</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>Init با یک رکورد سالم</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="34" t="inlineStr">
         <is>
           <t>گام ۱: یک رکورد سالم با CRC درست در صفحهٔ A بنویس و بقیهٔ فلش را خالی بگذار.
 گام ۲: برد را بوت کن.
 گام ۳: رکورد خوانده‌شده را با همان رکوردی که نوشتی مقایسه کن؛ باید عیناً همان باشد (CRC درست یعنی پذیرفته شده).</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="33" t="inlineStr">
         <is>
           <t>همان رکورد خوانده شود</t>
         </is>
       </c>
-      <c r="E6" s="12" t="n"/>
-      <c r="F6" s="14" t="n"/>
-      <c r="G6" s="15">
+      <c r="E6" s="33" t="n"/>
+      <c r="F6" s="35" t="n"/>
+      <c r="G6" s="36">
         <f>IF(OR(F3="",F3="در انتظار"),"",IF(G3="",TODAY(),G3))</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="G7" s="16">
+      <c r="A7" s="27" t="n"/>
+      <c r="B7" s="27" t="n"/>
+      <c r="C7" s="27" t="n"/>
+      <c r="D7" s="27" t="n"/>
+      <c r="E7" s="27" t="n"/>
+      <c r="F7" s="27" t="n"/>
+      <c r="G7" s="37">
         <f>IF(OR(F7="",F7="در انتظار"),"",IF(G7="",TODAY(),G7))</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="G8" s="16">
+      <c r="A8" s="27" t="n"/>
+      <c r="B8" s="27" t="n"/>
+      <c r="C8" s="27" t="n"/>
+      <c r="D8" s="27" t="n"/>
+      <c r="E8" s="27" t="n"/>
+      <c r="F8" s="27" t="n"/>
+      <c r="G8" s="37">
         <f>IF(OR(F8="",F8="در انتظار"),"",IF(G8="",TODAY(),G8))</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="G9" s="16">
+      <c r="A9" s="27" t="n"/>
+      <c r="B9" s="27" t="n"/>
+      <c r="C9" s="27" t="n"/>
+      <c r="D9" s="27" t="n"/>
+      <c r="E9" s="27" t="n"/>
+      <c r="F9" s="27" t="n"/>
+      <c r="G9" s="37">
         <f>IF(OR(F9="",F9="در انتظار"),"",IF(G9="",TODAY(),G9))</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="G10" s="16">
+      <c r="A10" s="27" t="n"/>
+      <c r="B10" s="27" t="n"/>
+      <c r="C10" s="27" t="n"/>
+      <c r="D10" s="27" t="n"/>
+      <c r="E10" s="27" t="n"/>
+      <c r="F10" s="27" t="n"/>
+      <c r="G10" s="37">
         <f>IF(OR(F10="",F10="در انتظار"),"",IF(G10="",TODAY(),G10))</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="G11" s="16">
+      <c r="A11" s="27" t="n"/>
+      <c r="B11" s="27" t="n"/>
+      <c r="C11" s="27" t="n"/>
+      <c r="D11" s="27" t="n"/>
+      <c r="E11" s="27" t="n"/>
+      <c r="F11" s="27" t="n"/>
+      <c r="G11" s="37">
         <f>IF(OR(F11="",F11="در انتظار"),"",IF(G11="",TODAY(),G11))</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="G12" s="16">
+      <c r="A12" s="27" t="n"/>
+      <c r="B12" s="27" t="n"/>
+      <c r="C12" s="27" t="n"/>
+      <c r="D12" s="27" t="n"/>
+      <c r="E12" s="27" t="n"/>
+      <c r="F12" s="27" t="n"/>
+      <c r="G12" s="37">
         <f>IF(OR(F12="",F12="در انتظار"),"",IF(G12="",TODAY(),G12))</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="G13" s="16">
+      <c r="A13" s="27" t="n"/>
+      <c r="B13" s="27" t="n"/>
+      <c r="C13" s="27" t="n"/>
+      <c r="D13" s="27" t="n"/>
+      <c r="E13" s="27" t="n"/>
+      <c r="F13" s="27" t="n"/>
+      <c r="G13" s="37">
         <f>IF(OR(F13="",F13="در انتظار"),"",IF(G13="",TODAY(),G13))</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="G14" s="16">
+      <c r="A14" s="27" t="n"/>
+      <c r="B14" s="27" t="n"/>
+      <c r="C14" s="27" t="n"/>
+      <c r="D14" s="27" t="n"/>
+      <c r="E14" s="27" t="n"/>
+      <c r="F14" s="27" t="n"/>
+      <c r="G14" s="37">
         <f>IF(OR(F14="",F14="در انتظار"),"",IF(G14="",TODAY(),G14))</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="G15" s="16">
+      <c r="A15" s="27" t="n"/>
+      <c r="B15" s="27" t="n"/>
+      <c r="C15" s="27" t="n"/>
+      <c r="D15" s="27" t="n"/>
+      <c r="E15" s="27" t="n"/>
+      <c r="F15" s="27" t="n"/>
+      <c r="G15" s="37">
         <f>IF(OR(F15="",F15="در انتظار"),"",IF(G15="",TODAY(),G15))</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="G16" s="16">
+      <c r="A16" s="27" t="n"/>
+      <c r="B16" s="27" t="n"/>
+      <c r="C16" s="27" t="n"/>
+      <c r="D16" s="27" t="n"/>
+      <c r="E16" s="27" t="n"/>
+      <c r="F16" s="27" t="n"/>
+      <c r="G16" s="37">
         <f>IF(OR(F16="",F16="در انتظار"),"",IF(G16="",TODAY(),G16))</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="G17" s="16">
+      <c r="A17" s="27" t="n"/>
+      <c r="B17" s="27" t="n"/>
+      <c r="C17" s="27" t="n"/>
+      <c r="D17" s="27" t="n"/>
+      <c r="E17" s="27" t="n"/>
+      <c r="F17" s="27" t="n"/>
+      <c r="G17" s="37">
         <f>IF(OR(F17="",F17="در انتظار"),"",IF(G17="",TODAY(),G17))</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="G18" s="16">
+      <c r="A18" s="27" t="n"/>
+      <c r="B18" s="27" t="n"/>
+      <c r="C18" s="27" t="n"/>
+      <c r="D18" s="27" t="n"/>
+      <c r="E18" s="27" t="n"/>
+      <c r="F18" s="27" t="n"/>
+      <c r="G18" s="37">
         <f>IF(OR(F18="",F18="در انتظار"),"",IF(G18="",TODAY(),G18))</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="G19" s="16">
+      <c r="A19" s="27" t="n"/>
+      <c r="B19" s="27" t="n"/>
+      <c r="C19" s="27" t="n"/>
+      <c r="D19" s="27" t="n"/>
+      <c r="E19" s="27" t="n"/>
+      <c r="F19" s="27" t="n"/>
+      <c r="G19" s="37">
         <f>IF(OR(F19="",F19="در انتظار"),"",IF(G19="",TODAY(),G19))</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="G20" s="16">
+      <c r="A20" s="27" t="n"/>
+      <c r="B20" s="27" t="n"/>
+      <c r="C20" s="27" t="n"/>
+      <c r="D20" s="27" t="n"/>
+      <c r="E20" s="27" t="n"/>
+      <c r="F20" s="27" t="n"/>
+      <c r="G20" s="37">
         <f>IF(OR(F20="",F20="در انتظار"),"",IF(G20="",TODAY(),G20))</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="G21" s="16">
+      <c r="A21" s="27" t="n"/>
+      <c r="B21" s="27" t="n"/>
+      <c r="C21" s="27" t="n"/>
+      <c r="D21" s="27" t="n"/>
+      <c r="E21" s="27" t="n"/>
+      <c r="F21" s="27" t="n"/>
+      <c r="G21" s="37">
         <f>IF(OR(F21="",F21="در انتظار"),"",IF(G21="",TODAY(),G21))</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="G22" s="16">
+      <c r="A22" s="27" t="n"/>
+      <c r="B22" s="27" t="n"/>
+      <c r="C22" s="27" t="n"/>
+      <c r="D22" s="27" t="n"/>
+      <c r="E22" s="27" t="n"/>
+      <c r="F22" s="27" t="n"/>
+      <c r="G22" s="37">
         <f>IF(OR(F22="",F22="در انتظار"),"",IF(G22="",TODAY(),G22))</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="G23" s="16">
+      <c r="A23" s="27" t="n"/>
+      <c r="B23" s="27" t="n"/>
+      <c r="C23" s="27" t="n"/>
+      <c r="D23" s="27" t="n"/>
+      <c r="E23" s="27" t="n"/>
+      <c r="F23" s="27" t="n"/>
+      <c r="G23" s="37">
         <f>IF(OR(F23="",F23="در انتظار"),"",IF(G23="",TODAY(),G23))</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="G24" s="16">
+      <c r="A24" s="27" t="n"/>
+      <c r="B24" s="27" t="n"/>
+      <c r="C24" s="27" t="n"/>
+      <c r="D24" s="27" t="n"/>
+      <c r="E24" s="27" t="n"/>
+      <c r="F24" s="27" t="n"/>
+      <c r="G24" s="37">
         <f>IF(OR(F24="",F24="در انتظار"),"",IF(G24="",TODAY(),G24))</f>
         <v/>
       </c>
@@ -1552,36 +1978,36 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>سناریو</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="26" t="inlineStr">
         <is>
           <t>مرجع کد</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="25" t="inlineStr">
         <is>
           <t>ذخیره فلش</t>
         </is>
       </c>
-      <c r="B2" s="22" t="inlineStr">
+      <c r="B2" s="41" t="inlineStr">
         <is>
           <t>diag.c func__Diag_WriteFlash</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="25" t="inlineStr">
         <is>
           <t>پروتکل ESP</t>
         </is>
       </c>
-      <c r="B3" s="22" t="inlineStr">
+      <c r="B3" s="41" t="inlineStr">
         <is>
           <t>esp_link.c SendDiagChunk/SendDiagAll</t>
         </is>
@@ -1607,68 +2033,68 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="25" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="25" t="inlineStr">
         <is>
           <t>شرح ایراد</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="25" t="inlineStr">
         <is>
           <t>اصلاح</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="25" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="25" t="inlineStr">
         <is>
           <t>سرریز RAM هنگام لینک (264 بایت) بعد از استاتیک‌شدن بافرهای Init، و قاب ~2064 بایتی func__Diag_SaveNow روی استک 1024 بایتی تسک کنترل (سرریز استک هنگام ذخیره)</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="25" t="inlineStr">
         <is>
           <t>رزرو هیپ لینکر صفر شد (تخصیص فقط استاتیک است) و Init/SaveNow با بافر کمکی Stage بازنویسی شدند: فقط seqها اسکالر می‌مانند؛ کامیت‌های fix(linker) و fix(Diag) روی شاخه arena/859ce091-changeover</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="25" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="25" t="inlineStr">
         <is>
           <t>ممیزی خط‌به‌خط: ذخیره فلش Diag (حین شارژ حدود هر ۶۰ ثانیه) برخلاف ذخیره‌های NVM و CalLut شارژر را معلق نمی‌کرد؛ پاک‌کردن صفحه کل CPU را ۲۰ تا ۴۰ میلی‌ثانیه نگه می‌دارد و گیت‌ها داخل پنجره کور سوییچ می‌کردند</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="25" t="inlineStr">
         <is>
           <t>در func__Diag_SaveNow دور WriteFlash، ‏func__Charger_SetSuspended(true)‎ + ‏func__BspPwm_StopAll()‎ و بعد ‏SetSuspended(false)‎ اضافه شد (زمینه تسک کنترل، توقف بی‌درنگ، آینه duty دست‌نخورده)؛ هر دو گیت سبز</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B4" s="22" t="inlineStr">
+      <c r="B4" s="41" t="inlineStr">
         <is>
           <t>ممیزی خط‌به‌خط (مورد ۶): func__Diag_RecordFault شمارنده‌ها را با شماره خام بیت (‏1u &lt;&lt; 6‎، ‏1u &lt;&lt; 7‎ و بیت ۰) رمزگشایی می‌کرد؛ جابه‌جایی بیت‌های FAULT در app_types.h بی‌صدا آمار را غلط می‌کرد و کامنت «reuse for ADC» روی شمارنده ovCount گمراه‌کننده بود</t>
         </is>
       </c>
-      <c r="C4" s="22" t="inlineStr">
+      <c r="C4" s="41" t="inlineStr">
         <is>
           <t>هر سه شرط با ثابت‌های نام‌دار FAULT_CHARGER_BAT_LOST / FAULT_CHARGER_TECHNICAL / FAULT_ADC نوشته شد (نام فیلد ovCount به‌خاطر چیدمان رکورد فلش ماند)؛ نگهبان tools/check_diag_fault_bits.py اضافه شد تا برگشت شماره خام برای همیشه FAIL شود؛ یکسانی رفتار با مقایسه اسمبلی ثابت شد</t>
         </is>
@@ -1694,23 +2120,24 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="25" t="inlineStr">
         <is>
           <t>تأیید</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="25" t="inlineStr">
         <is>
           <t>امضا</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="25" t="inlineStr">
         <is>
           <t>11 مورد دیاگ روی برد تست شد و پنل سه‌صفحه‌ای نمایش می‌دهد</t>
         </is>
       </c>
+      <c r="B2" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1728,102 +2155,112 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="25" t="inlineStr">
         <is>
           <t>فایل</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="25" t="inlineStr">
         <is>
           <t>توضیح</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="22" t="inlineStr">
+      <c r="A2" s="41" t="inlineStr">
         <is>
           <t>diag.h</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="25" t="inlineStr">
         <is>
           <t>ساختار diag_record_t و API</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="22" t="inlineStr">
+      <c r="A3" s="41" t="inlineStr">
         <is>
           <t>diag.c</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="25" t="inlineStr">
         <is>
           <t>پیاده‌سازی فلش و لاگ</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="22" t="inlineStr">
+      <c r="A4" s="41" t="inlineStr">
         <is>
           <t>README.md</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>شرح ماژول، رکورد و مسیر تست</t>
         </is>
       </c>
     </row>
-    <row r="5"/>
+    <row r="5">
+      <c r="A5" s="27" t="n"/>
+      <c r="B5" s="27" t="n"/>
+    </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="27" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
+      <c r="B6" s="27" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="27" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
+      <c r="B7" s="27" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="27" t="inlineStr">
         <is>
           <t>انجام شد</t>
         </is>
       </c>
+      <c r="B8" s="27" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="27" t="inlineStr">
         <is>
           <t>قبول</t>
         </is>
       </c>
+      <c r="B9" s="27" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="27" t="inlineStr">
         <is>
           <t>رد</t>
         </is>
       </c>
+      <c r="B10" s="27" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="27" t="inlineStr">
         <is>
           <t>مسدود</t>
         </is>
       </c>
+      <c r="B11" s="27" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="27" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
+      <c r="B12" s="27" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1850,60 +2287,70 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="17" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ماشین حالت ماژول لاگ تشخیصی (Diag)</t>
         </is>
       </c>
-    </row>
-    <row r="2"/>
+      <c r="B1" s="27" t="n"/>
+      <c r="C1" s="27" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="27" t="n"/>
+      <c r="B2" s="27" t="n"/>
+      <c r="C2" s="27" t="n"/>
+    </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="18" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>حالت‌ها و گذارهای همین ماژول</t>
         </is>
       </c>
-      <c r="B3" s="19" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Diag_State_Machine.xlsx</t>
         </is>
       </c>
+      <c r="C3" s="27" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>ماشین حالت کل برنامه (نمای سیستمی)</t>
         </is>
       </c>
-      <c r="B4" s="19" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>../../../Documentation/System_State_Machine.xlsx</t>
         </is>
       </c>
+      <c r="C4" s="27" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>راهنمای رنگ‌ها</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>سبز = عادی/سالم · زرد = هشدار یا انتظار · قرمز = خطا یا قفل · نارنجی = در حال کار · خاکستری = بی‌کار · آبی = اطلاعاتی</t>
         </is>
       </c>
+      <c r="C5" s="27" t="n"/>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>بازتولید</t>
         </is>
       </c>
-      <c r="B6" s="19" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>python3 tools/make_module_state_machines.py</t>
         </is>
       </c>
+      <c r="C6" s="27" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Firmware/Modules/Diag/Diag_Validation.xlsx
+++ b/Firmware/Modules/Diag/Diag_Validation.xlsx
@@ -31,7 +31,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -134,6 +134,10 @@
       <sz val="11"/>
       <u val="single"/>
     </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -158,7 +162,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -194,11 +198,12 @@
         <color rgb="00B4C6E7"/>
       </bottom>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -301,6 +306,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -667,7 +675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -708,6 +716,14 @@
       <c r="A7" s="25" t="inlineStr">
         <is>
           <t>تست‌ها: 1) فلش ping-pong 0x0800F800/0xFC00 با CRC32، 2) Init انتخاب رکورد سالم با seq جدیدتر، 3) AddChargeSec هر کانال، 4) RecordChargeComplete، 5) RecordFault با snapshot کامل، 6) RecordPowerOff/On با محاسبه duration، 7) UpdateMinMax، 8) Tick هر ثانیه + debounce save 60s، 9) TIME_SYNC از ESP، 10) DIAG_REQ و ارسال 5 چانک</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="42" t="inlineStr">
+        <is>
+          <t>اولویت تست‌های عملی: «بالا» یعنی رفتار اصلی‌ای که در کار عادی دستگاه می‌بینید (روشن‌شدن، شروع و پایان شارژ، چهره‌های اصلی چراغ‌ها، رفتن تغذیه روی برق ورودی، خطاهای اصلی)؛ اول همین‌ها را انجام دهید. «متوسط» رفتارهای فرعیِ کاربردی است و «پایین» ریزه‌کاری‌ها (مثل اثر نوسان چند درصدی روی ریتم چشمک یا لبه‌های دقیق درصد و زمان).
+ستون «چه چیزی باید ببینید تا بگویید درست است» می‌گوید دقیقاً چه چیزی را باید ببینید یا بشنوید تا آن تست را قبول کنید؛ اگر چیز دیگری دیدید، وضعیت را «رد» بزنید و در شرح ایراد بنویسید چه دیدید.</t>
         </is>
       </c>
     </row>
@@ -723,7 +739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -746,27 +762,32 @@
           <t>شرح تست</t>
         </is>
       </c>
-      <c r="C1" s="26" t="inlineStr">
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>اولویت</t>
+        </is>
+      </c>
+      <c r="D1" s="26" t="inlineStr">
         <is>
           <t>روش</t>
         </is>
       </c>
-      <c r="D1" s="26" t="inlineStr">
-        <is>
-          <t>نتیجه مورد انتظار</t>
-        </is>
-      </c>
       <c r="E1" s="26" t="inlineStr">
         <is>
+          <t>چه چیزی باید ببینید تا بگویید درست است</t>
+        </is>
+      </c>
+      <c r="F1" s="26" t="inlineStr">
+        <is>
           <t>نتیجه واقعی</t>
         </is>
       </c>
-      <c r="F1" s="26" t="inlineStr">
+      <c r="G1" s="26" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="G1" s="26" t="inlineStr">
+      <c r="H1" s="26" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
@@ -775,239 +796,279 @@
     <row r="2" ht="40.5" customHeight="1">
       <c r="A2" s="28" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B2" s="29" t="inlineStr">
+        <is>
+          <t>RecordChargeComplete</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D2" s="30" t="inlineStr">
+        <is>
+          <t>گام ۱: یک باتری را تا پرشدن کامل شارژ کن.
+گام ۲: در گزارش پنل ببین «شارژ کامل» ثبت شده یا نه.
+گام ۳: یک بار دیگر هم انجام بده و شمارش را چک کن.</t>
+        </is>
+      </c>
+      <c r="E2" s="29" t="inlineStr">
+        <is>
+          <t>باید ببینید: هر شارژ کامل فقط یک بار شمرده و در گزارش ثبت می‌شود. اگر نشمرد یا دوبار شمرد، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="F2" s="29" t="n"/>
+      <c r="G2" s="31" t="n"/>
+      <c r="H2" s="32">
+        <f>IF(OR(G2="",G2="در انتظار"),"",IF(H2="",TODAY(),H2))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="40.5" customHeight="1">
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B3" s="33" t="inlineStr">
+        <is>
+          <t>RecordFault</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D3" s="34" t="inlineStr">
+        <is>
+          <t>گام ۱: ساعت دستگاه را از پنل درست کن.
+گام ۲: حین شارژ سیم باتری را بکش تا خطای ۶ بیاید.
+گام ۳: در سوابق پنل ببین خطا با زمان درست ثبت شده.</t>
+        </is>
+      </c>
+      <c r="E3" s="33" t="inlineStr">
+        <is>
+          <t>باید ببینید: خطای قطع باتری در سوابق پنل با زمان درست هست. اگر نبود یا زمانش غلط بود، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="F3" s="33" t="n"/>
+      <c r="G3" s="35" t="n"/>
+      <c r="H3" s="36">
+        <f>IF(OR(G3="",G3="در انتظار"),"",IF(H3="",TODAY(),H3))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="40.5" customHeight="1">
+      <c r="A4" s="28" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B4" s="29" t="inlineStr">
+        <is>
+          <t>PowerOff/On</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D4" s="30" t="inlineStr">
+        <is>
+          <t>گام ۱: ساعت را از پنل همگام کن.
+گام ۲: برق شهر را بکش، یک دقیقه صبر کن و برگردان.
+گام ۳: در سوابق، قطع و وصل و مدت خاموشی را چک کن.</t>
+        </is>
+      </c>
+      <c r="E4" s="29" t="inlineStr">
+        <is>
+          <t>باید ببینید: قطع و وصل برق با زمان و مدت خاموشی درست در سوابق ثبت شده است. اگر نبود یا مدتش غلط بود، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="F4" s="29" t="n"/>
+      <c r="G4" s="31" t="n"/>
+      <c r="H4" s="32">
+        <f>IF(OR(G4="",G4="در انتظار"),"",IF(H4="",TODAY(),H4))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="40.5" customHeight="1">
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B5" s="33" t="inlineStr">
+        <is>
+          <t>DIAG_REQ</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D5" s="34" t="inlineStr">
+        <is>
+          <t>گام ۱: در پنل درخواست گزارش کامل بده.
+گام ۲: صبر کن همهٔ بخش‌های گزارش بیاید و بخوانشان.</t>
+        </is>
+      </c>
+      <c r="E5" s="33" t="inlineStr">
+        <is>
+          <t>باید ببینید: گزارش کامل و خوانا می‌آید و بخشی گم نمی‌شود. اگر ناقص آمد، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="F5" s="33" t="n"/>
+      <c r="G5" s="35" t="n"/>
+      <c r="H5" s="36">
+        <f>IF(OR(G5="",G5="در انتظار"),"",IF(H5="",TODAY(),H5))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="40.5" customHeight="1">
+      <c r="A6" s="28" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B2" s="29" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>Init بدون رکورد</t>
         </is>
       </c>
-      <c r="C2" s="30" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D6" s="30" t="inlineStr">
         <is>
           <t>گام ۱: فلش هر دو صفحهٔ Diag (نشانی 1032192 و 1033216) را کامل پاک کن.
 گام ۲: برد را بوت کن و رکورد خوانده‌شده را از پنل بخوان.
 گام ۳: باید رکورد پیش‌فرض ساخته شده باشد: کمینه‌ها 4294967295 (بزرگ‌ترین عدد 32 بیتی) و همهٔ شمارنده‌ها صفر.</t>
         </is>
       </c>
-      <c r="D2" s="29" t="inlineStr">
-        <is>
-          <t>پیش‌فرض با min=0xFFFFFFFF و شمارنده صفر</t>
-        </is>
-      </c>
-      <c r="E2" s="29" t="n"/>
-      <c r="F2" s="31" t="n"/>
-      <c r="G2" s="32">
-        <f>IF(OR(F2="",F2="در انتظار"),"",IF(G2="",TODAY(),G2))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3" ht="40.5" customHeight="1">
-      <c r="A3" s="28" t="inlineStr">
+      <c r="E6" s="29" t="inlineStr">
+        <is>
+          <t>باید ببینید: بعد از پاک‌بودن حافظه، دستگاه عادی بالا می‌آید و شمارنده‌ها و سابقه‌ها از صفر شروع می‌شوند. اگر مقدار عجیب یا سابقهٔ خیالی دیدید، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="F6" s="29" t="n"/>
+      <c r="G6" s="31" t="n"/>
+      <c r="H6" s="32">
+        <f>IF(OR(G6="",G6="در انتظار"),"",IF(H6="",TODAY(),H6))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="40.5" customHeight="1">
+      <c r="A7" s="28" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B3" s="33" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>AddChargeSec</t>
         </is>
       </c>
-      <c r="C3" s="34" t="inlineStr">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D7" s="34" t="inlineStr">
         <is>
           <t>گام ۱: یک باتری نیمه‌خالی را به شارژ واقعی بزن و زمان بگیر.
 گام ۲: بعد از مدتی شارژ، از پنل گزارش زمان شارژ همان کانال را بخوان.
 گام ۳: عدد گزارش را با زمان واقعی خودت مقایسه کن.</t>
         </is>
       </c>
-      <c r="D3" s="33" t="inlineStr">
-        <is>
-          <t>زمان شارژ ثبت‌شده با زمان واقعی می‌خواند و برای هر کانال جدا نگه داشته می‌شود</t>
-        </is>
-      </c>
-      <c r="E3" s="33" t="n"/>
-      <c r="F3" s="35" t="n"/>
-      <c r="G3" s="36">
-        <f>IF(OR(F5="",F5="در انتظار"),"",IF(G5="",TODAY(),G5))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="40.5" customHeight="1">
-      <c r="A4" s="28" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B4" s="29" t="inlineStr">
-        <is>
-          <t>RecordChargeComplete</t>
-        </is>
-      </c>
-      <c r="C4" s="30" t="inlineStr">
-        <is>
-          <t>گام ۱: یک باتری را تا پرشدن کامل شارژ کن.
-گام ۲: در گزارش پنل ببین «شارژ کامل» ثبت شده یا نه.
-گام ۳: یک بار دیگر هم انجام بده و شمارش را چک کن.</t>
-        </is>
-      </c>
-      <c r="D4" s="29" t="inlineStr">
-        <is>
-          <t>هر شارژ کامل یک بار شمرده و ثبت می‌شود</t>
-        </is>
-      </c>
-      <c r="E4" s="29" t="n"/>
-      <c r="F4" s="31" t="n"/>
-      <c r="G4" s="32">
-        <f>IF(OR(F6="",F6="در انتظار"),"",IF(G6="",TODAY(),G6))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="40.5" customHeight="1">
-      <c r="A5" s="28" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B5" s="33" t="inlineStr">
-        <is>
-          <t>RecordFault</t>
-        </is>
-      </c>
-      <c r="C5" s="34" t="inlineStr">
-        <is>
-          <t>گام ۱: ساعت دستگاه را از پنل درست کن.
-گام ۲: حین شارژ سیم باتری را بکش تا خطای ۶ بیاید.
-گام ۳: در سوابق پنل ببین خطا با زمان درست ثبت شده.</t>
-        </is>
-      </c>
-      <c r="D5" s="33" t="inlineStr">
-        <is>
-          <t>خطای ۶ در سوابق با زمان درست هست</t>
-        </is>
-      </c>
-      <c r="E5" s="33" t="n"/>
-      <c r="F5" s="35" t="n"/>
-      <c r="G5" s="36">
-        <f>IF(OR(F7="",F7="در انتظار"),"",IF(G7="",TODAY(),G7))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="40.5" customHeight="1">
-      <c r="A6" s="28" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B6" s="29" t="inlineStr">
-        <is>
-          <t>PowerOff/On</t>
-        </is>
-      </c>
-      <c r="C6" s="30" t="inlineStr">
-        <is>
-          <t>گام ۱: ساعت را از پنل همگام کن.
-گام ۲: برق شهر را بکش، یک دقیقه صبر کن و برگردان.
-گام ۳: در سوابق، قطع و وصل و مدت خاموشی را چک کن.</t>
-        </is>
-      </c>
-      <c r="D6" s="29" t="inlineStr">
-        <is>
-          <t>قطع و وصل برق با زمان و مدت درست ثبت شده</t>
-        </is>
-      </c>
-      <c r="E6" s="29" t="n"/>
-      <c r="F6" s="31" t="n"/>
-      <c r="G6" s="32">
-        <f>IF(OR(F8="",F8="در انتظار"),"",IF(G8="",TODAY(),G8))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="40.5" customHeight="1">
-      <c r="A7" s="28" t="inlineStr">
+      <c r="E7" s="33" t="inlineStr">
+        <is>
+          <t>باید ببینید: زمان شارژ ثبت‌شده با زمان واقعی می‌خواند و برای هر کانال جدا نگه داشته می‌شود. اگر نخواند، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="F7" s="33" t="n"/>
+      <c r="G7" s="35" t="n"/>
+      <c r="H7" s="36">
+        <f>IF(OR(G7="",G7="در انتظار"),"",IF(H7="",TODAY(),H7))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="40.5" customHeight="1">
+      <c r="A8" s="28" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B7" s="33" t="inlineStr">
+      <c r="B8" s="33" t="inlineStr">
         <is>
           <t>Min/Max</t>
         </is>
       </c>
-      <c r="C7" s="34" t="inlineStr">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D8" s="34" t="inlineStr">
         <is>
           <t>گام ۱: ورودی را از منبع آزمایشگاهی بده.
 گام ۲: ولتاژ را آرام از کم به زیاد و برگردان (مثلاً ۱۸ تا ۳۰ ولت).
 گام ۳: کمینه و بیشینهٔ ثبت‌شده را در گزارش با منبع مقایسه کن.</t>
         </is>
       </c>
-      <c r="D7" s="33" t="inlineStr">
-        <is>
-          <t>کمینه و بیشینهٔ ولتاژ ورودی درست ثبت شده</t>
-        </is>
-      </c>
-      <c r="E7" s="33" t="n"/>
-      <c r="F7" s="35" t="n"/>
-      <c r="G7" s="36">
-        <f>IF(OR(F9="",F9="در انتظار"),"",IF(G9="",TODAY(),G9))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="54" customHeight="1">
-      <c r="A8" s="28" t="inlineStr">
+      <c r="E8" s="33" t="inlineStr">
+        <is>
+          <t>باید ببینید: کمینه و بیشینهٔ ولتاژ ورودی در گزارش با منبع آزمایشگاهی می‌خواند. اگر نخواند، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="F8" s="33" t="n"/>
+      <c r="G8" s="35" t="n"/>
+      <c r="H8" s="36">
+        <f>IF(OR(G8="",G8="در انتظار"),"",IF(H8="",TODAY(),H8))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="54" customHeight="1">
+      <c r="A9" s="28" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B8" s="29" t="inlineStr">
+      <c r="B9" s="29" t="inlineStr">
         <is>
           <t>TIME_SYNC</t>
         </is>
       </c>
-      <c r="C8" s="30" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D9" s="30" t="inlineStr">
         <is>
           <t>گام ۱: از پنل ساعت دستگاه را با ساعت کامپیوتر همگام کن.
 گام ۲: یک رویداد بساز (مثلاً خطای ۶).
 گام ۳: زمان رویداد را در سوابق با ساعت واقعی مقایسه کن.</t>
         </is>
       </c>
-      <c r="D8" s="29" t="inlineStr">
-        <is>
-          <t>زمان رویدادها با ساعت واقعی می‌خواند</t>
-        </is>
-      </c>
-      <c r="E8" s="29" t="n"/>
-      <c r="F8" s="31" t="n"/>
-      <c r="G8" s="32">
-        <f>IF(OR(F10="",F10="در انتظار"),"",IF(G10="",TODAY(),G10))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="40.5" customHeight="1">
-      <c r="A9" s="28" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B9" s="33" t="inlineStr">
-        <is>
-          <t>DIAG_REQ</t>
-        </is>
-      </c>
-      <c r="C9" s="34" t="inlineStr">
-        <is>
-          <t>گام ۱: در پنل درخواست گزارش کامل بده.
-گام ۲: صبر کن همهٔ بخش‌های گزارش بیاید و بخوانشان.</t>
-        </is>
-      </c>
-      <c r="D9" s="33" t="inlineStr">
-        <is>
-          <t>گزارش کامل و خوانا می‌آید؛ بخشی گم نمی‌شود</t>
-        </is>
-      </c>
-      <c r="E9" s="33" t="n"/>
-      <c r="F9" s="35" t="n"/>
-      <c r="G9" s="36">
-        <f>IF(OR(F11="",F11="در انتظار"),"",IF(G11="",TODAY(),G11))</f>
+      <c r="E9" s="29" t="inlineStr">
+        <is>
+          <t>باید ببینید: زمان رویدادها با ساعت واقعی می‌خواند. اگر اختلاف دیدید، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="F9" s="29" t="n"/>
+      <c r="G9" s="31" t="n"/>
+      <c r="H9" s="32">
+        <f>IF(OR(G9="",G9="در انتظار"),"",IF(H9="",TODAY(),H9))</f>
         <v/>
       </c>
     </row>
@@ -1022,513 +1083,438 @@
           <t>ذخیره فلش حین شارژ فعال: تعلیق شارژر دور نوشتن</t>
         </is>
       </c>
-      <c r="C10" s="34" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D10" s="34" t="inlineStr">
         <is>
           <t>گام ۱: شارژ واقعی یک باتری را شروع کن.
 گام ۲: حین شارژ یک خطای ۶ بساز و پاک کن تا دستگاه سابقه ذخیره کند.
 گام ۳: بعدش ببین شارژ عادی ادامه دارد و گزارش تازه سالم خوانده می‌شود.</t>
         </is>
       </c>
-      <c r="D10" s="33" t="inlineStr">
-        <is>
-          <t>ذخیره‌کردن سابقه وسط شارژ، شارژ را خراب نمی‌کند و گزارش سالم است</t>
-        </is>
-      </c>
       <c r="E10" s="33" t="inlineStr">
         <is>
+          <t>باید ببینید: ذخیره‌شدن سابقه وسط شارژ، شارژ را خراب نمی‌کند و گزارش سالم خوانده می‌شود. اگر شارژ به‌هم ریخت، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="F10" s="33" t="inlineStr">
+        <is>
           <t>هاست: هر دو گیت سبز و بودجه RAM/استک سالم (ctrl ‏384/1024‎، آزاد 1544 بایت)؛ نتیجه برد: در انتظار</t>
         </is>
       </c>
-      <c r="F10" s="35" t="n"/>
-      <c r="G10" s="36">
-        <f>IF(OR(F13="",F13="در انتظار"),"",IF(G13="",TODAY(),G13))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="40.5" customHeight="1">
-      <c r="A11" s="27" t="n"/>
-      <c r="B11" s="27" t="n"/>
-      <c r="C11" s="27" t="n"/>
-      <c r="D11" s="27" t="n"/>
-      <c r="E11" s="27" t="n"/>
-      <c r="F11" s="27" t="n"/>
-      <c r="G11" s="37">
-        <f>IF(OR(F15="",F15="در انتظار"),"",IF(G15="",TODAY(),G15))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="40.5" customHeight="1">
-      <c r="A12" s="27" t="n"/>
-      <c r="B12" s="27" t="n"/>
-      <c r="C12" s="27" t="n"/>
-      <c r="D12" s="27" t="n"/>
-      <c r="E12" s="27" t="n"/>
-      <c r="F12" s="27" t="n"/>
-      <c r="G12" s="37">
-        <f>IF(OR(F16="",F16="در انتظار"),"",IF(G16="",TODAY(),G16))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="54" customHeight="1">
-      <c r="A13" s="27" t="n"/>
-      <c r="B13" s="27" t="n"/>
-      <c r="C13" s="27" t="n"/>
-      <c r="D13" s="27" t="n"/>
-      <c r="E13" s="27" t="n"/>
-      <c r="F13" s="27" t="n"/>
-      <c r="G13" s="37">
-        <f>IF(OR(F17="",F17="در انتظار"),"",IF(G17="",TODAY(),G17))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="54" customHeight="1">
-      <c r="A14" s="27" t="n"/>
-      <c r="B14" s="27" t="n"/>
-      <c r="C14" s="27" t="n"/>
-      <c r="D14" s="27" t="n"/>
-      <c r="E14" s="27" t="n"/>
-      <c r="F14" s="27" t="n"/>
-      <c r="G14" s="37">
-        <f>IF(OR(F18="",F18="در انتظار"),"",IF(G18="",TODAY(),G18))</f>
-        <v/>
-      </c>
+      <c r="G10" s="35" t="n"/>
+      <c r="H10" s="36">
+        <f>IF(OR(G10="",G10="در انتظار"),"",IF(H10="",TODAY(),H10))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="43" t="n"/>
+      <c r="B11" s="43" t="n"/>
+      <c r="C11" s="43" t="n"/>
+      <c r="D11" s="43" t="n"/>
+      <c r="E11" s="43" t="n"/>
+      <c r="F11" s="43" t="n"/>
+      <c r="G11" s="43" t="n"/>
+      <c r="H11" s="44" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="43" t="n"/>
+      <c r="B12" s="43" t="n"/>
+      <c r="C12" s="43" t="n"/>
+      <c r="D12" s="43" t="n"/>
+      <c r="E12" s="43" t="n"/>
+      <c r="F12" s="43" t="n"/>
+      <c r="G12" s="43" t="n"/>
+      <c r="H12" s="44" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="43" t="n"/>
+      <c r="B13" s="43" t="n"/>
+      <c r="C13" s="43" t="n"/>
+      <c r="D13" s="43" t="n"/>
+      <c r="E13" s="43" t="n"/>
+      <c r="F13" s="43" t="n"/>
+      <c r="G13" s="43" t="n"/>
+      <c r="H13" s="44" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="43" t="n"/>
+      <c r="B14" s="43" t="n"/>
+      <c r="C14" s="43" t="n"/>
+      <c r="D14" s="43" t="n"/>
+      <c r="E14" s="43" t="n"/>
+      <c r="F14" s="43" t="n"/>
+      <c r="G14" s="43" t="n"/>
+      <c r="H14" s="44" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="27" t="n"/>
-      <c r="B15" s="27" t="n"/>
-      <c r="C15" s="27" t="n"/>
-      <c r="D15" s="27" t="n"/>
-      <c r="E15" s="27" t="n"/>
-      <c r="F15" s="27" t="n"/>
-      <c r="G15" s="37">
-        <f>IF(OR(F19="",F19="در انتظار"),"",IF(G19="",TODAY(),G19))</f>
-        <v/>
-      </c>
+      <c r="A15" s="43" t="n"/>
+      <c r="B15" s="43" t="n"/>
+      <c r="C15" s="43" t="n"/>
+      <c r="D15" s="43" t="n"/>
+      <c r="E15" s="43" t="n"/>
+      <c r="F15" s="43" t="n"/>
+      <c r="G15" s="43" t="n"/>
+      <c r="H15" s="44" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="27" t="n"/>
-      <c r="B16" s="27" t="n"/>
-      <c r="C16" s="27" t="n"/>
-      <c r="D16" s="27" t="n"/>
-      <c r="E16" s="27" t="n"/>
-      <c r="F16" s="27" t="n"/>
-      <c r="G16" s="37">
-        <f>IF(OR(F20="",F20="در انتظار"),"",IF(G20="",TODAY(),G20))</f>
-        <v/>
-      </c>
+      <c r="A16" s="43" t="n"/>
+      <c r="B16" s="43" t="n"/>
+      <c r="C16" s="43" t="n"/>
+      <c r="D16" s="43" t="n"/>
+      <c r="E16" s="43" t="n"/>
+      <c r="F16" s="43" t="n"/>
+      <c r="G16" s="43" t="n"/>
+      <c r="H16" s="44" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="27" t="n"/>
-      <c r="B17" s="27" t="n"/>
-      <c r="C17" s="27" t="n"/>
-      <c r="D17" s="27" t="n"/>
-      <c r="E17" s="27" t="n"/>
-      <c r="F17" s="27" t="n"/>
-      <c r="G17" s="37">
-        <f>IF(OR(F21="",F21="در انتظار"),"",IF(G21="",TODAY(),G21))</f>
-        <v/>
-      </c>
+      <c r="A17" s="43" t="n"/>
+      <c r="B17" s="43" t="n"/>
+      <c r="C17" s="43" t="n"/>
+      <c r="D17" s="43" t="n"/>
+      <c r="E17" s="43" t="n"/>
+      <c r="F17" s="43" t="n"/>
+      <c r="G17" s="43" t="n"/>
+      <c r="H17" s="44" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="27" t="n"/>
-      <c r="B18" s="27" t="n"/>
-      <c r="C18" s="27" t="n"/>
-      <c r="D18" s="27" t="n"/>
-      <c r="E18" s="27" t="n"/>
-      <c r="F18" s="27" t="n"/>
-      <c r="G18" s="37">
-        <f>IF(OR(F22="",F22="در انتظار"),"",IF(G22="",TODAY(),G22))</f>
-        <v/>
-      </c>
+      <c r="A18" s="43" t="n"/>
+      <c r="B18" s="43" t="n"/>
+      <c r="C18" s="43" t="n"/>
+      <c r="D18" s="43" t="n"/>
+      <c r="E18" s="43" t="n"/>
+      <c r="F18" s="43" t="n"/>
+      <c r="G18" s="43" t="n"/>
+      <c r="H18" s="44" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="27" t="n"/>
-      <c r="B19" s="27" t="n"/>
-      <c r="C19" s="27" t="n"/>
-      <c r="D19" s="27" t="n"/>
-      <c r="E19" s="27" t="n"/>
-      <c r="F19" s="27" t="n"/>
-      <c r="G19" s="37">
-        <f>IF(OR(F23="",F23="در انتظار"),"",IF(G23="",TODAY(),G23))</f>
-        <v/>
-      </c>
+      <c r="A19" s="43" t="n"/>
+      <c r="B19" s="43" t="n"/>
+      <c r="C19" s="43" t="n"/>
+      <c r="D19" s="43" t="n"/>
+      <c r="E19" s="43" t="n"/>
+      <c r="F19" s="43" t="n"/>
+      <c r="G19" s="43" t="n"/>
+      <c r="H19" s="44" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="27" t="n"/>
-      <c r="B20" s="27" t="n"/>
-      <c r="C20" s="27" t="n"/>
-      <c r="D20" s="27" t="n"/>
-      <c r="E20" s="27" t="n"/>
-      <c r="F20" s="27" t="n"/>
-      <c r="G20" s="37">
-        <f>IF(OR(F24="",F24="در انتظار"),"",IF(G24="",TODAY(),G24))</f>
-        <v/>
-      </c>
+      <c r="A20" s="43" t="n"/>
+      <c r="B20" s="43" t="n"/>
+      <c r="C20" s="43" t="n"/>
+      <c r="D20" s="43" t="n"/>
+      <c r="E20" s="43" t="n"/>
+      <c r="F20" s="43" t="n"/>
+      <c r="G20" s="43" t="n"/>
+      <c r="H20" s="44" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="27" t="n"/>
-      <c r="B21" s="27" t="n"/>
-      <c r="C21" s="27" t="n"/>
-      <c r="D21" s="27" t="n"/>
-      <c r="E21" s="27" t="n"/>
-      <c r="F21" s="27" t="n"/>
-      <c r="G21" s="37">
-        <f>IF(OR(F25="",F25="در انتظار"),"",IF(G25="",TODAY(),G25))</f>
-        <v/>
-      </c>
+      <c r="A21" s="43" t="n"/>
+      <c r="B21" s="43" t="n"/>
+      <c r="C21" s="43" t="n"/>
+      <c r="D21" s="43" t="n"/>
+      <c r="E21" s="43" t="n"/>
+      <c r="F21" s="43" t="n"/>
+      <c r="G21" s="43" t="n"/>
+      <c r="H21" s="44" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="27" t="n"/>
-      <c r="B22" s="27" t="n"/>
-      <c r="C22" s="27" t="n"/>
-      <c r="D22" s="27" t="n"/>
-      <c r="E22" s="27" t="n"/>
-      <c r="F22" s="27" t="n"/>
-      <c r="G22" s="37">
-        <f>IF(OR(F26="",F26="در انتظار"),"",IF(G26="",TODAY(),G26))</f>
-        <v/>
-      </c>
+      <c r="A22" s="43" t="n"/>
+      <c r="B22" s="43" t="n"/>
+      <c r="C22" s="43" t="n"/>
+      <c r="D22" s="43" t="n"/>
+      <c r="E22" s="43" t="n"/>
+      <c r="F22" s="43" t="n"/>
+      <c r="G22" s="43" t="n"/>
+      <c r="H22" s="44" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="27" t="n"/>
-      <c r="B23" s="27" t="n"/>
-      <c r="C23" s="27" t="n"/>
-      <c r="D23" s="27" t="n"/>
-      <c r="E23" s="27" t="n"/>
-      <c r="F23" s="27" t="n"/>
-      <c r="G23" s="37">
-        <f>IF(OR(F27="",F27="در انتظار"),"",IF(G27="",TODAY(),G27))</f>
-        <v/>
-      </c>
+      <c r="A23" s="43" t="n"/>
+      <c r="B23" s="43" t="n"/>
+      <c r="C23" s="43" t="n"/>
+      <c r="D23" s="43" t="n"/>
+      <c r="E23" s="43" t="n"/>
+      <c r="F23" s="43" t="n"/>
+      <c r="G23" s="43" t="n"/>
+      <c r="H23" s="44" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="27" t="n"/>
-      <c r="B24" s="27" t="n"/>
-      <c r="C24" s="27" t="n"/>
-      <c r="D24" s="27" t="n"/>
-      <c r="E24" s="27" t="n"/>
-      <c r="F24" s="27" t="n"/>
-      <c r="G24" s="37">
-        <f>IF(OR(F28="",F28="در انتظار"),"",IF(G28="",TODAY(),G28))</f>
-        <v/>
-      </c>
+      <c r="A24" s="43" t="n"/>
+      <c r="B24" s="43" t="n"/>
+      <c r="C24" s="43" t="n"/>
+      <c r="D24" s="43" t="n"/>
+      <c r="E24" s="43" t="n"/>
+      <c r="F24" s="43" t="n"/>
+      <c r="G24" s="43" t="n"/>
+      <c r="H24" s="44" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="27" t="n"/>
-      <c r="B25" s="27" t="n"/>
-      <c r="C25" s="27" t="n"/>
-      <c r="D25" s="27" t="n"/>
-      <c r="E25" s="27" t="n"/>
-      <c r="F25" s="27" t="n"/>
-      <c r="G25" s="37">
-        <f>IF(OR(F29="",F29="در انتظار"),"",IF(G29="",TODAY(),G29))</f>
-        <v/>
-      </c>
+      <c r="A25" s="43" t="n"/>
+      <c r="B25" s="43" t="n"/>
+      <c r="C25" s="43" t="n"/>
+      <c r="D25" s="43" t="n"/>
+      <c r="E25" s="43" t="n"/>
+      <c r="F25" s="43" t="n"/>
+      <c r="G25" s="43" t="n"/>
+      <c r="H25" s="44" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="27" t="n"/>
-      <c r="B26" s="27" t="n"/>
-      <c r="C26" s="27" t="n"/>
-      <c r="D26" s="27" t="n"/>
-      <c r="E26" s="27" t="n"/>
-      <c r="F26" s="27" t="n"/>
-      <c r="G26" s="37">
-        <f>IF(OR(F30="",F30="در انتظار"),"",IF(G30="",TODAY(),G30))</f>
-        <v/>
-      </c>
+      <c r="A26" s="43" t="n"/>
+      <c r="B26" s="43" t="n"/>
+      <c r="C26" s="43" t="n"/>
+      <c r="D26" s="43" t="n"/>
+      <c r="E26" s="43" t="n"/>
+      <c r="F26" s="43" t="n"/>
+      <c r="G26" s="43" t="n"/>
+      <c r="H26" s="44" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="27" t="n"/>
-      <c r="B27" s="27" t="n"/>
-      <c r="C27" s="27" t="n"/>
-      <c r="D27" s="27" t="n"/>
-      <c r="E27" s="27" t="n"/>
-      <c r="F27" s="27" t="n"/>
-      <c r="G27" s="37">
-        <f>IF(OR(F31="",F31="در انتظار"),"",IF(G31="",TODAY(),G31))</f>
-        <v/>
-      </c>
+      <c r="A27" s="43" t="n"/>
+      <c r="B27" s="43" t="n"/>
+      <c r="C27" s="43" t="n"/>
+      <c r="D27" s="43" t="n"/>
+      <c r="E27" s="43" t="n"/>
+      <c r="F27" s="43" t="n"/>
+      <c r="G27" s="43" t="n"/>
+      <c r="H27" s="44" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="27" t="n"/>
-      <c r="B28" s="27" t="n"/>
-      <c r="C28" s="27" t="n"/>
-      <c r="D28" s="27" t="n"/>
-      <c r="E28" s="27" t="n"/>
-      <c r="F28" s="27" t="n"/>
-      <c r="G28" s="37">
-        <f>IF(OR(F32="",F32="در انتظار"),"",IF(G32="",TODAY(),G32))</f>
-        <v/>
-      </c>
+      <c r="A28" s="43" t="n"/>
+      <c r="B28" s="43" t="n"/>
+      <c r="C28" s="43" t="n"/>
+      <c r="D28" s="43" t="n"/>
+      <c r="E28" s="43" t="n"/>
+      <c r="F28" s="43" t="n"/>
+      <c r="G28" s="43" t="n"/>
+      <c r="H28" s="44" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="27" t="n"/>
-      <c r="B29" s="27" t="n"/>
-      <c r="C29" s="27" t="n"/>
-      <c r="D29" s="27" t="n"/>
-      <c r="E29" s="27" t="n"/>
-      <c r="F29" s="27" t="n"/>
-      <c r="G29" s="37">
-        <f>IF(OR(F33="",F33="در انتظار"),"",IF(G33="",TODAY(),G33))</f>
-        <v/>
-      </c>
+      <c r="A29" s="43" t="n"/>
+      <c r="B29" s="43" t="n"/>
+      <c r="C29" s="43" t="n"/>
+      <c r="D29" s="43" t="n"/>
+      <c r="E29" s="43" t="n"/>
+      <c r="F29" s="43" t="n"/>
+      <c r="G29" s="43" t="n"/>
+      <c r="H29" s="44" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="27" t="n"/>
-      <c r="B30" s="27" t="n"/>
-      <c r="C30" s="27" t="n"/>
-      <c r="D30" s="27" t="n"/>
-      <c r="E30" s="27" t="n"/>
-      <c r="F30" s="27" t="n"/>
-      <c r="G30" s="37">
-        <f>IF(OR(F34="",F34="در انتظار"),"",IF(G34="",TODAY(),G34))</f>
-        <v/>
-      </c>
+      <c r="A30" s="43" t="n"/>
+      <c r="B30" s="43" t="n"/>
+      <c r="C30" s="43" t="n"/>
+      <c r="D30" s="43" t="n"/>
+      <c r="E30" s="43" t="n"/>
+      <c r="F30" s="43" t="n"/>
+      <c r="G30" s="43" t="n"/>
+      <c r="H30" s="44" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="27" t="n"/>
-      <c r="B31" s="27" t="n"/>
-      <c r="C31" s="27" t="n"/>
-      <c r="D31" s="27" t="n"/>
-      <c r="E31" s="27" t="n"/>
-      <c r="F31" s="27" t="n"/>
-      <c r="G31" s="37">
-        <f>IF(OR(F35="",F35="در انتظار"),"",IF(G35="",TODAY(),G35))</f>
-        <v/>
-      </c>
+      <c r="A31" s="43" t="n"/>
+      <c r="B31" s="43" t="n"/>
+      <c r="C31" s="43" t="n"/>
+      <c r="D31" s="43" t="n"/>
+      <c r="E31" s="43" t="n"/>
+      <c r="F31" s="43" t="n"/>
+      <c r="G31" s="43" t="n"/>
+      <c r="H31" s="44" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="27" t="n"/>
-      <c r="B32" s="27" t="n"/>
-      <c r="C32" s="27" t="n"/>
-      <c r="D32" s="27" t="n"/>
-      <c r="E32" s="27" t="n"/>
-      <c r="F32" s="27" t="n"/>
-      <c r="G32" s="37">
-        <f>IF(OR(F36="",F36="در انتظار"),"",IF(G36="",TODAY(),G36))</f>
-        <v/>
-      </c>
+      <c r="A32" s="43" t="n"/>
+      <c r="B32" s="43" t="n"/>
+      <c r="C32" s="43" t="n"/>
+      <c r="D32" s="43" t="n"/>
+      <c r="E32" s="43" t="n"/>
+      <c r="F32" s="43" t="n"/>
+      <c r="G32" s="43" t="n"/>
+      <c r="H32" s="44" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="27" t="n"/>
-      <c r="B33" s="27" t="n"/>
-      <c r="C33" s="27" t="n"/>
-      <c r="D33" s="27" t="n"/>
-      <c r="E33" s="27" t="n"/>
-      <c r="F33" s="27" t="n"/>
-      <c r="G33" s="37">
-        <f>IF(OR(F37="",F37="در انتظار"),"",IF(G37="",TODAY(),G37))</f>
-        <v/>
-      </c>
+      <c r="A33" s="43" t="n"/>
+      <c r="B33" s="43" t="n"/>
+      <c r="C33" s="43" t="n"/>
+      <c r="D33" s="43" t="n"/>
+      <c r="E33" s="43" t="n"/>
+      <c r="F33" s="43" t="n"/>
+      <c r="G33" s="43" t="n"/>
+      <c r="H33" s="44" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="27" t="n"/>
-      <c r="B34" s="27" t="n"/>
-      <c r="C34" s="27" t="n"/>
-      <c r="D34" s="27" t="n"/>
-      <c r="E34" s="27" t="n"/>
-      <c r="F34" s="27" t="n"/>
-      <c r="G34" s="37">
-        <f>IF(OR(F38="",F38="در انتظار"),"",IF(G38="",TODAY(),G38))</f>
-        <v/>
-      </c>
+      <c r="A34" s="43" t="n"/>
+      <c r="B34" s="43" t="n"/>
+      <c r="C34" s="43" t="n"/>
+      <c r="D34" s="43" t="n"/>
+      <c r="E34" s="43" t="n"/>
+      <c r="F34" s="43" t="n"/>
+      <c r="G34" s="43" t="n"/>
+      <c r="H34" s="44" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="27" t="n"/>
-      <c r="B35" s="27" t="n"/>
-      <c r="C35" s="27" t="n"/>
-      <c r="D35" s="27" t="n"/>
-      <c r="E35" s="27" t="n"/>
-      <c r="F35" s="27" t="n"/>
-      <c r="G35" s="37">
-        <f>IF(OR(F39="",F39="در انتظار"),"",IF(G39="",TODAY(),G39))</f>
-        <v/>
-      </c>
+      <c r="A35" s="43" t="n"/>
+      <c r="B35" s="43" t="n"/>
+      <c r="C35" s="43" t="n"/>
+      <c r="D35" s="43" t="n"/>
+      <c r="E35" s="43" t="n"/>
+      <c r="F35" s="43" t="n"/>
+      <c r="G35" s="43" t="n"/>
+      <c r="H35" s="44" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="27" t="n"/>
-      <c r="B36" s="27" t="n"/>
-      <c r="C36" s="27" t="n"/>
-      <c r="D36" s="27" t="n"/>
-      <c r="E36" s="27" t="n"/>
-      <c r="F36" s="27" t="n"/>
-      <c r="G36" s="37">
-        <f>IF(OR(F40="",F40="در انتظار"),"",IF(G40="",TODAY(),G40))</f>
-        <v/>
-      </c>
+      <c r="A36" s="43" t="n"/>
+      <c r="B36" s="43" t="n"/>
+      <c r="C36" s="43" t="n"/>
+      <c r="D36" s="43" t="n"/>
+      <c r="E36" s="43" t="n"/>
+      <c r="F36" s="43" t="n"/>
+      <c r="G36" s="43" t="n"/>
+      <c r="H36" s="44" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="27" t="n"/>
-      <c r="B37" s="27" t="n"/>
-      <c r="C37" s="27" t="n"/>
-      <c r="D37" s="27" t="n"/>
-      <c r="E37" s="27" t="n"/>
-      <c r="F37" s="27" t="n"/>
-      <c r="G37" s="37">
-        <f>IF(OR(F41="",F41="در انتظار"),"",IF(G41="",TODAY(),G41))</f>
-        <v/>
-      </c>
+      <c r="A37" s="43" t="n"/>
+      <c r="B37" s="43" t="n"/>
+      <c r="C37" s="43" t="n"/>
+      <c r="D37" s="43" t="n"/>
+      <c r="E37" s="43" t="n"/>
+      <c r="F37" s="43" t="n"/>
+      <c r="G37" s="43" t="n"/>
+      <c r="H37" s="44" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="27" t="n"/>
-      <c r="B38" s="27" t="n"/>
-      <c r="C38" s="27" t="n"/>
-      <c r="D38" s="27" t="n"/>
-      <c r="E38" s="27" t="n"/>
-      <c r="F38" s="27" t="n"/>
-      <c r="G38" s="37">
-        <f>IF(OR(F42="",F42="در انتظار"),"",IF(G42="",TODAY(),G42))</f>
-        <v/>
-      </c>
+      <c r="A38" s="43" t="n"/>
+      <c r="B38" s="43" t="n"/>
+      <c r="C38" s="43" t="n"/>
+      <c r="D38" s="43" t="n"/>
+      <c r="E38" s="43" t="n"/>
+      <c r="F38" s="43" t="n"/>
+      <c r="G38" s="43" t="n"/>
+      <c r="H38" s="44" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="27" t="n"/>
-      <c r="B39" s="27" t="n"/>
-      <c r="C39" s="27" t="n"/>
-      <c r="D39" s="27" t="n"/>
-      <c r="E39" s="27" t="n"/>
-      <c r="F39" s="27" t="n"/>
-      <c r="G39" s="37">
-        <f>IF(OR(F43="",F43="در انتظار"),"",IF(G43="",TODAY(),G43))</f>
-        <v/>
-      </c>
+      <c r="A39" s="43" t="n"/>
+      <c r="B39" s="43" t="n"/>
+      <c r="C39" s="43" t="n"/>
+      <c r="D39" s="43" t="n"/>
+      <c r="E39" s="43" t="n"/>
+      <c r="F39" s="43" t="n"/>
+      <c r="G39" s="43" t="n"/>
+      <c r="H39" s="44" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="27" t="n"/>
-      <c r="B40" s="27" t="n"/>
-      <c r="C40" s="27" t="n"/>
-      <c r="D40" s="27" t="n"/>
-      <c r="E40" s="27" t="n"/>
-      <c r="F40" s="27" t="n"/>
-      <c r="G40" s="37">
-        <f>IF(OR(F44="",F44="در انتظار"),"",IF(G44="",TODAY(),G44))</f>
-        <v/>
-      </c>
+      <c r="A40" s="43" t="n"/>
+      <c r="B40" s="43" t="n"/>
+      <c r="C40" s="43" t="n"/>
+      <c r="D40" s="43" t="n"/>
+      <c r="E40" s="43" t="n"/>
+      <c r="F40" s="43" t="n"/>
+      <c r="G40" s="43" t="n"/>
+      <c r="H40" s="44" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="27" t="n"/>
-      <c r="B41" s="27" t="n"/>
-      <c r="C41" s="27" t="n"/>
-      <c r="D41" s="27" t="n"/>
-      <c r="E41" s="27" t="n"/>
-      <c r="F41" s="27" t="n"/>
-      <c r="G41" s="37">
-        <f>IF(OR(F45="",F45="در انتظار"),"",IF(G45="",TODAY(),G45))</f>
-        <v/>
-      </c>
+      <c r="A41" s="43" t="n"/>
+      <c r="B41" s="43" t="n"/>
+      <c r="C41" s="43" t="n"/>
+      <c r="D41" s="43" t="n"/>
+      <c r="E41" s="43" t="n"/>
+      <c r="F41" s="43" t="n"/>
+      <c r="G41" s="43" t="n"/>
+      <c r="H41" s="44" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="27" t="n"/>
-      <c r="B42" s="27" t="n"/>
-      <c r="C42" s="27" t="n"/>
-      <c r="D42" s="27" t="n"/>
-      <c r="E42" s="27" t="n"/>
-      <c r="F42" s="27" t="n"/>
-      <c r="G42" s="37">
-        <f>IF(OR(F46="",F46="در انتظار"),"",IF(G46="",TODAY(),G46))</f>
-        <v/>
-      </c>
+      <c r="A42" s="43" t="n"/>
+      <c r="B42" s="43" t="n"/>
+      <c r="C42" s="43" t="n"/>
+      <c r="D42" s="43" t="n"/>
+      <c r="E42" s="43" t="n"/>
+      <c r="F42" s="43" t="n"/>
+      <c r="G42" s="43" t="n"/>
+      <c r="H42" s="44" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="27" t="n"/>
-      <c r="B43" s="27" t="n"/>
-      <c r="C43" s="27" t="n"/>
-      <c r="D43" s="27" t="n"/>
-      <c r="E43" s="27" t="n"/>
-      <c r="F43" s="27" t="n"/>
-      <c r="G43" s="37">
-        <f>IF(OR(F47="",F47="در انتظار"),"",IF(G47="",TODAY(),G47))</f>
-        <v/>
-      </c>
+      <c r="A43" s="43" t="n"/>
+      <c r="B43" s="43" t="n"/>
+      <c r="C43" s="43" t="n"/>
+      <c r="D43" s="43" t="n"/>
+      <c r="E43" s="43" t="n"/>
+      <c r="F43" s="43" t="n"/>
+      <c r="G43" s="43" t="n"/>
+      <c r="H43" s="44" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="27" t="n"/>
-      <c r="B44" s="27" t="n"/>
-      <c r="C44" s="27" t="n"/>
-      <c r="D44" s="27" t="n"/>
-      <c r="E44" s="27" t="n"/>
-      <c r="F44" s="27" t="n"/>
-      <c r="G44" s="37">
-        <f>IF(OR(F48="",F48="در انتظار"),"",IF(G48="",TODAY(),G48))</f>
-        <v/>
-      </c>
+      <c r="A44" s="43" t="n"/>
+      <c r="B44" s="43" t="n"/>
+      <c r="C44" s="43" t="n"/>
+      <c r="D44" s="43" t="n"/>
+      <c r="E44" s="43" t="n"/>
+      <c r="F44" s="43" t="n"/>
+      <c r="G44" s="43" t="n"/>
+      <c r="H44" s="44" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="27" t="n"/>
-      <c r="B45" s="27" t="n"/>
-      <c r="C45" s="27" t="n"/>
-      <c r="D45" s="27" t="n"/>
-      <c r="E45" s="27" t="n"/>
-      <c r="F45" s="27" t="n"/>
-      <c r="G45" s="37">
-        <f>IF(OR(F49="",F49="در انتظار"),"",IF(G49="",TODAY(),G49))</f>
-        <v/>
-      </c>
+      <c r="A45" s="43" t="n"/>
+      <c r="B45" s="43" t="n"/>
+      <c r="C45" s="43" t="n"/>
+      <c r="D45" s="43" t="n"/>
+      <c r="E45" s="43" t="n"/>
+      <c r="F45" s="43" t="n"/>
+      <c r="G45" s="43" t="n"/>
+      <c r="H45" s="44" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="27" t="n"/>
-      <c r="B46" s="27" t="n"/>
-      <c r="C46" s="27" t="n"/>
-      <c r="D46" s="27" t="n"/>
-      <c r="E46" s="27" t="n"/>
-      <c r="F46" s="27" t="n"/>
-      <c r="G46" s="37">
-        <f>IF(OR(F50="",F50="در انتظار"),"",IF(G50="",TODAY(),G50))</f>
-        <v/>
-      </c>
+      <c r="A46" s="43" t="n"/>
+      <c r="B46" s="43" t="n"/>
+      <c r="C46" s="43" t="n"/>
+      <c r="D46" s="43" t="n"/>
+      <c r="E46" s="43" t="n"/>
+      <c r="F46" s="43" t="n"/>
+      <c r="G46" s="43" t="n"/>
+      <c r="H46" s="44" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="27" t="n"/>
-      <c r="B47" s="27" t="n"/>
-      <c r="C47" s="27" t="n"/>
-      <c r="D47" s="27" t="n"/>
-      <c r="E47" s="27" t="n"/>
-      <c r="F47" s="27" t="n"/>
-      <c r="G47" s="37">
-        <f>IF(OR(F51="",F51="در انتظار"),"",IF(G51="",TODAY(),G51))</f>
-        <v/>
-      </c>
+      <c r="A47" s="43" t="n"/>
+      <c r="B47" s="43" t="n"/>
+      <c r="C47" s="43" t="n"/>
+      <c r="D47" s="43" t="n"/>
+      <c r="E47" s="43" t="n"/>
+      <c r="F47" s="43" t="n"/>
+      <c r="G47" s="43" t="n"/>
+      <c r="H47" s="44" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="27" t="n"/>
-      <c r="B48" s="27" t="n"/>
-      <c r="C48" s="27" t="n"/>
-      <c r="D48" s="27" t="n"/>
-      <c r="E48" s="27" t="n"/>
-      <c r="F48" s="27" t="n"/>
-      <c r="G48" s="37">
-        <f>IF(OR(F52="",F52="در انتظار"),"",IF(G52="",TODAY(),G52))</f>
-        <v/>
-      </c>
+      <c r="A48" s="43" t="n"/>
+      <c r="B48" s="43" t="n"/>
+      <c r="C48" s="43" t="n"/>
+      <c r="D48" s="43" t="n"/>
+      <c r="E48" s="43" t="n"/>
+      <c r="F48" s="43" t="n"/>
+      <c r="G48" s="43" t="n"/>
+      <c r="H48" s="44" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="27" t="n"/>
-      <c r="B49" s="27" t="n"/>
-      <c r="C49" s="27" t="n"/>
-      <c r="D49" s="27" t="n"/>
-      <c r="E49" s="27" t="n"/>
-      <c r="F49" s="27" t="n"/>
-      <c r="G49" s="37">
-        <f>IF(OR(F53="",F53="در انتظار"),"",IF(G53="",TODAY(),G53))</f>
-        <v/>
-      </c>
+      <c r="A49" s="43" t="n"/>
+      <c r="B49" s="43" t="n"/>
+      <c r="C49" s="43" t="n"/>
+      <c r="D49" s="43" t="n"/>
+      <c r="E49" s="43" t="n"/>
+      <c r="F49" s="43" t="n"/>
+      <c r="G49" s="43" t="n"/>
+      <c r="H49" s="44" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="27" t="n"/>
-      <c r="B50" s="27" t="n"/>
-      <c r="C50" s="27" t="n"/>
-      <c r="D50" s="27" t="n"/>
-      <c r="E50" s="27" t="n"/>
-      <c r="F50" s="27" t="n"/>
-      <c r="G50" s="37">
-        <f>IF(OR(F54="",F54="در انتظار"),"",IF(G54="",TODAY(),G54))</f>
-        <v/>
-      </c>
+      <c r="A50" s="43" t="n"/>
+      <c r="B50" s="43" t="n"/>
+      <c r="C50" s="43" t="n"/>
+      <c r="D50" s="43" t="n"/>
+      <c r="E50" s="43" t="n"/>
+      <c r="F50" s="43" t="n"/>
+      <c r="G50" s="43" t="n"/>
+      <c r="H50" s="44" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:G52"/>
   <dataValidations count="1">
-    <dataValidation sqref="F2:F94" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" prompt="وضعیت تست را از فهرست انتخاب کنید" type="list">
+    <dataValidation sqref="G2:G10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>='فهرست‌ها'!$A$7:$A$12</formula1>
     </dataValidation>
   </dataValidations>
@@ -2292,8 +2278,6 @@
           <t>ماشین حالت ماژول لاگ تشخیصی (Diag)</t>
         </is>
       </c>
-      <c r="B1" s="27" t="n"/>
-      <c r="C1" s="27" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="27" t="n"/>

--- a/Firmware/Modules/Diag/Diag_Validation.xlsx
+++ b/Firmware/Modules/Diag/Diag_Validation.xlsx
@@ -1691,7 +1691,7 @@
       <c r="E5" s="29" t="n"/>
       <c r="F5" s="31" t="n"/>
       <c r="G5" s="32">
-        <f>IF(OR(F4="",F4="در انتظار"),"",IF(G4="",TODAY(),G4))</f>
+        <f>IF(OR(F5="",F5="در انتظار"),"",IF(G5="",TODAY(),G5))</f>
         <v/>
       </c>
     </row>
@@ -1721,7 +1721,7 @@
       <c r="E6" s="33" t="n"/>
       <c r="F6" s="35" t="n"/>
       <c r="G6" s="36">
-        <f>IF(OR(F3="",F3="در انتظار"),"",IF(G3="",TODAY(),G3))</f>
+        <f>IF(OR(F6="",F6="در انتظار"),"",IF(G6="",TODAY(),G6))</f>
         <v/>
       </c>
     </row>

--- a/Firmware/Modules/Diag/Diag_Validation.xlsx
+++ b/Firmware/Modules/Diag/Diag_Validation.xlsx
@@ -719,6 +719,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="42" t="inlineStr">
         <is>
@@ -806,7 +807,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>بالا</t>
+          <t>متوسط</t>
         </is>
       </c>
       <c r="D2" s="30" t="inlineStr">
@@ -841,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>بالا</t>
+          <t>متوسط</t>
         </is>
       </c>
       <c r="D3" s="34" t="inlineStr">
@@ -876,7 +877,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>بالا</t>
+          <t>متوسط</t>
         </is>
       </c>
       <c r="D4" s="30" t="inlineStr">
@@ -911,7 +912,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>بالا</t>
+          <t>متوسط</t>
         </is>
       </c>
       <c r="D5" s="34" t="inlineStr">

--- a/Firmware/Modules/Diag/Diag_Validation.xlsx
+++ b/Firmware/Modules/Diag/Diag_Validation.xlsx
@@ -688,7 +688,18 @@
     <row r="2">
       <c r="A2" s="25" t="inlineStr">
         <is>
-          <t>Diag | لاگ تشخیصی 11 مورد تأییدشده: زمان کل شارژ هر کانال+مجموع، تعداد شارژ کامل، آپتایم کل+از آخرین ریست، تعداد ریست، ماکس/مین ولتاژها، جریان ماکس، 10 خطای آخر با ساعت، لاگ 20 قطع/وصل، شمارنده‌ها، زمان همگام‌سازی، نسخه/UID</t>
+          <t>Diag | این ماژول 11 چیز را روی برد نگه می‌دارد:
+۱) زمان کل شارژ هر کانال و جمع آن‌ها
+۲) تعداد شارژهای کامل
+۳) زمان روشن‌بودن دستگاه، هم از اول و هم از آخرین ریست
+۴) تعداد ریست‌ها
+۵) بیشترین و کمترین ولتاژها
+۶) بیشترین جریان هر کانال
+۷) 10 خطای آخر، با ساعت رخ‌دادن
+۸) 20 بار قطع و وصل برق شهر
+۹) شمارنده‌ها
+۱۰) زمان همگام‌شدن ساعت
+۱۱) نسخهٔ برنامه و شناسهٔ یکتای تراشه (UID)</t>
         </is>
       </c>
     </row>
@@ -705,7 +716,18 @@
     <row r="5">
       <c r="A5" s="25" t="inlineStr">
         <is>
-          <t>11 مورد ذخیره روی برد تأیید شد: 1) زمان کل شارژ هر کانال+مجموع، 2) تعداد شارژ کامل، 3) آپتایم کل+از آخرین ریست، 4) تعداد ریست، 5) ماکس/مین ولتاژها (Vin/Vpack/Vlow/Vhigh/Imb)، 6) جریان ماکس هر کانال، 7) 10 خطای آخر با ساعت، 8) لاگ 20 قطع/وصل برق شهر، 9) شمارنده‌ها (عدم تعادل/باتری کم/قطع FAULT_CHARGER_BAT_LOST/فنی FAULT_CHARGER_TECHNICAL/FAULT_ADC)، 10) زمان همگام‌سازی ساعت، 11) نسخه/UID</t>
+          <t>11 مورد ذخیره روی برد:
+۱) زمان کل شارژ هر کانال و جمع آن‌ها
+۲) تعداد شارژ کامل
+۳) زمان روشن‌بودن کل و از آخرین ریست
+۴) تعداد ریست
+۵) کمترین و بیشترین ولتاژها (Vin و Vpack و Vlow و Vhigh و Imb)
+۶) بیشترین جریان هر کانال
+۷) 10 خطای آخر با ساعت
+۸) 20 قطع و وصل برق شهر
+۹) شمارنده‌ها (عدم‌توازن، باتری کم، قطع باتری FAULT_CHARGER_BAT_LOST، فنی FAULT_CHARGER_TECHNICAL و FAULT_ADC)
+۱۰) زمان همگام‌سازی ساعت
+۱۱) نسخه و شناسهٔ یکتا (UID)</t>
         </is>
       </c>
     </row>
@@ -715,16 +737,29 @@
     <row r="7">
       <c r="A7" s="25" t="inlineStr">
         <is>
-          <t>تست‌ها: 1) فلش ping-pong 0x0800F800/0xFC00 با CRC32، 2) Init انتخاب رکورد سالم با seq جدیدتر، 3) AddChargeSec هر کانال، 4) RecordChargeComplete، 5) RecordFault با snapshot کامل، 6) RecordPowerOff/On با محاسبه duration، 7) UpdateMinMax، 8) Tick هر ثانیه + debounce save 60s، 9) TIME_SYNC از ESP، 10) DIAG_REQ و ارسال 5 چانک</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
+          <t>تست‌ها:
+۱) فلش به نوبت در دو صفحه نوشته می‌شود (ping-pong): 0x0800F800 و 0x0800FC00. هر رکورد کنترل صحت (CRC32) دارد.
+۲) موقع روشن‌شدن، رکورد سالم با شمارهٔ ترتیب تازه‌تر (seq) انتخاب می‌شود.
+۳) زمان شارژ هر کانال جدا شمرده می‌شود (AddChargeSec).
+۴) پایان شارژ کامل ثبت می‌شود (RecordChargeComplete).
+۵) هر خطا با همهٔ دادهٔ آن لحظه ثبت می‌شود (RecordFault).
+۶) قطع و وصل برق شهر ثبت می‌شود و مدت قطع حساب می‌شود (RecordPowerOff/On).
+۷) کمترین و بیشترین‌ها به‌روز می‌شوند (UpdateMinMax).
+۸) هر ثانیه یک تیک می‌خورد (Tick) و ذخیره با 60 ثانیه صبر آرام (debounce) انجام می‌شود.
+۹) ساعت از ESP همگام می‌شود (TIME_SYNC).
+۱۰) پنل می‌تواند لاگ را بخواهد (DIAG_REQ) و جواب در 5 تکه فرستاده می‌شود.</t>
+        </is>
+      </c>
+    </row>
     <row r="9">
       <c r="A9" s="42" t="inlineStr">
         <is>
-          <t>اولویت تست‌های عملی: «بالا» یعنی رفتار اصلی‌ای که در کار عادی دستگاه می‌بینید (روشن‌شدن، شروع و پایان شارژ، چهره‌های اصلی چراغ‌ها، رفتن تغذیه روی برق ورودی، خطاهای اصلی)؛ اول همین‌ها را انجام دهید. «متوسط» رفتارهای فرعیِ کاربردی است و «پایین» ریزه‌کاری‌ها (مثل اثر نوسان چند درصدی روی ریتم چشمک یا لبه‌های دقیق درصد و زمان).
-ستون «چه چیزی باید ببینید تا بگویید درست است» می‌گوید دقیقاً چه چیزی را باید ببینید یا بشنوید تا آن تست را قبول کنید؛ اگر چیز دیگری دیدید، وضعیت را «رد» بزنید و در شرح ایراد بنویسید چه دیدید.</t>
+          <t>اولویت‌ها ساده‌اند:
+«بالا» یعنی اول همین‌ها را تست کن. این‌ها کارهای اصلی دستگاه‌اند: روشن‌شدن، شروع و پایان شارژ، چراغ‌های اصلی، رفتن تغذیه روی برق ورودی و خطاهای اصلی.
+«متوسط» یعنی کارهای فرعی ولی کاربردی.
+«پایین» یعنی ریزه‌کاری‌ها؛ مثل اثر نوسان کوچک روی ریتم چشمک.
+در ستون «چه چیزی باید ببینید تا بگویید درست است» نوشته‌ایم دقیقاً چه باید ببینی یا بشنوی.
+اگر چیز دیگری دیدی، وضعیت را «رد» بزن و در «شرح ایراد» بنویس چه دیدی.</t>
         </is>
       </c>
     </row>
@@ -763,7 +798,7 @@
           <t>شرح تست</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="26" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
@@ -805,7 +840,7 @@
           <t>RecordChargeComplete</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="30" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -840,7 +875,7 @@
           <t>RecordFault</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="34" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -875,7 +910,7 @@
           <t>PowerOff/On</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="30" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -910,7 +945,7 @@
           <t>DIAG_REQ</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="34" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -944,7 +979,7 @@
           <t>Init بدون رکورد</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="30" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -979,7 +1014,7 @@
           <t>AddChargeSec</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="34" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -1014,7 +1049,7 @@
           <t>Min/Max</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="34" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -1049,7 +1084,7 @@
           <t>TIME_SYNC</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="30" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -1084,7 +1119,7 @@
           <t>ذخیره فلش حین شارژ فعال: تعلیق شارژر دور نوشتن</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="34" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -1610,9 +1645,9 @@
       </c>
       <c r="C3" s="40" t="inlineStr">
         <is>
-          <t>گام ۱ (هاست): ابزار tools/measure_ram.py را اجرا کن و عمق استک تسک کنترل (ctrl) و حافظهٔ آزاد را بخوان.
-گام ۲ (هاست): قاب func__Diag_SaveNow باید روی استک تسک کنترل جا شده باشد و هیچ بافر استاتیک اضافه‌ای در Init نباشد.
-گام ۳ (برد): برد را ریبوت کن و رکورد ذخیره‌شده را بخوان: باید در صفحهٔ قدیمی‌تر با seq+1 نوشته شده و بعد از ریست سالم خوانده شود.</t>
+          <t>گام ۱ (هاست): ابزار tools/measure_ram.py را اجرا کن. عمق استک تسک کنترل (ctrl) و حافظهٔ آزاد را بخوان.
+گام ۲ (هاست): قاب تابع func__Diag_SaveNow باید روی استک تسک کنترل جا شده باشد. در Init هیچ بافر استاتیک اضافه‌ای نباید باشد.
+گام ۳ (برد): برد را ریبوت کن و رکورد ذخیره‌شده را بخوان. باید در صفحهٔ قدیمی‌تر با seq+1 نوشته شده باشد و بعد از ریست سالم خوانده شود.</t>
         </is>
       </c>
       <c r="D3" s="29" t="inlineStr">
@@ -1644,10 +1679,11 @@
       </c>
       <c r="C4" s="40" t="inlineStr">
         <is>
-          <t>گام ۱ (هاست): python3 tools/check_diag_fault_bits.py را اجرا کن؛ باید PASS بدهد (قبل از اصلاح روی کد قدیم FAIL می‌شد).
-گام ۲ (هاست): اسمبلی تابع func__Diag_RecordFault قبل و بعد از اصلاح را مقایسه کن؛ باید بایت‌به‌بایت یکی باشد.
-گام ۳ (برد): از پنل یک‌بار خطای قطع باتری و یک‌بار خطای فنی بساز.
-گام ۴ (برد): شمارنده‌ها را بخوان: هر رویداد باید فقط شمارندهٔ خودش را زیاد کرده باشد (قطع باتری ← FAULT_CHARGER_BAT_LOST، فنی ← FAULT_CHARGER_TECHNICAL، ADC ← شمارندهٔ ovCount). نتیجهٔ برد هنوز در انتظار است.</t>
+          <t>گام ۱ (هاست): python3 tools/check_diag_fault_bits.py را اجرا کن. باید PASS بدهد. (قبل از اصلاح، روی کد قدیم FAIL می‌شد.)
+گام ۲ (هاست): اسمبلی تابع func__Diag_RecordFault را قبل و بعد از اصلاح مقایسه کن. باید بایت‌به‌بایت یکی باشد.
+گام ۳ (برد): از پنل یک بار خطای قطع باتری بساز و یک بار خطای فنی.
+گام ۴ (برد): شمارنده‌ها را بخوان. هر رویداد باید فقط شمارندهٔ خودش را زیاد کرده باشد: قطع باتری برای FAULT_CHARGER_BAT_LOST، خطای فنی برای FAULT_CHARGER_TECHNICAL و خطای ADC برای شمارندهٔ ovCount.
+گام ۵ (برد): نتیجهٔ برد هنوز در انتظار است.</t>
         </is>
       </c>
       <c r="D4" s="29" t="inlineStr">

--- a/Firmware/Modules/Diag/Diag_Validation.xlsx
+++ b/Firmware/Modules/Diag/Diag_Validation.xlsx
@@ -139,7 +139,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -159,6 +159,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9E2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -203,7 +213,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -309,6 +319,24 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="18" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -679,7 +707,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="25" t="inlineStr">
+      <c r="A1" s="45" t="inlineStr">
         <is>
           <t>برگه تست و اعتبارسنجی عملی ماژول Diag</t>
         </is>
@@ -704,7 +732,7 @@
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="26" t="inlineStr">
+      <c r="A3" s="46" t="inlineStr">
         <is>
           <t>هدف فایل</t>
         </is>
@@ -714,7 +742,7 @@
       <c r="A4" s="27" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="47" t="inlineStr">
         <is>
           <t>11 مورد ذخیره روی برد:
 ۱) زمان کل شارژ هر کانال و جمع آن‌ها
@@ -735,7 +763,7 @@
       <c r="A6" s="27" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="25" t="inlineStr">
+      <c r="A7" s="47" t="inlineStr">
         <is>
           <t>تست‌ها:
 ۱) فلش به نوبت در دو صفحه نوشته می‌شود (ping-pong): 0x0800F800 و 0x0800FC00. هر رکورد کنترل صحت (CRC32) دارد.
@@ -751,8 +779,9 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
-      <c r="A9" s="42" t="inlineStr">
+      <c r="A9" s="48" t="inlineStr">
         <is>
           <t>اولویت‌ها ساده‌اند:
 «بالا» یعنی اول همین‌ها را تست کن. این‌ها کارهای اصلی دستگاه‌اند: روشن‌شدن، شروع و پایان شارژ، چراغ‌های اصلی، رفتن تغذیه روی برق ورودی و خطاهای اصلی.
@@ -788,42 +817,42 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="26" t="inlineStr">
+      <c r="A1" s="46" t="inlineStr">
         <is>
           <t>ردیف</t>
         </is>
       </c>
-      <c r="B1" s="26" t="inlineStr">
+      <c r="B1" s="46" t="inlineStr">
         <is>
           <t>شرح تست</t>
         </is>
       </c>
-      <c r="C1" s="26" t="inlineStr">
+      <c r="C1" s="46" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D1" s="26" t="inlineStr">
+      <c r="D1" s="46" t="inlineStr">
         <is>
           <t>روش</t>
         </is>
       </c>
-      <c r="E1" s="26" t="inlineStr">
+      <c r="E1" s="46" t="inlineStr">
         <is>
           <t>چه چیزی باید ببینید تا بگویید درست است</t>
         </is>
       </c>
-      <c r="F1" s="26" t="inlineStr">
+      <c r="F1" s="46" t="inlineStr">
         <is>
           <t>نتیجه واقعی</t>
         </is>
       </c>
-      <c r="G1" s="26" t="inlineStr">
+      <c r="G1" s="46" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="H1" s="26" t="inlineStr">
+      <c r="H1" s="46" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
@@ -870,31 +899,31 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B3" s="33" t="inlineStr">
+      <c r="B3" s="49" t="inlineStr">
         <is>
           <t>RecordFault</t>
         </is>
       </c>
-      <c r="C3" s="34" t="inlineStr">
+      <c r="C3" s="50" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D3" s="34" t="inlineStr">
+      <c r="D3" s="50" t="inlineStr">
         <is>
           <t>گام ۱: ساعت دستگاه را از پنل درست کن.
 گام ۲: حین شارژ سیم باتری را بکش تا خطای ۶ بیاید.
 گام ۳: در سوابق پنل ببین خطا با زمان درست ثبت شده.</t>
         </is>
       </c>
-      <c r="E3" s="33" t="inlineStr">
+      <c r="E3" s="49" t="inlineStr">
         <is>
           <t>باید ببینید: خطای قطع باتری در سوابق پنل با زمان درست هست. اگر نبود یا زمانش غلط بود، قبول نیست.</t>
         </is>
       </c>
       <c r="F3" s="33" t="n"/>
       <c r="G3" s="35" t="n"/>
-      <c r="H3" s="36">
+      <c r="H3" s="51">
         <f>IF(OR(G3="",G3="در انتظار"),"",IF(H3="",TODAY(),H3))</f>
         <v/>
       </c>
@@ -940,30 +969,30 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B5" s="33" t="inlineStr">
+      <c r="B5" s="49" t="inlineStr">
         <is>
           <t>DIAG_REQ</t>
         </is>
       </c>
-      <c r="C5" s="34" t="inlineStr">
+      <c r="C5" s="50" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D5" s="34" t="inlineStr">
+      <c r="D5" s="50" t="inlineStr">
         <is>
           <t>گام ۱: در پنل درخواست گزارش کامل بده.
 گام ۲: صبر کن همهٔ بخش‌های گزارش بیاید و بخوانشان.</t>
         </is>
       </c>
-      <c r="E5" s="33" t="inlineStr">
+      <c r="E5" s="49" t="inlineStr">
         <is>
           <t>باید ببینید: گزارش کامل و خوانا می‌آید و بخشی گم نمی‌شود. اگر ناقص آمد، قبول نیست.</t>
         </is>
       </c>
       <c r="F5" s="33" t="n"/>
       <c r="G5" s="35" t="n"/>
-      <c r="H5" s="36">
+      <c r="H5" s="51">
         <f>IF(OR(G5="",G5="در انتظار"),"",IF(H5="",TODAY(),H5))</f>
         <v/>
       </c>
@@ -1009,31 +1038,31 @@
           <t>4</t>
         </is>
       </c>
-      <c r="B7" s="33" t="inlineStr">
+      <c r="B7" s="49" t="inlineStr">
         <is>
           <t>AddChargeSec</t>
         </is>
       </c>
-      <c r="C7" s="34" t="inlineStr">
+      <c r="C7" s="50" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D7" s="34" t="inlineStr">
+      <c r="D7" s="50" t="inlineStr">
         <is>
           <t>گام ۱: یک باتری نیمه‌خالی را به شارژ واقعی بزن و زمان بگیر.
 گام ۲: بعد از مدتی شارژ، از پنل گزارش زمان شارژ همان کانال را بخوان.
 گام ۳: عدد گزارش را با زمان واقعی خودت مقایسه کن.</t>
         </is>
       </c>
-      <c r="E7" s="33" t="inlineStr">
+      <c r="E7" s="49" t="inlineStr">
         <is>
           <t>باید ببینید: زمان شارژ ثبت‌شده با زمان واقعی می‌خواند و برای هر کانال جدا نگه داشته می‌شود. اگر نخواند، قبول نیست.</t>
         </is>
       </c>
       <c r="F7" s="33" t="n"/>
       <c r="G7" s="35" t="n"/>
-      <c r="H7" s="36">
+      <c r="H7" s="51">
         <f>IF(OR(G7="",G7="در انتظار"),"",IF(H7="",TODAY(),H7))</f>
         <v/>
       </c>
@@ -1044,31 +1073,31 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B8" s="33" t="inlineStr">
+      <c r="B8" s="29" t="inlineStr">
         <is>
           <t>Min/Max</t>
         </is>
       </c>
-      <c r="C8" s="34" t="inlineStr">
+      <c r="C8" s="30" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D8" s="34" t="inlineStr">
+      <c r="D8" s="30" t="inlineStr">
         <is>
           <t>گام ۱: ورودی را از منبع آزمایشگاهی بده.
 گام ۲: ولتاژ را آرام از کم به زیاد و برگردان (مثلاً ۱۸ تا ۳۰ ولت).
 گام ۳: کمینه و بیشینهٔ ثبت‌شده را در گزارش با منبع مقایسه کن.</t>
         </is>
       </c>
-      <c r="E8" s="33" t="inlineStr">
+      <c r="E8" s="29" t="inlineStr">
         <is>
           <t>باید ببینید: کمینه و بیشینهٔ ولتاژ ورودی در گزارش با منبع آزمایشگاهی می‌خواند. اگر نخواند، قبول نیست.</t>
         </is>
       </c>
       <c r="F8" s="33" t="n"/>
       <c r="G8" s="35" t="n"/>
-      <c r="H8" s="36">
+      <c r="H8" s="32">
         <f>IF(OR(G8="",G8="در انتظار"),"",IF(H8="",TODAY(),H8))</f>
         <v/>
       </c>
@@ -1079,31 +1108,31 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B9" s="29" t="inlineStr">
+      <c r="B9" s="49" t="inlineStr">
         <is>
           <t>TIME_SYNC</t>
         </is>
       </c>
-      <c r="C9" s="30" t="inlineStr">
+      <c r="C9" s="50" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D9" s="30" t="inlineStr">
+      <c r="D9" s="50" t="inlineStr">
         <is>
           <t>گام ۱: از پنل ساعت دستگاه را با ساعت کامپیوتر همگام کن.
 گام ۲: یک رویداد بساز (مثلاً خطای ۶).
 گام ۳: زمان رویداد را در سوابق با ساعت واقعی مقایسه کن.</t>
         </is>
       </c>
-      <c r="E9" s="29" t="inlineStr">
+      <c r="E9" s="49" t="inlineStr">
         <is>
           <t>باید ببینید: زمان رویدادها با ساعت واقعی می‌خواند. اگر اختلاف دیدید، قبول نیست.</t>
         </is>
       </c>
       <c r="F9" s="29" t="n"/>
       <c r="G9" s="31" t="n"/>
-      <c r="H9" s="32">
+      <c r="H9" s="51">
         <f>IF(OR(G9="",G9="در انتظار"),"",IF(H9="",TODAY(),H9))</f>
         <v/>
       </c>
@@ -1114,35 +1143,35 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B10" s="33" t="inlineStr">
+      <c r="B10" s="29" t="inlineStr">
         <is>
           <t>ذخیره فلش حین شارژ فعال: تعلیق شارژر دور نوشتن</t>
         </is>
       </c>
-      <c r="C10" s="34" t="inlineStr">
+      <c r="C10" s="30" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D10" s="34" t="inlineStr">
+      <c r="D10" s="30" t="inlineStr">
         <is>
           <t>گام ۱: شارژ واقعی یک باتری را شروع کن.
 گام ۲: حین شارژ یک خطای ۶ بساز و پاک کن تا دستگاه سابقه ذخیره کند.
 گام ۳: بعدش ببین شارژ عادی ادامه دارد و گزارش تازه سالم خوانده می‌شود.</t>
         </is>
       </c>
-      <c r="E10" s="33" t="inlineStr">
+      <c r="E10" s="29" t="inlineStr">
         <is>
           <t>باید ببینید: ذخیره‌شدن سابقه وسط شارژ، شارژ را خراب نمی‌کند و گزارش سالم خوانده می‌شود. اگر شارژ به‌هم ریخت، قبول نیست.</t>
         </is>
       </c>
-      <c r="F10" s="33" t="inlineStr">
+      <c r="F10" s="29" t="inlineStr">
         <is>
           <t>هاست: هر دو گیت سبز و بودجه RAM/استک سالم (ctrl ‏384/1024‎، آزاد 1544 بایت)؛ نتیجه برد: در انتظار</t>
         </is>
       </c>
       <c r="G10" s="35" t="n"/>
-      <c r="H10" s="36">
+      <c r="H10" s="32">
         <f>IF(OR(G10="",G10="در انتظار"),"",IF(H10="",TODAY(),H10))</f>
         <v/>
       </c>
@@ -1562,7 +1591,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00808080"/>
+    <tabColor rgb="00385723"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1579,7 +1608,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="38" t="inlineStr">
+      <c r="A1" s="45" t="inlineStr">
         <is>
           <t>تست‌های برنامه‌نویسی و هاست (جدا از ولیدیشن عملی برد)</t>
         </is>
@@ -1596,37 +1625,37 @@
       <c r="G1" s="27" t="n"/>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="26" t="inlineStr">
+      <c r="A2" s="46" t="inlineStr">
         <is>
           <t>ردیف</t>
         </is>
       </c>
-      <c r="B2" s="26" t="inlineStr">
+      <c r="B2" s="46" t="inlineStr">
         <is>
           <t>شرح تست</t>
         </is>
       </c>
-      <c r="C2" s="26" t="inlineStr">
+      <c r="C2" s="46" t="inlineStr">
         <is>
           <t>روش</t>
         </is>
       </c>
-      <c r="D2" s="26" t="inlineStr">
+      <c r="D2" s="46" t="inlineStr">
         <is>
           <t>نتیجه مورد انتظار</t>
         </is>
       </c>
-      <c r="E2" s="26" t="inlineStr">
+      <c r="E2" s="46" t="inlineStr">
         <is>
           <t>نتیجه واقعی</t>
         </is>
       </c>
-      <c r="F2" s="26" t="inlineStr">
+      <c r="F2" s="46" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="G2" s="26" t="inlineStr">
+      <c r="G2" s="46" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
@@ -1672,12 +1701,12 @@
           <t>13</t>
         </is>
       </c>
-      <c r="B4" s="29" t="inlineStr">
+      <c r="B4" s="49" t="inlineStr">
         <is>
           <t>شمارنده‌های خطا با نام FAULT_* رمزگشایی می‌شوند (نه شماره خام بیت)</t>
         </is>
       </c>
-      <c r="C4" s="40" t="inlineStr">
+      <c r="C4" s="52" t="inlineStr">
         <is>
           <t>گام ۱ (هاست): python3 tools/check_diag_fault_bits.py را اجرا کن. باید PASS بدهد. (قبل از اصلاح، روی کد قدیم FAIL می‌شد.)
 گام ۲ (هاست): اسمبلی تابع func__Diag_RecordFault را قبل و بعد از اصلاح مقایسه کن. باید بایت‌به‌بایت یکی باشد.
@@ -1686,18 +1715,18 @@
 گام ۵ (برد): نتیجهٔ برد هنوز در انتظار است.</t>
         </is>
       </c>
-      <c r="D4" s="29" t="inlineStr">
+      <c r="D4" s="49" t="inlineStr">
         <is>
           <t>چک هاست PASS؛ اسمبلی تابع قبل/بعد بایت‌به‌بایت یکسان؛ روی برد هر رویداد فقط شمارنده خودش را زیاد کند</t>
         </is>
       </c>
-      <c r="E4" s="29" t="inlineStr">
+      <c r="E4" s="49" t="inlineStr">
         <is>
           <t>هاست 2026-10-15: چک‌نگهبان اول روی کد قدیم FAIL شد (هر سه خط خام را گرفت)، بعد از اصلاح PASS؛ اسمبلی یکسان؛ هر دو گیت سبز؛ نتیجه برد: در انتظار</t>
         </is>
       </c>
       <c r="F4" s="31" t="n"/>
-      <c r="G4" s="32">
+      <c r="G4" s="51">
         <f>IF(OR(F4="",F4="در انتظار"),"",IF(G4="",TODAY(),G4))</f>
         <v/>
       </c>
@@ -1738,26 +1767,26 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B6" s="33" t="inlineStr">
+      <c r="B6" s="49" t="inlineStr">
         <is>
           <t>Init با یک رکورد سالم</t>
         </is>
       </c>
-      <c r="C6" s="34" t="inlineStr">
+      <c r="C6" s="50" t="inlineStr">
         <is>
           <t>گام ۱: یک رکورد سالم با CRC درست در صفحهٔ A بنویس و بقیهٔ فلش را خالی بگذار.
 گام ۲: برد را بوت کن.
 گام ۳: رکورد خوانده‌شده را با همان رکوردی که نوشتی مقایسه کن؛ باید عیناً همان باشد (CRC درست یعنی پذیرفته شده).</t>
         </is>
       </c>
-      <c r="D6" s="33" t="inlineStr">
+      <c r="D6" s="49" t="inlineStr">
         <is>
           <t>همان رکورد خوانده شود</t>
         </is>
       </c>
       <c r="E6" s="33" t="n"/>
       <c r="F6" s="35" t="n"/>
-      <c r="G6" s="36">
+      <c r="G6" s="51">
         <f>IF(OR(F6="",F6="در انتظار"),"",IF(G6="",TODAY(),G6))</f>
         <v/>
       </c>
@@ -1997,16 +2026,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="26" t="inlineStr">
+      <c r="A1" s="46" t="inlineStr">
         <is>
           <t>سناریو</t>
         </is>
       </c>
-      <c r="B1" s="26" t="inlineStr">
+      <c r="B1" s="46" t="inlineStr">
         <is>
           <t>مرجع کد</t>
         </is>
@@ -2036,6 +2065,10 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId1"/>
@@ -2052,7 +2085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2123,6 +2156,9 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId1"/>
@@ -2139,7 +2175,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2162,6 +2198,11 @@
       </c>
       <c r="B2" s="27" t="n"/>
     </row>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2170,7 +2211,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00808080"/>
+    <tabColor rgb="00A6A6A6"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -2302,7 +2343,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2316,11 +2357,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="27" t="n"/>
-      <c r="B2" s="27" t="n"/>
-      <c r="C2" s="27" t="n"/>
-    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -2332,7 +2369,6 @@
           <t>Diag_State_Machine.xlsx</t>
         </is>
       </c>
-      <c r="C3" s="27" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -2345,7 +2381,6 @@
           <t>../../../Documentation/System_State_Machine.xlsx</t>
         </is>
       </c>
-      <c r="C4" s="27" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
@@ -2358,7 +2393,6 @@
           <t>سبز = عادی/سالم · زرد = هشدار یا انتظار · قرمز = خطا یا قفل · نارنجی = در حال کار · خاکستری = بی‌کار · آبی = اطلاعاتی</t>
         </is>
       </c>
-      <c r="C5" s="27" t="n"/>
     </row>
     <row r="6" ht="24" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -2366,13 +2400,13 @@
           <t>بازتولید</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>python3 tools/make_module_state_machines.py</t>
         </is>
       </c>
-      <c r="C6" s="27" t="n"/>
-    </row>
+    </row>
+    <row r="7"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
@@ -2380,7 +2414,6 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Firmware/Modules/Diag/Diag_Validation.xlsx
+++ b/Firmware/Modules/Diag/Diag_Validation.xlsx
@@ -31,7 +31,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -138,6 +138,11 @@
       <name val="Vazirmatn"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <color rgb="00808080"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -213,7 +218,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -336,6 +341,15 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -703,7 +717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -779,7 +793,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="48" t="inlineStr">
         <is>
@@ -789,6 +802,18 @@
 «پایین» یعنی ریزه‌کاری‌ها؛ مثل اثر نوسان کوچک روی ریتم چشمک.
 در ستون «چه چیزی باید ببینید تا بگویید درست است» نوشته‌ایم دقیقاً چه باید ببینی یا بشنوی.
 اگر چیز دیگری دیدی، وضعیت را «رد» بزن و در «شرح ایراد» بنویس چه دیدی.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="53" t="inlineStr">
+        <is>
+          <t>پیش‌بینی زندهٔ برنامه</t>
+        </is>
+      </c>
+      <c r="B11" s="54" t="inlineStr">
+        <is>
+          <t>در شیت «برنامه تست»، ستون آخر («پیش‌بینی زندهٔ برنامه») با فرمول اکسل حساب می‌کند که برنامهٔ روی برد با ورودی‌های فعلی چه کار می‌کند. ورودی‌ها خانه‌های زرد بالای همان شیت‌اند؛ عددشان را عوض کن، نتیجه را بخوان و با رفتار واقعی برد مقایسه کن. هر جا «—» است، آن تست پیش‌بینی فرمولی ندارد (مثل دیالوگ پنل یا تست‌های حافظه).</t>
         </is>
       </c>
     </row>
@@ -804,7 +829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -814,6 +839,7 @@
     <col width="38" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="52" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -857,6 +883,11 @@
           <t>تاریخ</t>
         </is>
       </c>
+      <c r="I1" s="46" t="inlineStr">
+        <is>
+          <t>پیش‌بینی زندهٔ برنامه (فرمول)</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="40.5" customHeight="1">
       <c r="A2" s="28" t="inlineStr">
@@ -892,6 +923,11 @@
         <f>IF(OR(G2="",G2="در انتظار"),"",IF(H2="",TODAY(),H2))</f>
         <v/>
       </c>
+      <c r="I2" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="40.5" customHeight="1">
       <c r="A3" s="28" t="inlineStr">
@@ -927,6 +963,11 @@
         <f>IF(OR(G3="",G3="در انتظار"),"",IF(H3="",TODAY(),H3))</f>
         <v/>
       </c>
+      <c r="I3" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="40.5" customHeight="1">
       <c r="A4" s="28" t="inlineStr">
@@ -962,6 +1003,11 @@
         <f>IF(OR(G4="",G4="در انتظار"),"",IF(H4="",TODAY(),H4))</f>
         <v/>
       </c>
+      <c r="I4" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="40.5" customHeight="1">
       <c r="A5" s="28" t="inlineStr">
@@ -996,6 +1042,11 @@
         <f>IF(OR(G5="",G5="در انتظار"),"",IF(H5="",TODAY(),H5))</f>
         <v/>
       </c>
+      <c r="I5" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="40.5" customHeight="1">
       <c r="A6" s="28" t="inlineStr">
@@ -1031,6 +1082,11 @@
         <f>IF(OR(G6="",G6="در انتظار"),"",IF(H6="",TODAY(),H6))</f>
         <v/>
       </c>
+      <c r="I6" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="40.5" customHeight="1">
       <c r="A7" s="28" t="inlineStr">
@@ -1066,6 +1122,11 @@
         <f>IF(OR(G7="",G7="در انتظار"),"",IF(H7="",TODAY(),H7))</f>
         <v/>
       </c>
+      <c r="I7" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="40.5" customHeight="1">
       <c r="A8" s="28" t="inlineStr">
@@ -1101,6 +1162,11 @@
         <f>IF(OR(G8="",G8="در انتظار"),"",IF(H8="",TODAY(),H8))</f>
         <v/>
       </c>
+      <c r="I8" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="54" customHeight="1">
       <c r="A9" s="28" t="inlineStr">
@@ -1136,6 +1202,11 @@
         <f>IF(OR(G9="",G9="در انتظار"),"",IF(H9="",TODAY(),H9))</f>
         <v/>
       </c>
+      <c r="I9" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="40.5" customHeight="1">
       <c r="A10" s="28" t="inlineStr">
@@ -1174,6 +1245,11 @@
       <c r="H10" s="32">
         <f>IF(OR(G10="",G10="در انتظار"),"",IF(H10="",TODAY(),H10))</f>
         <v/>
+      </c>
+      <c r="I10" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -2026,7 +2102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -2065,10 +2141,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId1"/>
@@ -2085,7 +2157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2156,9 +2228,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId1"/>
@@ -2175,7 +2244,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2198,11 +2267,6 @@
       </c>
       <c r="B2" s="27" t="n"/>
     </row>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2343,7 +2407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2357,7 +2421,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -2406,7 +2469,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>

--- a/Firmware/Modules/Diag/Diag_Validation.xlsx
+++ b/Firmware/Modules/Diag/Diag_Validation.xlsx
@@ -1253,14 +1253,45 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="43" t="n"/>
-      <c r="B11" s="43" t="n"/>
-      <c r="C11" s="43" t="n"/>
-      <c r="D11" s="43" t="n"/>
-      <c r="E11" s="43" t="n"/>
-      <c r="F11" s="43" t="n"/>
-      <c r="G11" s="43" t="n"/>
-      <c r="H11" s="44" t="n"/>
+      <c r="A11" s="28" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B11" s="29" t="inlineStr">
+        <is>
+          <t>ذخیره رکورد وسط شارژ پیوسته (دستور کاربر ۲۰۲۶-۱۰-۲۸)</t>
+        </is>
+      </c>
+      <c r="C11" s="30" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D11" s="30" t="inlineStr">
+        <is>
+          <t>گام ۱: یک باتری خالی را به شارژ بزن و شارژ را قطع نکن.
+گام ۲: هر ۵ دقیقه یک بار با پنل گزارش کامل بگیر و «زمان کل شارژ» و «شمارندهٔ روز» را یادداشت کن.
+گام ۳: پس از حدود ۱۲ دقیقه، در حالی که هنوز شارژ ادامه دارد، برق دستگاه را قطع و وصل کن.
+گام ۴: بعد از بالا آمدن، گزارش را دوباره بگیر.</t>
+        </is>
+      </c>
+      <c r="E11" s="29" t="inlineStr">
+        <is>
+          <t>باید ببینید: زمان کل شارژ ذخیره‌شده تا لحظهٔ قطع برق، حداکثر ۱۰ دقیقه عقب‌تر از زمان واقعی است (نه صفر و نه کل شارژ). پیش از اصلاح، این عدد صفر می‌ماند. اگر بیشتر از ۱۰ دقیقه عقب بود، یعنی نوشتن رخ نداده؛ اگر دقیقاً برابر بود، یعنی نوشتن خیلی زودتر از موعد انجام شده که باتری را بی‌دلیل می‌فرساید.</t>
+        </is>
+      </c>
+      <c r="F11" s="29" t="n"/>
+      <c r="G11" s="35" t="n"/>
+      <c r="H11" s="32">
+        <f>IF(OR(G11="",G11="در انتظار"),"",IF(H11="",TODAY(),H11))</f>
+        <v/>
+      </c>
+      <c r="I11" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="43" t="n"/>
@@ -1868,13 +1899,36 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="27" t="n"/>
-      <c r="B7" s="27" t="n"/>
-      <c r="C7" s="27" t="n"/>
-      <c r="D7" s="27" t="n"/>
-      <c r="E7" s="27" t="n"/>
-      <c r="F7" s="27" t="n"/>
-      <c r="G7" s="37">
+      <c r="A7" s="28" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B7" s="29" t="inlineStr">
+        <is>
+          <t>آپتایم از تیک کرنل و ثانیه‌های شارژ از تفاضل آپتایم + ذخیره حین شارژ پیوسته</t>
+        </is>
+      </c>
+      <c r="C7" s="40" t="inlineStr">
+        <is>
+          <t>گام ۱ (هاست): ‏bash Firmware/Modules/Diag/Tester/run_host_test_diag.sh‎ را اجرا کن؛ خودِ ‏diag.c‎ با ساعت بدلی کرنل، شارژر بدلی و دو صفحهٔ فلش نگاشت‌شده روی آدرس واقعی اجرا می‌شود.
+گام ۲: باید ۳۱ بررسی و ۰ خطا بدهد.
+گام ۳ (هاست): همان تست را روی ‏diag.c‎ قبل از اصلاح (‏git show‎) اجرا کن؛ باید در گروه آپتایم و گروه ذخیره شکست بخورد (سنجش A/B).
+گام ۴ (برد): نتیجهٔ برد در تست ۱۵ دیده می‌شود.</t>
+        </is>
+      </c>
+      <c r="D7" s="29" t="inlineStr">
+        <is>
+          <t>۳۱ بررسی PASS؛ در کد قدیم همین تست FAIL؛ ثبت در دروازهٔ ‏tools/check_firmware_syntax.sh‎</t>
+        </is>
+      </c>
+      <c r="E7" s="29" t="inlineStr">
+        <is>
+          <t>هاست 2026-10-28: ‏DIAG HOST TEST: PASS‎ (۳۱/۳۱) و دروازهٔ کامل syntax PASS؛ A/B روی کد قدیم: آپتایم ۱ در برابر ۳۰، نوشتن فلش ۰ در برابر ۳</t>
+        </is>
+      </c>
+      <c r="F7" s="31" t="n"/>
+      <c r="G7" s="32">
         <f>IF(OR(F7="",F7="در انتظار"),"",IF(G7="",TODAY(),G7))</f>
         <v/>
       </c>
@@ -2157,7 +2211,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2225,6 +2279,40 @@
       <c r="C4" s="41" t="inlineStr">
         <is>
           <t>هر سه شرط با ثابت‌های نام‌دار FAULT_CHARGER_BAT_LOST / FAULT_CHARGER_TECHNICAL / FAULT_ADC نوشته شد (نام فیلد ovCount به‌خاطر چیدمان رکورد فلش ماند)؛ نگهبان tools/check_diag_fault_bits.py اضافه شد تا برگشت شماره خام برای همیشه FAIL شود؛ یکسانی رفتار با مقایسه اسمبلی ثابت شد</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="25" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B5" s="41" t="inlineStr">
+        <is>
+          <t>ممیزی ۲۰۲۶-۱۰-۲۸: آپتایم Diag با شمردن ۱۰۰ دورِ حلقهٔ تسک کنترل حساب می‌شد، در حالی که هر دور = تأخیر ‏10ms‎ به‌علاوهٔ کار همان دور. پس «ثانیهٔ» برد بلندتر از ثانیهٔ واقعی بود و چون پنل ساعت دیواری‌اش را روی همین آپتایم می‌بندد (‏HELLO_ACK‎)، ساعتِ بازیابی‌شده هم همان‌قدر کند می‌شد. سنجش: پس از ۳۰ ثانیهٔ واقعی آپتایم ۱ بود، و با پاس ‏12ms‎ پس از ۲۱۶۰ ثانیه آپتایم ۱۸۰۰ (۱۶٪ کند)</t>
+        </is>
+      </c>
+      <c r="C5" s="41" t="inlineStr">
+        <is>
+          <t>آپتایم از شمارندهٔ تیک کرنل خوانده می‌شود (‏osKernelGetTickCount/osKernelGetTickFreq‎) و سرریز ۳۲بیتی تیک با یک شمارندهٔ ثانیهٔ جدا جبران می‌شود. نتیجهٔ همان سنجش: ۳۰ و ۲۱۹۰ ثانیه. تابع ‏func__Diag_UptimeSeconds‎</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="25" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B6" s="41" t="inlineStr">
+        <is>
+          <t>ممیزی ۲۰۲۶-۱۰-۲۸ (مورد ۳ ممیزی): در شارژ پیوسته رکورد دیاگ هرگز روی فلش نمی‌رفت. هر ثانیهٔ شارژ همان دیبانس ۶۰ ثانیه‌ای را از نو مسلح می‌کرد، پس تا وقتی کانالی پیوسته شارژ می‌کرد نوشتن رخ نمی‌داد و قطع برق در میانهٔ شارژ کل ثانیه‌های آن نشست را دور می‌ریخت. سنجش: ۱۸۰۰ ثانیه شارژ → صفر نوشتن</t>
+        </is>
+      </c>
+      <c r="C6" s="41" t="inlineStr">
+        <is>
+          <t>دیبانس فقط روی گذارِ ‏Dirty‎ از خاموش به روشن مسلح می‌شود، و حین شارژ هر ‏DIAG_SAVE_CHARGE_SEC‎ (۶۰۰ ثانیه) یک نوشتن انجام می‌شود. ثانیه‌های شارژ هم از تفاضل آپتایم واقعی گرفته می‌شوند و فاصلهٔ بیش از ‏DIAG_CHARGE_GAP_SEC‎ (۲ ثانیه) بی‌کاری حساب می‌شود، نه شارژ. نتیجهٔ همان سنجش: ۳ نوشتن و ۲۱۵۹ ثانیه در برابر ۲۱۶۰ ثانیهٔ واقعی</t>
         </is>
       </c>
     </row>

--- a/Firmware/Modules/Diag/Diag_Validation.xlsx
+++ b/Firmware/Modules/Diag/Diag_Validation.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="برنامه تست" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="تست‌های برنامه‌نویسی" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="مراجع سناریو" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="ثبت ایراد" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="تأیید نهایی" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="فهرست‌ها" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="ماشین حالت" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="برنامه تست" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تست‌های برنامه‌نویسی" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="مراجع سناریو" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ثبت ایراد" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تأیید نهایی" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="فهرست‌ها" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ماشین حالت" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$1:$G$52</definedName>
